--- a/blendmaster_backend_OOP/output/build_report_2024-11-28_06-00.xlsx
+++ b/blendmaster_backend_OOP/output/build_report_2024-11-28_06-00.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L620"/>
+  <dimension ref="A1:L608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17422,7 +17422,7 @@
         <v>45625.25</v>
       </c>
       <c r="C425" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>45625.25</v>
       </c>
       <c r="C426" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45625.25</v>
       </c>
       <c r="C427" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45625.25</v>
       </c>
       <c r="C428" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45625.25</v>
       </c>
       <c r="C429" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45625.25</v>
       </c>
       <c r="C430" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>45625.25</v>
       </c>
       <c r="C431" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>45625.25</v>
       </c>
       <c r="C432" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>45625.25</v>
       </c>
       <c r="C433" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>45625.25</v>
       </c>
       <c r="C434" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>45625.25</v>
       </c>
       <c r="C435" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45625.25</v>
       </c>
       <c r="C436" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45625.25</v>
       </c>
       <c r="C437" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>45625.25</v>
       </c>
       <c r="C438" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45625.25</v>
       </c>
       <c r="C439" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>45625.25</v>
       </c>
       <c r="C440" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>45625.25</v>
       </c>
       <c r="C441" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>45625.25</v>
       </c>
       <c r="C442" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>45625.25</v>
       </c>
       <c r="C443" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45625.25</v>
       </c>
       <c r="C444" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>45625.25</v>
       </c>
       <c r="C445" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45625.25</v>
       </c>
       <c r="C446" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -18302,7 +18302,7 @@
         <v>45625.25</v>
       </c>
       <c r="C447" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45625.25</v>
       </c>
       <c r="C448" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>45625.25</v>
       </c>
       <c r="C449" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>45625.25</v>
       </c>
       <c r="C450" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>45625.25</v>
       </c>
       <c r="C451" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45625.25</v>
       </c>
       <c r="C452" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45625.25</v>
       </c>
       <c r="C453" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>45625.25</v>
       </c>
       <c r="C454" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45625.25</v>
       </c>
       <c r="C455" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>45625.25</v>
       </c>
       <c r="C456" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>45625.25</v>
       </c>
       <c r="C457" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45625.25</v>
       </c>
       <c r="C458" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45625.25</v>
       </c>
       <c r="C459" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45625.25</v>
       </c>
       <c r="C460" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45625.25</v>
       </c>
       <c r="C461" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>45625.25</v>
       </c>
       <c r="C462" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45625.25</v>
       </c>
       <c r="C463" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>45625.25</v>
       </c>
       <c r="C464" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>45625.25</v>
       </c>
       <c r="C465" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45625.25</v>
       </c>
       <c r="C466" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45625.25</v>
       </c>
       <c r="C467" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>45625.25</v>
       </c>
       <c r="C468" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>45625.25</v>
       </c>
       <c r="C469" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45625.25</v>
       </c>
       <c r="C470" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45625.25</v>
       </c>
       <c r="C471" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45625.25</v>
       </c>
       <c r="C472" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45625.25</v>
       </c>
       <c r="C473" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45625.25</v>
       </c>
       <c r="C474" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>45625.25</v>
       </c>
       <c r="C475" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>45625.25</v>
       </c>
       <c r="C476" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>45625.25</v>
       </c>
       <c r="C477" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45625.25</v>
       </c>
       <c r="C478" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45625.25</v>
       </c>
       <c r="C479" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45625.25</v>
       </c>
       <c r="C480" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45625.25</v>
       </c>
       <c r="C481" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45625.25</v>
       </c>
       <c r="C482" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45625.25</v>
       </c>
       <c r="C483" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45625.25</v>
       </c>
       <c r="C484" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45625.25</v>
       </c>
       <c r="C485" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45625.25</v>
       </c>
       <c r="C486" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45625.25</v>
       </c>
       <c r="C487" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45625.25</v>
       </c>
       <c r="C488" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>45625.25</v>
       </c>
       <c r="C489" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>45625.25</v>
       </c>
       <c r="C490" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45625.25</v>
       </c>
       <c r="C491" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45625.25</v>
       </c>
       <c r="C492" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45625.25</v>
       </c>
       <c r="C493" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45625.25</v>
       </c>
       <c r="C494" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>45625.25</v>
       </c>
       <c r="C495" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>45625.25</v>
       </c>
       <c r="C496" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45625.25</v>
       </c>
       <c r="C497" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45625.25</v>
       </c>
       <c r="C498" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>45625.25</v>
       </c>
       <c r="C499" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45625.25</v>
       </c>
       <c r="C500" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45625.25</v>
       </c>
       <c r="C501" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>45625.25</v>
       </c>
       <c r="C502" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45625.25</v>
       </c>
       <c r="C503" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45625.25</v>
       </c>
       <c r="C504" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45625.25</v>
       </c>
       <c r="C505" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45625.25</v>
       </c>
       <c r="C506" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -20673,25 +20673,25 @@
         <v>240</v>
       </c>
       <c r="F506" s="2" t="n">
-        <v>45625.56811260735</v>
+        <v>45625.25234285779</v>
       </c>
       <c r="G506" t="n">
         <v>372610.9866868142</v>
       </c>
       <c r="H506" t="n">
-        <v>59.52693895672711</v>
+        <v>59.52598767269989</v>
       </c>
       <c r="I506" t="n">
-        <v>4.135543603063843</v>
+        <v>4.13477551685537</v>
       </c>
       <c r="J506" t="n">
-        <v>3.319075029790526</v>
+        <v>3.320874886541835</v>
       </c>
       <c r="K506" t="n">
-        <v>0.1407047130935142</v>
+        <v>0.140740873701981</v>
       </c>
       <c r="L506" t="n">
-        <v>0.04835763323451475</v>
+        <v>0.04836762327810713</v>
       </c>
     </row>
     <row r="507">
@@ -20702,7 +20702,7 @@
         <v>45625.25</v>
       </c>
       <c r="C507" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -20713,25 +20713,25 @@
         <v>240</v>
       </c>
       <c r="F507" s="2" t="n">
-        <v>45625.57245982957</v>
+        <v>45625.25723553456</v>
       </c>
       <c r="G507" t="n">
         <v>372850.9866868142</v>
       </c>
       <c r="H507" t="n">
-        <v>59.52862975083224</v>
+        <v>59.52672840743954</v>
       </c>
       <c r="I507" t="n">
-        <v>4.13575962913898</v>
+        <v>4.134224445538995</v>
       </c>
       <c r="J507" t="n">
-        <v>3.317868724153128</v>
+        <v>3.321466120560521</v>
       </c>
       <c r="K507" t="n">
-        <v>0.1406666622591352</v>
+        <v>0.1407389369237123</v>
       </c>
       <c r="L507" t="n">
-        <v>0.048343516088083</v>
+        <v>0.04836348331430963</v>
       </c>
     </row>
     <row r="508">
@@ -20742,7 +20742,7 @@
         <v>45625.25</v>
       </c>
       <c r="C508" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -20753,25 +20753,25 @@
         <v>240</v>
       </c>
       <c r="F508" s="2" t="n">
-        <v>45625.5768070518</v>
+        <v>45625.26212821133</v>
       </c>
       <c r="G508" t="n">
         <v>373090.9866868142</v>
       </c>
       <c r="H508" t="n">
-        <v>59.53031836964718</v>
+        <v>59.52746818918732</v>
       </c>
       <c r="I508" t="n">
-        <v>4.135975377285891</v>
+        <v>4.133674083203113</v>
       </c>
       <c r="J508" t="n">
-        <v>3.316663970487571</v>
+        <v>3.322056593927412</v>
       </c>
       <c r="K508" t="n">
-        <v>0.140628660379036</v>
+        <v>0.1407370026372046</v>
       </c>
       <c r="L508" t="n">
-        <v>0.04832941710405808</v>
+        <v>0.04835934867678023</v>
       </c>
     </row>
     <row r="509">
@@ -20782,7 +20782,7 @@
         <v>45625.25</v>
       </c>
       <c r="C509" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -20793,25 +20793,25 @@
         <v>240</v>
       </c>
       <c r="F509" s="2" t="n">
-        <v>45625.58115427402</v>
+        <v>45625.2670208881</v>
       </c>
       <c r="G509" t="n">
         <v>373330.9866868142</v>
       </c>
       <c r="H509" t="n">
-        <v>59.53200481736712</v>
+        <v>59.52820701978117</v>
       </c>
       <c r="I509" t="n">
-        <v>4.136190848040583</v>
+        <v>4.133124428480397</v>
       </c>
       <c r="J509" t="n">
-        <v>3.31546076580075</v>
+        <v>3.322646308109488</v>
       </c>
       <c r="K509" t="n">
-        <v>0.1405907073588039</v>
+        <v>0.1407350708376523</v>
       </c>
       <c r="L509" t="n">
-        <v>0.04831533624741228</v>
+        <v>0.04835521935524679</v>
       </c>
     </row>
     <row r="510">
@@ -20822,7 +20822,7 @@
         <v>45625.25</v>
       </c>
       <c r="C510" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -20833,25 +20833,25 @@
         <v>240</v>
       </c>
       <c r="F510" s="2" t="n">
-        <v>45625.58550149624</v>
+        <v>45625.27191356487</v>
       </c>
       <c r="G510" t="n">
         <v>373570.9866868142</v>
       </c>
       <c r="H510" t="n">
-        <v>59.53368909817654</v>
+        <v>59.52894490105428</v>
       </c>
       <c r="I510" t="n">
-        <v>4.136406041937686</v>
+        <v>4.132575480007032</v>
       </c>
       <c r="J510" t="n">
-        <v>3.314259107107248</v>
+        <v>3.323235264569959</v>
       </c>
       <c r="K510" t="n">
-        <v>0.1405528031042693</v>
+        <v>0.1407331415202623</v>
       </c>
       <c r="L510" t="n">
-        <v>0.04830127348320789</v>
+        <v>0.04835109533946354</v>
       </c>
     </row>
     <row r="511">
@@ -20862,7 +20862,7 @@
         <v>45625.25</v>
       </c>
       <c r="C511" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -20873,25 +20873,25 @@
         <v>240</v>
       </c>
       <c r="F511" s="2" t="n">
-        <v>45625.58984871846</v>
+        <v>45625.27680624164</v>
       </c>
       <c r="G511" t="n">
         <v>373810.9866868142</v>
       </c>
       <c r="H511" t="n">
-        <v>59.53537121624912</v>
+        <v>59.52968183483515</v>
       </c>
       <c r="I511" t="n">
-        <v>4.13662095951046</v>
+        <v>4.132027236422705</v>
       </c>
       <c r="J511" t="n">
-        <v>3.313058991429317</v>
+        <v>3.323823464768279</v>
       </c>
       <c r="K511" t="n">
-        <v>0.1405149475215042</v>
+        <v>0.1407312146802535</v>
       </c>
       <c r="L511" t="n">
-        <v>0.04828722877659693</v>
+        <v>0.04834697661921106</v>
       </c>
     </row>
     <row r="512">
@@ -20902,7 +20902,7 @@
         <v>45625.25</v>
       </c>
       <c r="C512" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -20913,25 +20913,25 @@
         <v>240</v>
       </c>
       <c r="F512" s="2" t="n">
-        <v>45625.59419594068</v>
+        <v>45625.28169891841</v>
       </c>
       <c r="G512" t="n">
         <v>374050.9866868142</v>
       </c>
       <c r="H512" t="n">
-        <v>59.53705117574787</v>
+        <v>59.53041782294756</v>
       </c>
       <c r="I512" t="n">
-        <v>4.136835601290792</v>
+        <v>4.131479696370597</v>
       </c>
       <c r="J512" t="n">
-        <v>3.31186041579685</v>
+        <v>3.324410910160155</v>
       </c>
       <c r="K512" t="n">
-        <v>0.1404771405168217</v>
+        <v>0.1407292903128574</v>
       </c>
       <c r="L512" t="n">
-        <v>0.04827320209282087</v>
+        <v>0.0483428631842961</v>
       </c>
     </row>
     <row r="513">
@@ -20942,7 +20942,7 @@
         <v>45625.25</v>
       </c>
       <c r="C513" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -20953,25 +20953,25 @@
         <v>240</v>
       </c>
       <c r="F513" s="2" t="n">
-        <v>45625.5985431629</v>
+        <v>45625.28659159518</v>
       </c>
       <c r="G513" t="n">
         <v>374290.9866868142</v>
       </c>
       <c r="H513" t="n">
-        <v>59.53872898082509</v>
+        <v>59.53115286721066</v>
       </c>
       <c r="I513" t="n">
-        <v>4.137049967809207</v>
+        <v>4.130932858497367</v>
       </c>
       <c r="J513" t="n">
-        <v>3.310663377247358</v>
+        <v>3.32499760219756</v>
       </c>
       <c r="K513" t="n">
-        <v>0.1404393819967752</v>
+        <v>0.1407273684133175</v>
       </c>
       <c r="L513" t="n">
-        <v>0.0482591933972103</v>
+        <v>0.04833875502455161</v>
       </c>
     </row>
     <row r="514">
@@ -20982,7 +20982,7 @@
         <v>45625.25</v>
       </c>
       <c r="C514" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -20993,25 +20993,25 @@
         <v>240</v>
       </c>
       <c r="F514" s="2" t="n">
-        <v>45625.60289038513</v>
+        <v>45625.29148427195</v>
       </c>
       <c r="G514" t="n">
         <v>374530.9866868142</v>
       </c>
       <c r="H514" t="n">
-        <v>59.54040463562245</v>
+        <v>59.53188696943889</v>
       </c>
       <c r="I514" t="n">
-        <v>4.13726405959487</v>
+        <v>4.130386721453143</v>
       </c>
       <c r="J514" t="n">
-        <v>3.309467872825948</v>
+        <v>3.325583542328746</v>
       </c>
       <c r="K514" t="n">
-        <v>0.1404016718681576</v>
+        <v>0.1407254489768897</v>
       </c>
       <c r="L514" t="n">
-        <v>0.0482452026551847</v>
+        <v>0.04833465212983658</v>
       </c>
     </row>
     <row r="515">
@@ -21022,7 +21022,7 @@
         <v>45625.25</v>
       </c>
       <c r="C515" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -21033,25 +21033,25 @@
         <v>240</v>
       </c>
       <c r="F515" s="2" t="n">
-        <v>45625.60723760735</v>
+        <v>45625.29637694873</v>
       </c>
       <c r="G515" t="n">
         <v>374770.9866868142</v>
       </c>
       <c r="H515" t="n">
-        <v>59.54207814427101</v>
+        <v>59.53262013144207</v>
       </c>
       <c r="I515" t="n">
-        <v>4.137477877175589</v>
+        <v>4.129841283891511</v>
       </c>
       <c r="J515" t="n">
-        <v>3.308273899585291</v>
+        <v>3.326168731998256</v>
       </c>
       <c r="K515" t="n">
-        <v>0.1403640100380007</v>
+        <v>0.1407235319988418</v>
       </c>
       <c r="L515" t="n">
-        <v>0.04823122983225212</v>
+        <v>0.04833055449003598</v>
       </c>
     </row>
     <row r="516">
@@ -21062,7 +21062,7 @@
         <v>45625.25</v>
       </c>
       <c r="C516" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -21073,25 +21073,25 @@
         <v>240</v>
       </c>
       <c r="F516" s="2" t="n">
-        <v>45625.61158482957</v>
+        <v>45625.3012696255</v>
       </c>
       <c r="G516" t="n">
         <v>375010.9866868142</v>
       </c>
       <c r="H516" t="n">
-        <v>59.54374951089126</v>
+        <v>59.53335235502539</v>
       </c>
       <c r="I516" t="n">
-        <v>4.137691421077823</v>
+        <v>4.129296544469504</v>
       </c>
       <c r="J516" t="n">
-        <v>3.307081454585609</v>
+        <v>3.326753172646934</v>
       </c>
       <c r="K516" t="n">
-        <v>0.140326396413574</v>
+        <v>0.1407216174744539</v>
       </c>
       <c r="L516" t="n">
-        <v>0.04821727489400891</v>
+        <v>0.04832646209506066</v>
       </c>
     </row>
     <row r="517">
@@ -21102,7 +21102,7 @@
         <v>45625.25</v>
       </c>
       <c r="C517" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -21110,28 +21110,28 @@
         </is>
       </c>
       <c r="E517" t="n">
-        <v>232.3566435834532</v>
+        <v>240</v>
       </c>
       <c r="F517" s="2" t="n">
-        <v>45625.61593205179</v>
+        <v>45625.30616230227</v>
       </c>
       <c r="G517" t="n">
-        <v>375243.3433303976</v>
+        <v>375250.9866868142</v>
       </c>
       <c r="H517" t="n">
-        <v>59.54536561205299</v>
+        <v>59.53408364198939</v>
       </c>
       <c r="I517" t="n">
-        <v>4.137897903931015</v>
+        <v>4.128752501847591</v>
       </c>
       <c r="J517" t="n">
-        <v>3.305928439007859</v>
+        <v>3.327336865711938</v>
       </c>
       <c r="K517" t="n">
-        <v>0.1402900265223746</v>
+        <v>0.1407197053990182</v>
       </c>
       <c r="L517" t="n">
-        <v>0.04820378139016995</v>
+        <v>0.04832237493484729</v>
       </c>
     </row>
     <row r="518">
@@ -21142,36 +21142,36 @@
         <v>45625.25</v>
       </c>
       <c r="C518" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E518" t="n">
         <v>240</v>
       </c>
       <c r="F518" s="2" t="n">
-        <v>45625.65760816168</v>
+        <v>45625.31105497904</v>
       </c>
       <c r="G518" t="n">
-        <v>445984.7353634185</v>
+        <v>375490.9866868142</v>
       </c>
       <c r="H518" t="n">
-        <v>60.88662387631096</v>
+        <v>59.53481399413004</v>
       </c>
       <c r="I518" t="n">
-        <v>3.876854982951027</v>
+        <v>4.128209154689664</v>
       </c>
       <c r="J518" t="n">
-        <v>2.51560395973375</v>
+        <v>3.327919812626751</v>
       </c>
       <c r="K518" t="n">
-        <v>0.1140098236714499</v>
+        <v>0.1407177957678388</v>
       </c>
       <c r="L518" t="n">
-        <v>0.04137643131977996</v>
+        <v>0.04831829299935827</v>
       </c>
     </row>
     <row r="519">
@@ -21182,36 +21182,36 @@
         <v>45625.25</v>
       </c>
       <c r="C519" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E519" t="n">
         <v>240</v>
       </c>
       <c r="F519" s="2" t="n">
-        <v>45625.6619553839</v>
+        <v>45625.31594765581</v>
       </c>
       <c r="G519" t="n">
-        <v>446224.7353634185</v>
+        <v>375730.9866868142</v>
       </c>
       <c r="H519" t="n">
-        <v>60.88776690794786</v>
+        <v>59.53554341323871</v>
       </c>
       <c r="I519" t="n">
-        <v>3.876948699862658</v>
+        <v>4.127666501663031</v>
       </c>
       <c r="J519" t="n">
-        <v>2.51484988573545</v>
+        <v>3.328502014821195</v>
       </c>
       <c r="K519" t="n">
-        <v>0.1139966562308858</v>
+        <v>0.1407158885762319</v>
       </c>
       <c r="L519" t="n">
-        <v>0.04137624391753594</v>
+        <v>0.04831421627858165</v>
       </c>
     </row>
     <row r="520">
@@ -21222,36 +21222,36 @@
         <v>45625.25</v>
       </c>
       <c r="C520" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E520" t="n">
         <v>240</v>
       </c>
       <c r="F520" s="2" t="n">
-        <v>45625.66630260612</v>
+        <v>45625.32084033258</v>
       </c>
       <c r="G520" t="n">
-        <v>446464.7353634185</v>
+        <v>375970.9866868142</v>
       </c>
       <c r="H520" t="n">
-        <v>60.8889087106967</v>
+        <v>59.53627190110219</v>
       </c>
       <c r="I520" t="n">
-        <v>3.877042316018028</v>
+        <v>4.127124541438401</v>
       </c>
       <c r="J520" t="n">
-        <v>2.514096622451838</v>
+        <v>3.32908347372144</v>
       </c>
       <c r="K520" t="n">
-        <v>0.113983502946807</v>
+        <v>0.1407139838195255</v>
       </c>
       <c r="L520" t="n">
-        <v>0.04137605671677049</v>
+        <v>0.04831014476253104</v>
       </c>
     </row>
     <row r="521">
@@ -21262,36 +21262,36 @@
         <v>45625.25</v>
       </c>
       <c r="C521" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E521" t="n">
         <v>240</v>
       </c>
       <c r="F521" s="2" t="n">
-        <v>45625.67064982835</v>
+        <v>45625.32573300935</v>
       </c>
       <c r="G521" t="n">
-        <v>446704.7353634185</v>
+        <v>376210.9866868142</v>
       </c>
       <c r="H521" t="n">
-        <v>60.89004928653818</v>
+        <v>59.53699945950272</v>
       </c>
       <c r="I521" t="n">
-        <v>3.877135831579535</v>
+        <v>4.126583272689877</v>
       </c>
       <c r="J521" t="n">
-        <v>2.513344168576204</v>
+        <v>3.329664190750017</v>
       </c>
       <c r="K521" t="n">
-        <v>0.113970363796396</v>
+        <v>0.1407120814930597</v>
       </c>
       <c r="L521" t="n">
-        <v>0.04137586971715887</v>
+        <v>0.04830607844124554</v>
       </c>
     </row>
     <row r="522">
@@ -21302,36 +21302,36 @@
         <v>45625.25</v>
       </c>
       <c r="C522" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E522" t="n">
         <v>240</v>
       </c>
       <c r="F522" s="2" t="n">
-        <v>45625.67499705057</v>
+        <v>45625.33062568613</v>
       </c>
       <c r="G522" t="n">
-        <v>446944.7353634185</v>
+        <v>376450.9866868142</v>
       </c>
       <c r="H522" t="n">
-        <v>60.8911886374488</v>
+        <v>59.53772609021799</v>
       </c>
       <c r="I522" t="n">
-        <v>3.877229246709231</v>
+        <v>4.126042694094941</v>
       </c>
       <c r="J522" t="n">
-        <v>2.512592522804642</v>
+        <v>3.330244167325831</v>
       </c>
       <c r="K522" t="n">
-        <v>0.1139572387568844</v>
+        <v>0.1407101815921865</v>
       </c>
       <c r="L522" t="n">
-        <v>0.04137568291837702</v>
+        <v>0.04830201730478962</v>
       </c>
     </row>
     <row r="523">
@@ -21342,36 +21342,36 @@
         <v>45625.25</v>
       </c>
       <c r="C523" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E523" t="n">
         <v>240</v>
       </c>
       <c r="F523" s="2" t="n">
-        <v>45625.67934427279</v>
+        <v>45625.3355183629</v>
       </c>
       <c r="G523" t="n">
-        <v>447184.7353634185</v>
+        <v>376690.9866868142</v>
       </c>
       <c r="H523" t="n">
-        <v>60.89232676540077</v>
+        <v>59.53845179502115</v>
       </c>
       <c r="I523" t="n">
-        <v>3.877322561568818</v>
+        <v>4.125502804334446</v>
       </c>
       <c r="J523" t="n">
-        <v>2.511841683836043</v>
+        <v>3.330823404864167</v>
       </c>
       <c r="K523" t="n">
-        <v>0.1139441278055527</v>
+        <v>0.1407082841122695</v>
       </c>
       <c r="L523" t="n">
-        <v>0.04137549632010162</v>
+        <v>0.04829796134325312</v>
       </c>
     </row>
     <row r="524">
@@ -21382,36 +21382,36 @@
         <v>45625.25</v>
       </c>
       <c r="C524" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E524" t="n">
         <v>240</v>
       </c>
       <c r="F524" s="2" t="n">
-        <v>45625.68369149501</v>
+        <v>45625.34041103967</v>
       </c>
       <c r="G524" t="n">
-        <v>447424.7353634185</v>
+        <v>376930.9866868142</v>
       </c>
       <c r="H524" t="n">
-        <v>60.8934636723621</v>
+        <v>59.53917657568086</v>
       </c>
       <c r="I524" t="n">
-        <v>3.877415776319651</v>
+        <v>4.124963602092607</v>
       </c>
       <c r="J524" t="n">
-        <v>2.511091650372096</v>
+        <v>3.331401904776709</v>
       </c>
       <c r="K524" t="n">
-        <v>0.1139310309197299</v>
+        <v>0.1407063890486845</v>
       </c>
       <c r="L524" t="n">
-        <v>0.04137530992200997</v>
+        <v>0.04829391054675108</v>
       </c>
     </row>
     <row r="525">
@@ -21422,36 +21422,36 @@
         <v>45625.25</v>
       </c>
       <c r="C525" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E525" t="n">
-        <v>240</v>
+        <v>166.2199859162001</v>
       </c>
       <c r="F525" s="2" t="n">
-        <v>45625.68803871724</v>
+        <v>45625.34530371644</v>
       </c>
       <c r="G525" t="n">
-        <v>447664.7353634185</v>
+        <v>377097.2066727304</v>
       </c>
       <c r="H525" t="n">
-        <v>60.89459936029656</v>
+        <v>59.53967800590596</v>
       </c>
       <c r="I525" t="n">
-        <v>3.87750889112274</v>
+        <v>4.124590561921236</v>
       </c>
       <c r="J525" t="n">
-        <v>2.510342421117267</v>
+        <v>3.331802132538701</v>
       </c>
       <c r="K525" t="n">
-        <v>0.1139179480767939</v>
+        <v>0.1407050779731925</v>
       </c>
       <c r="L525" t="n">
-        <v>0.04137512372378015</v>
+        <v>0.04829110805502524</v>
       </c>
     </row>
     <row r="526">
@@ -21462,36 +21462,36 @@
         <v>45625.25</v>
       </c>
       <c r="C526" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E526" t="n">
         <v>240</v>
       </c>
       <c r="F526" s="2" t="n">
-        <v>45625.69238593946</v>
+        <v>45625.42051092322</v>
       </c>
       <c r="G526" t="n">
-        <v>447904.7353634185</v>
+        <v>377337.2066727304</v>
       </c>
       <c r="H526" t="n">
-        <v>60.89573383116372</v>
+        <v>59.53922109426733</v>
       </c>
       <c r="I526" t="n">
-        <v>3.877601906138749</v>
+        <v>4.123987583018447</v>
       </c>
       <c r="J526" t="n">
-        <v>2.509593994778805</v>
+        <v>3.332695649006806</v>
       </c>
       <c r="K526" t="n">
-        <v>0.113904879254171</v>
+        <v>0.1407423890600333</v>
       </c>
       <c r="L526" t="n">
-        <v>0.04137493772509086</v>
+        <v>0.04829592595804314</v>
       </c>
     </row>
     <row r="527">
@@ -21502,36 +21502,36 @@
         <v>45625.25</v>
       </c>
       <c r="C527" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E527" t="n">
         <v>240</v>
       </c>
       <c r="F527" s="2" t="n">
-        <v>45625.69673316168</v>
+        <v>45625.42540359999</v>
       </c>
       <c r="G527" t="n">
-        <v>448144.7353634185</v>
+        <v>377577.2066727304</v>
       </c>
       <c r="H527" t="n">
-        <v>60.89686708691893</v>
+        <v>59.53876476348364</v>
       </c>
       <c r="I527" t="n">
-        <v>3.877694821527999</v>
+        <v>4.123385370660535</v>
       </c>
       <c r="J527" t="n">
-        <v>2.508846370066724</v>
+        <v>3.333588029580326</v>
       </c>
       <c r="K527" t="n">
-        <v>0.1138918244293358</v>
+        <v>0.1407796527146632</v>
       </c>
       <c r="L527" t="n">
-        <v>0.04137475192562151</v>
+        <v>0.04830073773623833</v>
       </c>
     </row>
     <row r="528">
@@ -21542,36 +21542,36 @@
         <v>45625.25</v>
       </c>
       <c r="C528" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E528" t="n">
         <v>240</v>
       </c>
       <c r="F528" s="2" t="n">
-        <v>45625.7010803839</v>
+        <v>45625.43029627676</v>
       </c>
       <c r="G528" t="n">
-        <v>448384.7353634185</v>
+        <v>377817.2066727304</v>
       </c>
       <c r="H528" t="n">
-        <v>60.8979991295134</v>
+        <v>59.53830901244797</v>
       </c>
       <c r="I528" t="n">
-        <v>3.877787637450467</v>
+        <v>4.122783923386707</v>
       </c>
       <c r="J528" t="n">
-        <v>2.5080995456938</v>
+        <v>3.334479276423915</v>
       </c>
       <c r="K528" t="n">
-        <v>0.1138787835798111</v>
+        <v>0.1408168690274731</v>
       </c>
       <c r="L528" t="n">
-        <v>0.04137456632505222</v>
+        <v>0.04830554340128279</v>
       </c>
     </row>
     <row r="529">
@@ -21582,36 +21582,36 @@
         <v>45625.25</v>
       </c>
       <c r="C529" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E529" t="n">
         <v>240</v>
       </c>
       <c r="F529" s="2" t="n">
-        <v>45625.70542760612</v>
+        <v>45625.43518895353</v>
       </c>
       <c r="G529" t="n">
-        <v>448624.7353634185</v>
+        <v>378057.2066727304</v>
       </c>
       <c r="H529" t="n">
-        <v>60.89912996089413</v>
+        <v>59.53785384005619</v>
       </c>
       <c r="I529" t="n">
-        <v>3.877880354065788</v>
+        <v>4.122183239739881</v>
       </c>
       <c r="J529" t="n">
-        <v>2.507353520375568</v>
+        <v>3.335369391696733</v>
       </c>
       <c r="K529" t="n">
-        <v>0.1138657566831679</v>
+        <v>0.1408540380886241</v>
       </c>
       <c r="L529" t="n">
-        <v>0.04137438092306375</v>
+        <v>0.04831034296481886</v>
       </c>
     </row>
     <row r="530">
@@ -21622,36 +21622,36 @@
         <v>45625.25</v>
       </c>
       <c r="C530" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E530" t="n">
-        <v>233.6583004429849</v>
+        <v>240</v>
       </c>
       <c r="F530" s="2" t="n">
-        <v>45625.70977482834</v>
+        <v>45625.4400816303</v>
       </c>
       <c r="G530" t="n">
-        <v>448858.3936638614</v>
+        <v>378297.2066727304</v>
       </c>
       <c r="H530" t="n">
-        <v>60.90022974969197</v>
+        <v>59.53739924520701</v>
       </c>
       <c r="I530" t="n">
-        <v>3.877970525506589</v>
+        <v>4.121583318266673</v>
       </c>
       <c r="J530" t="n">
-        <v>2.50662797428454</v>
+        <v>3.336258377552459</v>
       </c>
       <c r="K530" t="n">
-        <v>0.1138530873893696</v>
+        <v>0.1408911599880488</v>
       </c>
       <c r="L530" t="n">
-        <v>0.04137420061056669</v>
+        <v>0.04831513643845931</v>
       </c>
     </row>
     <row r="531">
@@ -21662,7 +21662,7 @@
         <v>45625.25</v>
       </c>
       <c r="C531" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -21673,25 +21673,25 @@
         <v>240</v>
       </c>
       <c r="F531" s="2" t="n">
-        <v>45625.70924535386</v>
+        <v>45625.44497430707</v>
       </c>
       <c r="G531" t="n">
-        <v>375483.3433303976</v>
+        <v>378537.2066727304</v>
       </c>
       <c r="H531" t="n">
-        <v>59.54461072544636</v>
+        <v>59.5369452268019</v>
       </c>
       <c r="I531" t="n">
-        <v>4.139875648606637</v>
+        <v>4.120984157517383</v>
       </c>
       <c r="J531" t="n">
-        <v>3.305181399677501</v>
+        <v>3.337146236139312</v>
       </c>
       <c r="K531" t="n">
-        <v>0.1402549938994926</v>
+        <v>0.1409282348154514</v>
       </c>
       <c r="L531" t="n">
-        <v>0.04820258051790317</v>
+        <v>0.0483199238337875</v>
       </c>
     </row>
     <row r="532">
@@ -21702,7 +21702,7 @@
         <v>45625.25</v>
       </c>
       <c r="C532" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -21713,25 +21713,25 @@
         <v>240</v>
       </c>
       <c r="F532" s="2" t="n">
-        <v>45625.71359257609</v>
+        <v>45625.44986698384</v>
       </c>
       <c r="G532" t="n">
-        <v>375723.3433303976</v>
+        <v>378777.2066727304</v>
       </c>
       <c r="H532" t="n">
-        <v>59.54385680323436</v>
+        <v>59.53649178374511</v>
       </c>
       <c r="I532" t="n">
-        <v>4.141850866642748</v>
+        <v>4.120385756045987</v>
       </c>
       <c r="J532" t="n">
-        <v>3.304435314716589</v>
+        <v>3.338032969600063</v>
       </c>
       <c r="K532" t="n">
-        <v>0.1402200060320385</v>
+        <v>0.1409652626603091</v>
       </c>
       <c r="L532" t="n">
-        <v>0.04820138117979363</v>
+        <v>0.04832470516235739</v>
       </c>
     </row>
     <row r="533">
@@ -21742,7 +21742,7 @@
         <v>45625.25</v>
       </c>
       <c r="C533" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -21753,25 +21753,25 @@
         <v>240</v>
       </c>
       <c r="F533" s="2" t="n">
-        <v>45625.71793979831</v>
+        <v>45625.45475966061</v>
       </c>
       <c r="G533" t="n">
-        <v>375963.3433303976</v>
+        <v>379017.2066727304</v>
       </c>
       <c r="H533" t="n">
-        <v>59.54310384357007</v>
+        <v>59.53603891494371</v>
       </c>
       <c r="I533" t="n">
-        <v>4.143823562878067</v>
+        <v>4.119788112410123</v>
       </c>
       <c r="J533" t="n">
-        <v>3.303690182297427</v>
+        <v>3.33891858007206</v>
       </c>
       <c r="K533" t="n">
-        <v>0.140185062834302</v>
+        <v>0.1410022436118721</v>
       </c>
       <c r="L533" t="n">
-        <v>0.04820018337290331</v>
+        <v>0.04832948043569373</v>
       </c>
     </row>
     <row r="534">
@@ -21782,7 +21782,7 @@
         <v>45625.25</v>
       </c>
       <c r="C534" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -21793,25 +21793,25 @@
         <v>240</v>
       </c>
       <c r="F534" s="2" t="n">
-        <v>45625.72228702053</v>
+        <v>45625.45965233738</v>
       </c>
       <c r="G534" t="n">
-        <v>376203.3433303976</v>
+        <v>379257.2066727304</v>
       </c>
       <c r="H534" t="n">
-        <v>59.54235184461134</v>
+        <v>59.53558661930748</v>
       </c>
       <c r="I534" t="n">
-        <v>4.145793742138962</v>
+        <v>4.119191225171078</v>
       </c>
       <c r="J534" t="n">
-        <v>3.302946000596986</v>
+        <v>3.339803069687236</v>
       </c>
       <c r="K534" t="n">
-        <v>0.1401501642207915</v>
+        <v>0.1410391777591651</v>
       </c>
       <c r="L534" t="n">
-        <v>0.04819898709430165</v>
+        <v>0.04833424966529203</v>
       </c>
     </row>
     <row r="535">
@@ -21822,7 +21822,7 @@
         <v>45625.25</v>
       </c>
       <c r="C535" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -21833,25 +21833,25 @@
         <v>240</v>
       </c>
       <c r="F535" s="2" t="n">
-        <v>45625.72663424275</v>
+        <v>45625.46454501415</v>
       </c>
       <c r="G535" t="n">
-        <v>376443.3433303976</v>
+        <v>379497.2066727304</v>
       </c>
       <c r="H535" t="n">
-        <v>59.54160080452068</v>
+        <v>59.53513489574899</v>
       </c>
       <c r="I535" t="n">
-        <v>4.147761409239497</v>
+        <v>4.118595092893782</v>
       </c>
       <c r="J535" t="n">
-        <v>3.302202767796883</v>
+        <v>3.340686440572135</v>
       </c>
       <c r="K535" t="n">
-        <v>0.1401153101062336</v>
+        <v>0.1410760651909871</v>
       </c>
       <c r="L535" t="n">
-        <v>0.0481977923410656</v>
+        <v>0.04833901286261877</v>
       </c>
     </row>
     <row r="536">
@@ -21862,7 +21862,7 @@
         <v>45625.25</v>
       </c>
       <c r="C536" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -21873,25 +21873,25 @@
         <v>240</v>
       </c>
       <c r="F536" s="2" t="n">
-        <v>45625.73098146498</v>
+        <v>45625.46943769092</v>
       </c>
       <c r="G536" t="n">
-        <v>376683.3433303976</v>
+        <v>379737.2066727304</v>
       </c>
       <c r="H536" t="n">
-        <v>59.54085072146527</v>
+        <v>59.53468374318356</v>
       </c>
       <c r="I536" t="n">
-        <v>4.149726568981464</v>
+        <v>4.117999714146792</v>
       </c>
       <c r="J536" t="n">
-        <v>3.301460482083374</v>
+        <v>3.341568694847923</v>
       </c>
       <c r="K536" t="n">
-        <v>0.1400805004055722</v>
+        <v>0.1411129059959131</v>
       </c>
       <c r="L536" t="n">
-        <v>0.04819659911027954</v>
+        <v>0.04834377003911143</v>
       </c>
     </row>
     <row r="537">
@@ -21902,7 +21902,7 @@
         <v>45625.25</v>
       </c>
       <c r="C537" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -21913,25 +21913,25 @@
         <v>240</v>
       </c>
       <c r="F537" s="2" t="n">
-        <v>45625.7353286872</v>
+        <v>45625.4743303677</v>
       </c>
       <c r="G537" t="n">
-        <v>376923.3433303976</v>
+        <v>379977.2066727304</v>
       </c>
       <c r="H537" t="n">
-        <v>59.540101593617</v>
+        <v>59.53423316052923</v>
       </c>
       <c r="I537" t="n">
-        <v>4.151689226154426</v>
+        <v>4.117405087502278</v>
       </c>
       <c r="J537" t="n">
-        <v>3.300719141647329</v>
+        <v>3.342449834630407</v>
       </c>
       <c r="K537" t="n">
-        <v>0.1400457350339675</v>
+        <v>0.141149700262294</v>
       </c>
       <c r="L537" t="n">
-        <v>0.04819540739903529</v>
+        <v>0.04834852120617859</v>
       </c>
     </row>
     <row r="538">
@@ -21942,7 +21942,7 @@
         <v>45625.25</v>
       </c>
       <c r="C538" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -21953,25 +21953,25 @@
         <v>240</v>
       </c>
       <c r="F538" s="2" t="n">
-        <v>45625.73967590942</v>
+        <v>45625.47922304447</v>
       </c>
       <c r="G538" t="n">
-        <v>377163.3433303976</v>
+        <v>380217.2066727304</v>
       </c>
       <c r="H538" t="n">
-        <v>59.53935341915239</v>
+        <v>59.53378314670681</v>
       </c>
       <c r="I538" t="n">
-        <v>4.153649385535756</v>
+        <v>4.116811211536021</v>
       </c>
       <c r="J538" t="n">
-        <v>3.299978744684227</v>
+        <v>3.343329862030053</v>
       </c>
       <c r="K538" t="n">
-        <v>0.1400110139067962</v>
+        <v>0.1411864480782577</v>
       </c>
       <c r="L538" t="n">
-        <v>0.04819421720443205</v>
+        <v>0.04835326637520001</v>
       </c>
     </row>
     <row r="539">
@@ -21982,7 +21982,7 @@
         <v>45625.25</v>
       </c>
       <c r="C539" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -21993,25 +21993,25 @@
         <v>240</v>
       </c>
       <c r="F539" s="2" t="n">
-        <v>45625.74402313164</v>
+        <v>45625.48411572124</v>
       </c>
       <c r="G539" t="n">
-        <v>377403.3433303976</v>
+        <v>380457.2066727304</v>
       </c>
       <c r="H539" t="n">
-        <v>59.53860619625259</v>
+        <v>59.53333370063979</v>
       </c>
       <c r="I539" t="n">
-        <v>4.155607051890674</v>
+        <v>4.11621808482739</v>
       </c>
       <c r="J539" t="n">
-        <v>3.299239289394134</v>
+        <v>3.344208779152</v>
       </c>
       <c r="K539" t="n">
-        <v>0.1399763369396497</v>
+        <v>0.1412231495317098</v>
       </c>
       <c r="L539" t="n">
-        <v>0.04819302852357642</v>
+        <v>0.04835800555752677</v>
       </c>
     </row>
     <row r="540">
@@ -22022,7 +22022,7 @@
         <v>45625.25</v>
       </c>
       <c r="C540" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -22033,25 +22033,25 @@
         <v>240</v>
       </c>
       <c r="F540" s="2" t="n">
-        <v>45625.74837035387</v>
+        <v>45625.48900839801</v>
       </c>
       <c r="G540" t="n">
-        <v>377643.3433303976</v>
+        <v>380697.2066727304</v>
       </c>
       <c r="H540" t="n">
-        <v>59.5378599231034</v>
+        <v>59.53288482125438</v>
       </c>
       <c r="I540" t="n">
-        <v>4.157562229972286</v>
+        <v>4.11562570595934</v>
       </c>
       <c r="J540" t="n">
-        <v>3.298500773981695</v>
+        <v>3.345086588096081</v>
       </c>
       <c r="K540" t="n">
-        <v>0.1399417040483344</v>
+        <v>0.1412598047103342</v>
       </c>
       <c r="L540" t="n">
-        <v>0.04819184135358236</v>
+        <v>0.0483627387644813</v>
       </c>
     </row>
     <row r="541">
@@ -22062,7 +22062,7 @@
         <v>45625.25</v>
       </c>
       <c r="C541" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -22073,25 +22073,25 @@
         <v>240</v>
       </c>
       <c r="F541" s="2" t="n">
-        <v>45625.25234285779</v>
+        <v>45625.49390107478</v>
       </c>
       <c r="G541" t="n">
-        <v>377883.3433303976</v>
+        <v>380937.2066727304</v>
       </c>
       <c r="H541" t="n">
-        <v>59.53858325304974</v>
+        <v>59.53243650747955</v>
       </c>
       <c r="I541" t="n">
-        <v>4.157004025174651</v>
+        <v>4.115034073518395</v>
       </c>
       <c r="J541" t="n">
-        <v>3.29909834457651</v>
+        <v>3.345963290956833</v>
       </c>
       <c r="K541" t="n">
-        <v>0.1399403006285199</v>
+        <v>0.1412964137015938</v>
       </c>
       <c r="L541" t="n">
-        <v>0.04818786816463038</v>
+        <v>0.0483674660073575</v>
       </c>
     </row>
     <row r="542">
@@ -22102,7 +22102,7 @@
         <v>45625.25</v>
       </c>
       <c r="C542" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -22113,25 +22113,25 @@
         <v>240</v>
       </c>
       <c r="F542" s="2" t="n">
-        <v>45625.25723553456</v>
+        <v>45625.49879375155</v>
       </c>
       <c r="G542" t="n">
-        <v>378123.3433303976</v>
+        <v>381177.2066727304</v>
       </c>
       <c r="H542" t="n">
-        <v>59.53930566478149</v>
+        <v>59.53198875824688</v>
       </c>
       <c r="I542" t="n">
-        <v>4.156446528977286</v>
+        <v>4.114443186094642</v>
       </c>
       <c r="J542" t="n">
-        <v>3.299695156599047</v>
+        <v>3.346838889823522</v>
       </c>
       <c r="K542" t="n">
-        <v>0.1399388989902444</v>
+        <v>0.1413329765927312</v>
       </c>
       <c r="L542" t="n">
-        <v>0.04818390001935192</v>
+        <v>0.04837218729742084</v>
       </c>
     </row>
     <row r="543">
@@ -22142,7 +22142,7 @@
         <v>45625.25</v>
       </c>
       <c r="C543" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -22153,25 +22153,25 @@
         <v>240</v>
       </c>
       <c r="F543" s="2" t="n">
-        <v>45625.26212821133</v>
+        <v>45625.50368642832</v>
       </c>
       <c r="G543" t="n">
-        <v>378363.3433303976</v>
+        <v>381417.2066727304</v>
       </c>
       <c r="H543" t="n">
-        <v>59.54002716004593</v>
+        <v>59.53155070319304</v>
       </c>
       <c r="I543" t="n">
-        <v>4.15588974003177</v>
+        <v>4.113848104177349</v>
       </c>
       <c r="J543" t="n">
-        <v>3.30029121149282</v>
+        <v>3.347710282186754</v>
       </c>
       <c r="K543" t="n">
-        <v>0.1399374991301179</v>
+        <v>0.1413695023654911</v>
       </c>
       <c r="L543" t="n">
-        <v>0.04817993690814922</v>
+        <v>0.04837677457971879</v>
       </c>
     </row>
     <row r="544">
@@ -22182,7 +22182,7 @@
         <v>45625.25</v>
       </c>
       <c r="C544" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -22193,25 +22193,25 @@
         <v>240</v>
       </c>
       <c r="F544" s="2" t="n">
-        <v>45625.2670208881</v>
+        <v>45625.51530954447</v>
       </c>
       <c r="G544" t="n">
-        <v>378603.3433303976</v>
+        <v>381657.2066727304</v>
       </c>
       <c r="H544" t="n">
-        <v>59.54074774058595</v>
+        <v>59.53194260437719</v>
       </c>
       <c r="I544" t="n">
-        <v>4.155333656993106</v>
+        <v>4.112805208253878</v>
       </c>
       <c r="J544" t="n">
-        <v>3.30088651069768</v>
+        <v>3.348298566773943</v>
       </c>
       <c r="K544" t="n">
-        <v>0.1399361010447588</v>
+        <v>0.1414067901703156</v>
       </c>
       <c r="L544" t="n">
-        <v>0.04817597882144884</v>
+        <v>0.0483697229484327</v>
       </c>
     </row>
     <row r="545">
@@ -22222,7 +22222,7 @@
         <v>45625.25</v>
       </c>
       <c r="C545" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -22233,25 +22233,25 @@
         <v>240</v>
       </c>
       <c r="F545" s="2" t="n">
-        <v>45625.27191356487</v>
+        <v>45625.52020222124</v>
       </c>
       <c r="G545" t="n">
-        <v>378843.3433303976</v>
+        <v>381897.2066727304</v>
       </c>
       <c r="H545" t="n">
-        <v>59.54146740813999</v>
+        <v>59.53233401298752</v>
       </c>
       <c r="I545" t="n">
-        <v>4.154778278519701</v>
+        <v>4.111763623128272</v>
       </c>
       <c r="J545" t="n">
-        <v>3.30148105564983</v>
+        <v>3.3488861119564</v>
       </c>
       <c r="K545" t="n">
-        <v>0.1399347047307941</v>
+        <v>0.1414440311087425</v>
       </c>
       <c r="L545" t="n">
-        <v>0.04817202574970161</v>
+        <v>0.04836268018022013</v>
       </c>
     </row>
     <row r="546">
@@ -22262,7 +22262,7 @@
         <v>45625.25</v>
       </c>
       <c r="C546" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -22273,25 +22273,25 @@
         <v>240</v>
       </c>
       <c r="F546" s="2" t="n">
-        <v>45625.27680624164</v>
+        <v>45625.52509489801</v>
       </c>
       <c r="G546" t="n">
-        <v>379083.3433303976</v>
+        <v>382137.2066727304</v>
       </c>
       <c r="H546" t="n">
-        <v>59.54218616444211</v>
+        <v>59.5327249299521</v>
       </c>
       <c r="I546" t="n">
-        <v>4.154223603273362</v>
+        <v>4.110723346330805</v>
       </c>
       <c r="J546" t="n">
-        <v>3.302074847781836</v>
+        <v>3.349472919127266</v>
       </c>
       <c r="K546" t="n">
-        <v>0.1399333101848592</v>
+        <v>0.1414812252690748</v>
       </c>
       <c r="L546" t="n">
-        <v>0.04816807768338253</v>
+        <v>0.0483556462583818</v>
       </c>
     </row>
     <row r="547">
@@ -22302,7 +22302,7 @@
         <v>45625.25</v>
       </c>
       <c r="C547" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -22313,25 +22313,25 @@
         <v>240</v>
       </c>
       <c r="F547" s="2" t="n">
-        <v>45625.28169891841</v>
+        <v>45625.52998757478</v>
       </c>
       <c r="G547" t="n">
-        <v>379323.3433303976</v>
+        <v>382377.2066727304</v>
       </c>
       <c r="H547" t="n">
-        <v>59.54290401122196</v>
+        <v>59.53311535619667</v>
       </c>
       <c r="I547" t="n">
-        <v>4.153669629919282</v>
+        <v>4.10968437539795</v>
       </c>
       <c r="J547" t="n">
-        <v>3.302667888522639</v>
+        <v>3.350058989676187</v>
       </c>
       <c r="K547" t="n">
-        <v>0.1399319174035985</v>
+        <v>0.1415183727393935</v>
       </c>
       <c r="L547" t="n">
-        <v>0.04816413461299071</v>
+        <v>0.04834862116626037</v>
       </c>
     </row>
     <row r="548">
@@ -22342,7 +22342,7 @@
         <v>45625.25</v>
       </c>
       <c r="C548" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -22353,25 +22353,25 @@
         <v>240</v>
       </c>
       <c r="F548" s="2" t="n">
-        <v>45625.28659159518</v>
+        <v>45625.53488025155</v>
       </c>
       <c r="G548" t="n">
-        <v>379563.3433303976</v>
+        <v>382617.2066727304</v>
       </c>
       <c r="H548" t="n">
-        <v>59.54362095020484</v>
+        <v>59.53350529264468</v>
       </c>
       <c r="I548" t="n">
-        <v>4.153116357126029</v>
+        <v>4.108646707872362</v>
       </c>
       <c r="J548" t="n">
-        <v>3.303260179297565</v>
+        <v>3.350644324989319</v>
       </c>
       <c r="K548" t="n">
-        <v>0.1399305263836643</v>
+        <v>0.1415554736075588</v>
       </c>
       <c r="L548" t="n">
-        <v>0.0481601965290493</v>
+        <v>0.04834160488724027</v>
       </c>
     </row>
     <row r="549">
@@ -22382,7 +22382,7 @@
         <v>45625.25</v>
       </c>
       <c r="C549" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -22393,25 +22393,25 @@
         <v>240</v>
       </c>
       <c r="F549" s="2" t="n">
-        <v>45625.29148427195</v>
+        <v>45625.53977292832</v>
       </c>
       <c r="G549" t="n">
-        <v>379803.3433303976</v>
+        <v>382857.2066727304</v>
       </c>
       <c r="H549" t="n">
-        <v>59.54433698311168</v>
+        <v>59.53389474021721</v>
       </c>
       <c r="I549" t="n">
-        <v>4.152563783565538</v>
+        <v>4.107610341302857</v>
       </c>
       <c r="J549" t="n">
-        <v>3.303851721528338</v>
+        <v>3.351228926449346</v>
       </c>
       <c r="K549" t="n">
-        <v>0.1399291371217177</v>
+        <v>0.1415925279612106</v>
       </c>
       <c r="L549" t="n">
-        <v>0.04815626342210539</v>
+        <v>0.04833459740474764</v>
       </c>
     </row>
     <row r="550">
@@ -22422,7 +22422,7 @@
         <v>45625.25</v>
       </c>
       <c r="C550" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -22433,25 +22433,25 @@
         <v>240</v>
       </c>
       <c r="F550" s="2" t="n">
-        <v>45625.29637694873</v>
+        <v>45625.54466560509</v>
       </c>
       <c r="G550" t="n">
-        <v>380043.3433303976</v>
+        <v>383097.2066727304</v>
       </c>
       <c r="H550" t="n">
-        <v>59.54505211165905</v>
+        <v>59.53428369983309</v>
       </c>
       <c r="I550" t="n">
-        <v>4.152011907913098</v>
+        <v>4.106575273244396</v>
       </c>
       <c r="J550" t="n">
-        <v>3.30444251663309</v>
+        <v>3.351812795435483</v>
       </c>
       <c r="K550" t="n">
-        <v>0.1399277496144281</v>
+        <v>0.1416295358877691</v>
       </c>
       <c r="L550" t="n">
-        <v>0.04815233528272997</v>
+        <v>0.0483275987022501</v>
       </c>
     </row>
     <row r="551">
@@ -22462,7 +22462,7 @@
         <v>45625.25</v>
       </c>
       <c r="C551" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -22473,25 +22473,25 @@
         <v>240</v>
       </c>
       <c r="F551" s="2" t="n">
-        <v>45625.3012696255</v>
+        <v>45625.54955828186</v>
       </c>
       <c r="G551" t="n">
-        <v>380283.3433303976</v>
+        <v>383337.2066727304</v>
       </c>
       <c r="H551" t="n">
-        <v>59.54576633755919</v>
+        <v>59.5346721724088</v>
       </c>
       <c r="I551" t="n">
-        <v>4.151460728847343</v>
+        <v>4.10554150125806</v>
       </c>
       <c r="J551" t="n">
-        <v>3.305032566026374</v>
+        <v>3.352395933323495</v>
       </c>
       <c r="K551" t="n">
-        <v>0.1399263638584735</v>
+        <v>0.1416664974744356</v>
       </c>
       <c r="L551" t="n">
-        <v>0.0481484121015178</v>
+        <v>0.0483206087632567</v>
       </c>
     </row>
     <row r="552">
@@ -22502,7 +22502,7 @@
         <v>45625.25</v>
       </c>
       <c r="C552" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -22513,25 +22513,25 @@
         <v>240</v>
       </c>
       <c r="F552" s="2" t="n">
-        <v>45625.30616230227</v>
+        <v>45625.55445095863</v>
       </c>
       <c r="G552" t="n">
-        <v>380523.3433303976</v>
+        <v>383577.2066727304</v>
       </c>
       <c r="H552" t="n">
-        <v>59.54647966252005</v>
+        <v>59.53506015885856</v>
       </c>
       <c r="I552" t="n">
-        <v>4.150910245050238</v>
+        <v>4.104509022911035</v>
       </c>
       <c r="J552" t="n">
-        <v>3.305621871119174</v>
+        <v>3.352978341485701</v>
       </c>
       <c r="K552" t="n">
-        <v>0.1399249798505401</v>
+        <v>0.1417034128081932</v>
       </c>
       <c r="L552" t="n">
-        <v>0.04814449386908739</v>
+        <v>0.04831362757131777</v>
       </c>
     </row>
     <row r="553">
@@ -22542,7 +22542,7 @@
         <v>45625.25</v>
       </c>
       <c r="C553" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -22553,25 +22553,25 @@
         <v>240</v>
       </c>
       <c r="F553" s="2" t="n">
-        <v>45625.31105497904</v>
+        <v>45625.5593436354</v>
       </c>
       <c r="G553" t="n">
-        <v>380763.3433303976</v>
+        <v>383817.2066727304</v>
       </c>
       <c r="H553" t="n">
-        <v>59.54719208824523</v>
+        <v>59.53544766009427</v>
       </c>
       <c r="I553" t="n">
-        <v>4.150360455207075</v>
+        <v>4.103477835776593</v>
       </c>
       <c r="J553" t="n">
-        <v>3.306210433318916</v>
+        <v>3.353560021290989</v>
       </c>
       <c r="K553" t="n">
-        <v>0.1399235975873224</v>
+        <v>0.1417402819758075</v>
       </c>
       <c r="L553" t="n">
-        <v>0.04814058057608091</v>
+        <v>0.04830665511002476</v>
       </c>
     </row>
     <row r="554">
@@ -22582,7 +22582,7 @@
         <v>45625.25</v>
       </c>
       <c r="C554" s="2" t="n">
-        <v>45625.75</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -22593,73 +22593,73 @@
         <v>240</v>
       </c>
       <c r="F554" s="2" t="n">
-        <v>45625.31594765581</v>
+        <v>45625.56423631217</v>
       </c>
       <c r="G554" t="n">
-        <v>381003.3433303976</v>
+        <v>384057.2066727304</v>
       </c>
       <c r="H554" t="n">
-        <v>59.54790361643407</v>
+        <v>59.5358346770256</v>
       </c>
       <c r="I554" t="n">
-        <v>4.149811358006454</v>
+        <v>4.10244793743407</v>
       </c>
       <c r="J554" t="n">
-        <v>3.306798254029479</v>
+        <v>3.354140974104824</v>
       </c>
       <c r="K554" t="n">
-        <v>0.1399222170655234</v>
+        <v>0.1417771050638269</v>
       </c>
       <c r="L554" t="n">
-        <v>0.04813667221316408</v>
+        <v>0.04829969136301014</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B555" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C555" s="2" t="n">
         <v>45625.75</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0107</t>
+          <t>CEN01_RP01_0106</t>
         </is>
       </c>
       <c r="E555" t="n">
-        <v>240</v>
+        <v>171.5431458111511</v>
       </c>
       <c r="F555" s="2" t="n">
-        <v>45625.32084033258</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="G555" t="n">
-        <v>381243.3433303976</v>
+        <v>441458.7632783963</v>
       </c>
       <c r="H555" t="n">
-        <v>59.54861424878161</v>
+        <v>60.88663521942041</v>
       </c>
       <c r="I555" t="n">
-        <v>4.149262952140282</v>
+        <v>3.876534699569179</v>
       </c>
       <c r="J555" t="n">
-        <v>3.307385334651209</v>
+        <v>2.515791112031039</v>
       </c>
       <c r="K555" t="n">
-        <v>0.1399208382818543</v>
+        <v>0.1140123324826181</v>
       </c>
       <c r="L555" t="n">
-        <v>0.04813276877102616</v>
+        <v>0.04137485918180678</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B556" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C556" s="2" t="n">
         <v>45625.75</v>
@@ -22673,33 +22673,33 @@
         <v>240</v>
       </c>
       <c r="F556" s="2" t="n">
-        <v>45625.32573300935</v>
+        <v>45625.56811260735</v>
       </c>
       <c r="G556" t="n">
-        <v>381483.3433303976</v>
+        <v>384297.2066727304</v>
       </c>
       <c r="H556" t="n">
-        <v>59.54932398697864</v>
+        <v>59.53746955562113</v>
       </c>
       <c r="I556" t="n">
-        <v>4.148715236303754</v>
+        <v>4.102678198007082</v>
       </c>
       <c r="J556" t="n">
-        <v>3.307971676580928</v>
+        <v>3.352948698788143</v>
       </c>
       <c r="K556" t="n">
-        <v>0.1399194612330347</v>
+        <v>0.1417395178397604</v>
       </c>
       <c r="L556" t="n">
-        <v>0.04812887024037981</v>
+        <v>0.04828603087879124</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B557" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C557" s="2" t="n">
         <v>45625.75</v>
@@ -22713,33 +22713,33 @@
         <v>240</v>
       </c>
       <c r="F557" s="2" t="n">
-        <v>45625.33062568613</v>
+        <v>45625.57245982957</v>
       </c>
       <c r="G557" t="n">
-        <v>381723.3433303976</v>
+        <v>384537.2066727304</v>
       </c>
       <c r="H557" t="n">
-        <v>59.55003283271169</v>
+        <v>59.53910239347337</v>
       </c>
       <c r="I557" t="n">
-        <v>4.148168209195348</v>
+        <v>4.102908171156477</v>
       </c>
       <c r="J557" t="n">
-        <v>3.308557281211943</v>
+        <v>3.351757911733566</v>
       </c>
       <c r="K557" t="n">
-        <v>0.1399180859157922</v>
+        <v>0.1417019775340864</v>
       </c>
       <c r="L557" t="n">
-        <v>0.04812497661196106</v>
+        <v>0.04827238744632263</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B558" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C558" s="2" t="n">
         <v>45625.75</v>
@@ -22753,33 +22753,33 @@
         <v>240</v>
       </c>
       <c r="F558" s="2" t="n">
-        <v>45625.3355183629</v>
+        <v>45625.5768070518</v>
       </c>
       <c r="G558" t="n">
-        <v>381963.3433303976</v>
+        <v>384777.2066727304</v>
       </c>
       <c r="H558" t="n">
-        <v>59.55074078766305</v>
+        <v>59.54073319440099</v>
       </c>
       <c r="I558" t="n">
-        <v>4.147621869516815</v>
+        <v>4.103137857420085</v>
       </c>
       <c r="J558" t="n">
-        <v>3.30914214993406</v>
+        <v>3.350568610156237</v>
       </c>
       <c r="K558" t="n">
-        <v>0.1399167123268629</v>
+        <v>0.1416644840590104</v>
       </c>
       <c r="L558" t="n">
-        <v>0.04812108787652922</v>
+        <v>0.04825876103369686</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B559" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C559" s="2" t="n">
         <v>45625.75</v>
@@ -22793,33 +22793,33 @@
         <v>240</v>
       </c>
       <c r="F559" s="2" t="n">
-        <v>45625.34041103967</v>
+        <v>45625.58115427402</v>
       </c>
       <c r="G559" t="n">
-        <v>382203.3433303976</v>
+        <v>385017.2066727304</v>
       </c>
       <c r="H559" t="n">
-        <v>59.55144785351079</v>
+        <v>59.54236196221311</v>
       </c>
       <c r="I559" t="n">
-        <v>4.147076215973163</v>
+        <v>4.103367257334397</v>
       </c>
       <c r="J559" t="n">
-        <v>3.309726284133595</v>
+        <v>3.349380791278245</v>
       </c>
       <c r="K559" t="n">
-        <v>0.139915340462991</v>
+        <v>0.1416270373269572</v>
       </c>
       <c r="L559" t="n">
-        <v>0.04811720402486683</v>
+        <v>0.04824515160908602</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B560" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C560" s="2" t="n">
         <v>45625.75</v>
@@ -22830,36 +22830,36 @@
         </is>
       </c>
       <c r="E560" t="n">
-        <v>166.2199859162001</v>
+        <v>240</v>
       </c>
       <c r="F560" s="2" t="n">
-        <v>45625.34530371644</v>
+        <v>45625.58550149624</v>
       </c>
       <c r="G560" t="n">
-        <v>382369.5633163138</v>
+        <v>385257.2066727304</v>
       </c>
       <c r="H560" t="n">
-        <v>59.55193703524371</v>
+        <v>59.54398870070941</v>
       </c>
       <c r="I560" t="n">
-        <v>4.146698706937881</v>
+        <v>4.103596371434564</v>
       </c>
       <c r="J560" t="n">
-        <v>3.310130415914111</v>
+        <v>3.348194452328601</v>
       </c>
       <c r="K560" t="n">
-        <v>0.1399143913424128</v>
+        <v>0.1415896372505695</v>
       </c>
       <c r="L560" t="n">
-        <v>0.04811451699183772</v>
+        <v>0.04823155914074155</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B561" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C561" s="2" t="n">
         <v>45625.75</v>
@@ -22873,33 +22873,33 @@
         <v>240</v>
       </c>
       <c r="F561" s="2" t="n">
-        <v>45625.42051092322</v>
+        <v>45625.58984871846</v>
       </c>
       <c r="G561" t="n">
-        <v>382609.5633163138</v>
+        <v>385497.2066727304</v>
       </c>
       <c r="H561" t="n">
-        <v>59.55147873010638</v>
+        <v>59.54561341368005</v>
       </c>
       <c r="I561" t="n">
-        <v>4.146090169274455</v>
+        <v>4.103825200254407</v>
       </c>
       <c r="J561" t="n">
-        <v>3.31102521377858</v>
+        <v>3.347009590543216</v>
       </c>
       <c r="K561" t="n">
-        <v>0.1399516842578176</v>
+        <v>0.1415522837427077</v>
       </c>
       <c r="L561" t="n">
-        <v>0.04811937927469818</v>
+        <v>0.04821798359699392</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B562" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C562" s="2" t="n">
         <v>45625.75</v>
@@ -22913,33 +22913,33 @@
         <v>240</v>
       </c>
       <c r="F562" s="2" t="n">
-        <v>45625.42540359999</v>
+        <v>45625.59419594068</v>
       </c>
       <c r="G562" t="n">
-        <v>382849.5633163138</v>
+        <v>385737.2066727304</v>
       </c>
       <c r="H562" t="n">
-        <v>59.55102099957195</v>
+        <v>59.54723610490581</v>
       </c>
       <c r="I562" t="n">
-        <v>4.145482394568875</v>
+        <v>4.104053744326418</v>
       </c>
       <c r="J562" t="n">
-        <v>3.31191888978471</v>
+        <v>3.345826203164882</v>
       </c>
       <c r="K562" t="n">
-        <v>0.1399889304169999</v>
+        <v>0.1415149767164492</v>
       </c>
       <c r="L562" t="n">
-        <v>0.04812423546144152</v>
+        <v>0.04820442494625242</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B563" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C563" s="2" t="n">
         <v>45625.75</v>
@@ -22953,33 +22953,33 @@
         <v>240</v>
       </c>
       <c r="F563" s="2" t="n">
-        <v>45625.43029627676</v>
+        <v>45625.5985431629</v>
       </c>
       <c r="G563" t="n">
-        <v>383089.5633163138</v>
+        <v>385977.2066727304</v>
       </c>
       <c r="H563" t="n">
-        <v>59.55056384256046</v>
+        <v>59.54885677815803</v>
       </c>
       <c r="I563" t="n">
-        <v>4.144875381387196</v>
+        <v>4.104282004181763</v>
       </c>
       <c r="J563" t="n">
-        <v>3.312811446040985</v>
+        <v>3.344644287443246</v>
       </c>
       <c r="K563" t="n">
-        <v>0.1400261299078358</v>
+        <v>0.1414777160850872</v>
       </c>
       <c r="L563" t="n">
-        <v>0.04812908556352514</v>
+        <v>0.04819088315700493</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B564" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C564" s="2" t="n">
         <v>45625.75</v>
@@ -22993,33 +22993,33 @@
         <v>240</v>
       </c>
       <c r="F564" s="2" t="n">
-        <v>45625.43518895353</v>
+        <v>45625.60289038513</v>
       </c>
       <c r="G564" t="n">
-        <v>383329.5633163138</v>
+        <v>386217.2066727304</v>
       </c>
       <c r="H564" t="n">
-        <v>59.55010725799469</v>
+        <v>59.5504754371987</v>
       </c>
       <c r="I564" t="n">
-        <v>4.144269128299064</v>
+        <v>4.10450998035029</v>
       </c>
       <c r="J564" t="n">
-        <v>3.313702884650609</v>
+        <v>3.343463840634793</v>
       </c>
       <c r="K564" t="n">
-        <v>0.1400632828179816</v>
+        <v>0.1414405017621309</v>
       </c>
       <c r="L564" t="n">
-        <v>0.04813392959237773</v>
+        <v>0.04817735819781763</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B565" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C565" s="2" t="n">
         <v>45625.75</v>
@@ -23033,33 +23033,33 @@
         <v>240</v>
       </c>
       <c r="F565" s="2" t="n">
-        <v>45625.4400816303</v>
+        <v>45625.60723760735</v>
       </c>
       <c r="G565" t="n">
-        <v>383569.5633163138</v>
+        <v>386457.2066727304</v>
       </c>
       <c r="H565" t="n">
-        <v>59.54965124480009</v>
+        <v>59.55209208578044</v>
       </c>
       <c r="I565" t="n">
-        <v>4.143663633877703</v>
+        <v>4.104737673360529</v>
       </c>
       <c r="J565" t="n">
-        <v>3.31459320771152</v>
+        <v>3.342284860002823</v>
       </c>
       <c r="K565" t="n">
-        <v>0.1401003892348741</v>
+        <v>0.1414033336613039</v>
       </c>
       <c r="L565" t="n">
-        <v>0.04813876755939937</v>
+        <v>0.04816385003733482</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B566" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C566" s="2" t="n">
         <v>45625.75</v>
@@ -23073,33 +23073,33 @@
         <v>240</v>
       </c>
       <c r="F566" s="2" t="n">
-        <v>45625.44497430707</v>
+        <v>45625.61158482957</v>
       </c>
       <c r="G566" t="n">
-        <v>383809.5633163138</v>
+        <v>386697.2066727304</v>
       </c>
       <c r="H566" t="n">
-        <v>59.54919580190481</v>
+        <v>59.55370672764658</v>
       </c>
       <c r="I566" t="n">
-        <v>4.143058896699908</v>
+        <v>4.104965083739699</v>
       </c>
       <c r="J566" t="n">
-        <v>3.315482417316409</v>
+        <v>3.341107342817429</v>
       </c>
       <c r="K566" t="n">
-        <v>0.1401374492457314</v>
+        <v>0.1413662116965444</v>
       </c>
       <c r="L566" t="n">
-        <v>0.04814359947596163</v>
+        <v>0.04815035864427861</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B567" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C567" s="2" t="n">
         <v>45625.75</v>
@@ -23110,36 +23110,36 @@
         </is>
       </c>
       <c r="E567" t="n">
-        <v>240</v>
+        <v>232.3566435834532</v>
       </c>
       <c r="F567" s="2" t="n">
-        <v>45625.44986698384</v>
+        <v>45625.61593205179</v>
       </c>
       <c r="G567" t="n">
-        <v>384049.5633163138</v>
+        <v>386929.5633163138</v>
       </c>
       <c r="H567" t="n">
-        <v>59.54874092823967</v>
+        <v>59.55526803914846</v>
       </c>
       <c r="I567" t="n">
-        <v>4.14245491534603</v>
+        <v>4.105184982931024</v>
       </c>
       <c r="J567" t="n">
-        <v>3.316370515552738</v>
+        <v>3.339968718108282</v>
       </c>
       <c r="K567" t="n">
-        <v>0.1401744629375535</v>
+        <v>0.1413303158413912</v>
       </c>
       <c r="L567" t="n">
-        <v>0.04814842535340767</v>
+        <v>0.04813731286143554</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B568" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C568" s="2" t="n">
         <v>45625.75</v>
@@ -23153,33 +23153,33 @@
         <v>240</v>
       </c>
       <c r="F568" s="2" t="n">
-        <v>45625.45475966061</v>
+        <v>45625.70924535386</v>
       </c>
       <c r="G568" t="n">
-        <v>384289.5633163138</v>
+        <v>387169.5633163138</v>
       </c>
       <c r="H568" t="n">
-        <v>59.54828662273819</v>
+        <v>59.55452979948172</v>
       </c>
       <c r="I568" t="n">
-        <v>4.141851688399967</v>
+        <v>4.107123310101342</v>
       </c>
       <c r="J568" t="n">
-        <v>3.317257504502753</v>
+        <v>3.339223126203088</v>
       </c>
       <c r="K568" t="n">
-        <v>0.1402114303971233</v>
+        <v>0.1412956957754771</v>
       </c>
       <c r="L568" t="n">
-        <v>0.04815324520305229</v>
+        <v>0.04813618943870825</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B569" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C569" s="2" t="n">
         <v>45625.75</v>
@@ -23193,33 +23193,33 @@
         <v>240</v>
       </c>
       <c r="F569" s="2" t="n">
-        <v>45625.45965233738</v>
+        <v>45625.71359257609</v>
       </c>
       <c r="G569" t="n">
-        <v>384529.5633163138</v>
+        <v>387409.5633163138</v>
       </c>
       <c r="H569" t="n">
-        <v>59.54783288433651</v>
+        <v>59.55379247449307</v>
       </c>
       <c r="I569" t="n">
-        <v>4.141249214449153</v>
+        <v>4.109059235686543</v>
       </c>
       <c r="J569" t="n">
-        <v>3.3181433862435</v>
+        <v>3.338478458085401</v>
       </c>
       <c r="K569" t="n">
-        <v>0.1402483517110069</v>
+        <v>0.1412611186037846</v>
       </c>
       <c r="L569" t="n">
-        <v>0.04815805903618206</v>
+        <v>0.04813506740790042</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B570" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C570" s="2" t="n">
         <v>45625.75</v>
@@ -23233,33 +23233,33 @@
         <v>240</v>
       </c>
       <c r="F570" s="2" t="n">
-        <v>45625.46454501415</v>
+        <v>45625.71793979831</v>
       </c>
       <c r="G570" t="n">
-        <v>384769.5633163138</v>
+        <v>387649.5633163138</v>
       </c>
       <c r="H570" t="n">
-        <v>59.54737971197346</v>
+        <v>59.55305606248363</v>
       </c>
       <c r="I570" t="n">
-        <v>4.140647492084545</v>
+        <v>4.110992764147205</v>
       </c>
       <c r="J570" t="n">
-        <v>3.319028162846845</v>
+        <v>3.337734712039426</v>
       </c>
       <c r="K570" t="n">
-        <v>0.1402852269655542</v>
+        <v>0.1412265842466442</v>
       </c>
       <c r="L570" t="n">
-        <v>0.04816286686405538</v>
+        <v>0.04813394676642676</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B571" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C571" s="2" t="n">
         <v>45625.75</v>
@@ -23273,33 +23273,33 @@
         <v>240</v>
       </c>
       <c r="F571" s="2" t="n">
-        <v>45625.46943769092</v>
+        <v>45625.72228702053</v>
       </c>
       <c r="G571" t="n">
-        <v>385009.5633163138</v>
+        <v>387889.5633163138</v>
       </c>
       <c r="H571" t="n">
-        <v>59.54692710459047</v>
+        <v>59.55232056175875</v>
       </c>
       <c r="I571" t="n">
-        <v>4.140046519900615</v>
+        <v>4.112923899932866</v>
       </c>
       <c r="J571" t="n">
-        <v>3.319911836379488</v>
+        <v>3.336991886353615</v>
       </c>
       <c r="K571" t="n">
-        <v>0.1403220562469002</v>
+        <v>0.1411920926245835</v>
       </c>
       <c r="L571" t="n">
-        <v>0.04816766869790257</v>
+        <v>0.0481328275117084</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B572" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C572" s="2" t="n">
         <v>45625.75</v>
@@ -23313,33 +23313,33 @@
         <v>240</v>
       </c>
       <c r="F572" s="2" t="n">
-        <v>45625.4743303677</v>
+        <v>45625.72663424275</v>
       </c>
       <c r="G572" t="n">
-        <v>385249.5633163138</v>
+        <v>388129.5633163138</v>
       </c>
       <c r="H572" t="n">
-        <v>59.54647506113168</v>
+        <v>59.55158597062793</v>
       </c>
       <c r="I572" t="n">
-        <v>4.139446296495335</v>
+        <v>4.11485264748206</v>
       </c>
       <c r="J572" t="n">
-        <v>3.320794408902977</v>
+        <v>3.336249979320653</v>
       </c>
       <c r="K572" t="n">
-        <v>0.140358839640965</v>
+        <v>0.1411576436583268</v>
       </c>
       <c r="L572" t="n">
-        <v>0.048172464548926</v>
+        <v>0.04813170964117284</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B573" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C573" s="2" t="n">
         <v>45625.75</v>
@@ -23353,33 +23353,33 @@
         <v>240</v>
       </c>
       <c r="F573" s="2" t="n">
-        <v>45625.47922304447</v>
+        <v>45625.73098146498</v>
       </c>
       <c r="G573" t="n">
-        <v>385489.5633163138</v>
+        <v>388369.5633163138</v>
       </c>
       <c r="H573" t="n">
-        <v>59.54602358054379</v>
+        <v>59.55085228740487</v>
       </c>
       <c r="I573" t="n">
-        <v>4.138846820470172</v>
+        <v>4.116779011222349</v>
       </c>
       <c r="J573" t="n">
-        <v>3.321675882473727</v>
+        <v>3.335508989237446</v>
       </c>
       <c r="K573" t="n">
-        <v>0.1403955772334547</v>
+        <v>0.1411232372687944</v>
       </c>
       <c r="L573" t="n">
-        <v>0.04817725442830009</v>
+        <v>0.04813059315225393</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B574" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C574" s="2" t="n">
         <v>45625.75</v>
@@ -23393,33 +23393,33 @@
         <v>240</v>
       </c>
       <c r="F574" s="2" t="n">
-        <v>45625.48411572124</v>
+        <v>45625.7353286872</v>
       </c>
       <c r="G574" t="n">
-        <v>385729.5633163138</v>
+        <v>388609.5633163138</v>
       </c>
       <c r="H574" t="n">
-        <v>59.54557266177615</v>
+        <v>59.55011951040745</v>
       </c>
       <c r="I574" t="n">
-        <v>4.13824809043007</v>
+        <v>4.118702995570356</v>
       </c>
       <c r="J574" t="n">
-        <v>3.322556259143036</v>
+        <v>3.334768914405106</v>
       </c>
       <c r="K574" t="n">
-        <v>0.1404322691098624</v>
+        <v>0.1410888733771018</v>
       </c>
       <c r="L574" t="n">
-        <v>0.0481820383471715</v>
+        <v>0.04812947804239188</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B575" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C575" s="2" t="n">
         <v>45625.75</v>
@@ -23433,33 +23433,33 @@
         <v>240</v>
       </c>
       <c r="F575" s="2" t="n">
-        <v>45625.48900839801</v>
+        <v>45625.73967590942</v>
       </c>
       <c r="G575" t="n">
-        <v>385969.5633163138</v>
+        <v>388849.5633163138</v>
       </c>
       <c r="H575" t="n">
-        <v>59.54512230378074</v>
+        <v>59.54938763795768</v>
       </c>
       <c r="I575" t="n">
-        <v>4.137650104983445</v>
+        <v>4.120624604931802</v>
       </c>
       <c r="J575" t="n">
-        <v>3.323435540957099</v>
+        <v>3.33402975312894</v>
       </c>
       <c r="K575" t="n">
-        <v>0.1404689153554682</v>
+        <v>0.1410545519045593</v>
       </c>
       <c r="L575" t="n">
-        <v>0.04818681631665912</v>
+        <v>0.04812836430903319</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B576" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C576" s="2" t="n">
         <v>45625.75</v>
@@ -23473,33 +23473,33 @@
         <v>240</v>
       </c>
       <c r="F576" s="2" t="n">
-        <v>45625.49390107478</v>
+        <v>45625.74402313164</v>
       </c>
       <c r="G576" t="n">
-        <v>386209.5633163138</v>
+        <v>389089.5633163138</v>
       </c>
       <c r="H576" t="n">
-        <v>59.5446725055121</v>
+        <v>59.54865666838172</v>
       </c>
       <c r="I576" t="n">
-        <v>4.137052862742172</v>
+        <v>4.122543843701537</v>
       </c>
       <c r="J576" t="n">
-        <v>3.324313729957024</v>
+        <v>3.333291503718438</v>
       </c>
       <c r="K576" t="n">
-        <v>0.1405055160553403</v>
+        <v>0.1410202727726715</v>
       </c>
       <c r="L576" t="n">
-        <v>0.04819158834785425</v>
+        <v>0.0481272519496307</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B577" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C577" s="2" t="n">
         <v>45625.75</v>
@@ -23513,33 +23513,33 @@
         <v>240</v>
       </c>
       <c r="F577" s="2" t="n">
-        <v>45625.49879375155</v>
+        <v>45625.74837035387</v>
       </c>
       <c r="G577" t="n">
-        <v>386449.5633163138</v>
+        <v>389329.5633163138</v>
       </c>
       <c r="H577" t="n">
-        <v>59.54422326592743</v>
+        <v>59.54792660000984</v>
       </c>
       <c r="I577" t="n">
-        <v>4.136456362321574</v>
+        <v>4.124460716263576</v>
       </c>
       <c r="J577" t="n">
-        <v>3.325190828178851</v>
+        <v>3.332554164487255</v>
       </c>
       <c r="K577" t="n">
-        <v>0.1405420712943358</v>
+        <v>0.1409860359031364</v>
       </c>
       <c r="L577" t="n">
-        <v>0.0481963544518206</v>
+        <v>0.04812614096164348</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B578" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C578" s="2" t="n">
         <v>45625.75</v>
@@ -23553,33 +23553,33 @@
         <v>240</v>
       </c>
       <c r="F578" s="2" t="n">
-        <v>45625.50368642832</v>
+        <v>45625.56912898894</v>
       </c>
       <c r="G578" t="n">
-        <v>386689.5633163138</v>
+        <v>389569.5633163138</v>
       </c>
       <c r="H578" t="n">
-        <v>59.54378359019532</v>
+        <v>59.54830045287135</v>
       </c>
       <c r="I578" t="n">
-        <v>4.135855731565115</v>
+        <v>4.12343246403439</v>
       </c>
       <c r="J578" t="n">
-        <v>3.326063775390044</v>
+        <v>3.333139837861173</v>
       </c>
       <c r="K578" t="n">
-        <v>0.1405785899305466</v>
+        <v>0.1410228026137113</v>
       </c>
       <c r="L578" t="n">
-        <v>0.04820098831953578</v>
+        <v>0.04811938695907614</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B579" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C579" s="2" t="n">
         <v>45625.75</v>
@@ -23593,33 +23593,33 @@
         <v>240</v>
       </c>
       <c r="F579" s="2" t="n">
-        <v>45625.51530954447</v>
+        <v>45625.57402166571</v>
       </c>
       <c r="G579" t="n">
-        <v>386929.5633163138</v>
+        <v>389809.5633163138</v>
       </c>
       <c r="H579" t="n">
-        <v>59.5441625636113</v>
+        <v>59.54867384538146</v>
       </c>
       <c r="I579" t="n">
-        <v>4.134813395662635</v>
+        <v>4.122405477964673</v>
       </c>
       <c r="J579" t="n">
-        <v>3.326657470562719</v>
+        <v>3.33372479005417</v>
       </c>
       <c r="K579" t="n">
-        <v>0.1406158602241191</v>
+        <v>0.1410595240508431</v>
       </c>
       <c r="L579" t="n">
-        <v>0.04819414180934931</v>
+        <v>0.04811264127318837</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B580" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C580" s="2" t="n">
         <v>45625.75</v>
@@ -23633,33 +23633,33 @@
         <v>240</v>
       </c>
       <c r="F580" s="2" t="n">
-        <v>45625.52020222124</v>
+        <v>45625.57891434249</v>
       </c>
       <c r="G580" t="n">
-        <v>387169.5633163138</v>
+        <v>390049.5633163138</v>
       </c>
       <c r="H580" t="n">
-        <v>59.5445410671886</v>
+        <v>59.54904677838996</v>
       </c>
       <c r="I580" t="n">
-        <v>4.13377235201368</v>
+        <v>4.121379755717197</v>
       </c>
       <c r="J580" t="n">
-        <v>3.327250429691786</v>
+        <v>3.33430902239749</v>
       </c>
       <c r="K580" t="n">
-        <v>0.1406530843112161</v>
+        <v>0.141096200298103</v>
       </c>
       <c r="L580" t="n">
-        <v>0.04818730378723939</v>
+        <v>0.04810590388862826</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B581" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C581" s="2" t="n">
         <v>45625.75</v>
@@ -23673,33 +23673,33 @@
         <v>240</v>
       </c>
       <c r="F581" s="2" t="n">
-        <v>45625.52509489801</v>
+        <v>45625.58380701926</v>
       </c>
       <c r="G581" t="n">
-        <v>387409.5633163138</v>
+        <v>390289.5633163138</v>
       </c>
       <c r="H581" t="n">
-        <v>59.5449191018004</v>
+        <v>59.54941925274452</v>
       </c>
       <c r="I581" t="n">
-        <v>4.1327325982166</v>
+        <v>4.120355294960484</v>
       </c>
       <c r="J581" t="n">
-        <v>3.327842654145178</v>
+        <v>3.334892536219098</v>
       </c>
       <c r="K581" t="n">
-        <v>0.1406902622777124</v>
+        <v>0.1411328314388565</v>
       </c>
       <c r="L581" t="n">
-        <v>0.04818047423743094</v>
+        <v>0.04809917479008164</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B582" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C582" s="2" t="n">
         <v>45625.75</v>
@@ -23713,33 +23713,33 @@
         <v>240</v>
       </c>
       <c r="F582" s="2" t="n">
-        <v>45625.52998757478</v>
+        <v>45625.58869969603</v>
       </c>
       <c r="G582" t="n">
-        <v>387649.5633163138</v>
+        <v>390529.5633163138</v>
       </c>
       <c r="H582" t="n">
-        <v>59.54529666831774</v>
+        <v>59.54979126929074</v>
       </c>
       <c r="I582" t="n">
-        <v>4.13169413187569</v>
+        <v>4.119332093368786</v>
       </c>
       <c r="J582" t="n">
-        <v>3.328434145287444</v>
+        <v>3.335475332843699</v>
       </c>
       <c r="K582" t="n">
-        <v>0.1407273942092699</v>
+        <v>0.1411694175562642</v>
       </c>
       <c r="L582" t="n">
-        <v>0.04817365314418795</v>
+        <v>0.04809245396227201</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B583" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C583" s="2" t="n">
         <v>45625.75</v>
@@ -23753,33 +23753,33 @@
         <v>240</v>
       </c>
       <c r="F583" s="2" t="n">
-        <v>45625.53488025155</v>
+        <v>45625.5935923728</v>
       </c>
       <c r="G583" t="n">
-        <v>387889.5633163138</v>
+        <v>390769.5633163138</v>
       </c>
       <c r="H583" t="n">
-        <v>59.54567376760949</v>
+        <v>59.55016282887215</v>
       </c>
       <c r="I583" t="n">
-        <v>4.130656950601178</v>
+        <v>4.118310148622068</v>
       </c>
       <c r="J583" t="n">
-        <v>3.329024904479756</v>
+        <v>3.336057413592739</v>
       </c>
       <c r="K583" t="n">
-        <v>0.1407644801913386</v>
+        <v>0.1412059587332825</v>
       </c>
       <c r="L583" t="n">
-        <v>0.04816684049181336</v>
+        <v>0.04808574138996037</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B584" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C584" s="2" t="n">
         <v>45625.75</v>
@@ -23793,33 +23793,33 @@
         <v>240</v>
       </c>
       <c r="F584" s="2" t="n">
-        <v>45625.53977292832</v>
+        <v>45625.59848504957</v>
       </c>
       <c r="G584" t="n">
-        <v>388129.5633163138</v>
+        <v>391009.5633163138</v>
       </c>
       <c r="H584" t="n">
-        <v>59.54605040054239</v>
+        <v>59.55053393233019</v>
       </c>
       <c r="I584" t="n">
-        <v>4.129621052009201</v>
+        <v>4.117289458405991</v>
       </c>
       <c r="J584" t="n">
-        <v>3.329614933079918</v>
+        <v>3.336638779784425</v>
       </c>
       <c r="K584" t="n">
-        <v>0.1408015203091571</v>
+        <v>0.141242455052664</v>
       </c>
       <c r="L584" t="n">
-        <v>0.04816003626464892</v>
+        <v>0.04807903705794517</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B585" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C585" s="2" t="n">
         <v>45625.75</v>
@@ -23833,33 +23833,33 @@
         <v>240</v>
       </c>
       <c r="F585" s="2" t="n">
-        <v>45625.54466560509</v>
+        <v>45625.60337772634</v>
       </c>
       <c r="G585" t="n">
-        <v>388369.5633163138</v>
+        <v>391249.5633163138</v>
       </c>
       <c r="H585" t="n">
-        <v>59.54642656798102</v>
+        <v>59.55092583818333</v>
       </c>
       <c r="I585" t="n">
-        <v>4.128586433721786</v>
+        <v>4.116262714303941</v>
       </c>
       <c r="J585" t="n">
-        <v>3.330204232442377</v>
+        <v>3.337203493758155</v>
       </c>
       <c r="K585" t="n">
-        <v>0.1408385146477533</v>
+        <v>0.1412794346732965</v>
       </c>
       <c r="L585" t="n">
-        <v>0.04815324044707512</v>
+        <v>0.04807220742418991</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B586" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C586" s="2" t="n">
         <v>45625.75</v>
@@ -23873,33 +23873,33 @@
         <v>240</v>
       </c>
       <c r="F586" s="2" t="n">
-        <v>45625.54955828186</v>
+        <v>45625.64093092067</v>
       </c>
       <c r="G586" t="n">
-        <v>388609.5633163138</v>
+        <v>391489.5633163138</v>
       </c>
       <c r="H586" t="n">
-        <v>59.54680227078781</v>
+        <v>59.5518534951961</v>
       </c>
       <c r="I586" t="n">
-        <v>4.127553093366839</v>
+        <v>4.115052930197768</v>
       </c>
       <c r="J586" t="n">
-        <v>3.330792803918236</v>
+        <v>3.337365449650315</v>
       </c>
       <c r="K586" t="n">
-        <v>0.1408754632919452</v>
+        <v>0.1413296898461592</v>
       </c>
       <c r="L586" t="n">
-        <v>0.04814645302351099</v>
+        <v>0.04806201790662522</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B587" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C587" s="2" t="n">
         <v>45625.75</v>
@@ -23913,33 +23913,33 @@
         <v>240</v>
       </c>
       <c r="F587" s="2" t="n">
-        <v>45625.55445095863</v>
+        <v>45625.64582359744</v>
       </c>
       <c r="G587" t="n">
-        <v>388849.5633163138</v>
+        <v>391729.5633163138</v>
       </c>
       <c r="H587" t="n">
-        <v>59.54717750982311</v>
+        <v>59.55278001551812</v>
       </c>
       <c r="I587" t="n">
-        <v>4.126521028578118</v>
+        <v>4.113844628482574</v>
       </c>
       <c r="J587" t="n">
-        <v>3.33138064885526</v>
+        <v>3.337527207092228</v>
       </c>
       <c r="K587" t="n">
-        <v>0.1409123663263412</v>
+        <v>0.1413798834395925</v>
       </c>
       <c r="L587" t="n">
-        <v>0.04813967397841405</v>
+        <v>0.04805184087463447</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B588" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C588" s="2" t="n">
         <v>45625.75</v>
@@ -23953,33 +23953,33 @@
         <v>240</v>
       </c>
       <c r="F588" s="2" t="n">
-        <v>45625.5593436354</v>
+        <v>45625.65071627421</v>
       </c>
       <c r="G588" t="n">
-        <v>389089.5633163138</v>
+        <v>391969.5633163138</v>
       </c>
       <c r="H588" t="n">
-        <v>59.54755228594509</v>
+        <v>59.55370540123737</v>
       </c>
       <c r="I588" t="n">
-        <v>4.125490236995223</v>
+        <v>4.112637806435388</v>
       </c>
       <c r="J588" t="n">
-        <v>3.331967768597891</v>
+        <v>3.337688766448424</v>
       </c>
       <c r="K588" t="n">
-        <v>0.1409492238353411</v>
+        <v>0.1414300155667104</v>
       </c>
       <c r="L588" t="n">
-        <v>0.04813290329628019</v>
+        <v>0.04804167630528321</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B589" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C589" s="2" t="n">
         <v>45625.75</v>
@@ -23993,33 +23993,33 @@
         <v>240</v>
       </c>
       <c r="F589" s="2" t="n">
-        <v>45625.56423631217</v>
+        <v>45625.65560895098</v>
       </c>
       <c r="G589" t="n">
-        <v>389329.5633163138</v>
+        <v>392209.5633163138</v>
       </c>
       <c r="H589" t="n">
-        <v>59.54792660000984</v>
+        <v>59.5546296544367</v>
       </c>
       <c r="I589" t="n">
-        <v>4.124460716263571</v>
+        <v>4.111432461339906</v>
       </c>
       <c r="J589" t="n">
-        <v>3.332554164487255</v>
+        <v>3.337850128082539</v>
       </c>
       <c r="K589" t="n">
-        <v>0.1409860359031364</v>
+        <v>0.1414800863403497</v>
       </c>
       <c r="L589" t="n">
-        <v>0.04812614096164348</v>
+        <v>0.0480315241756931</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B590" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C590" s="2" t="n">
         <v>45625.75</v>
@@ -24033,33 +24033,33 @@
         <v>240</v>
       </c>
       <c r="F590" s="2" t="n">
-        <v>45625.56912898894</v>
+        <v>45625.66050162775</v>
       </c>
       <c r="G590" t="n">
-        <v>389569.5633163138</v>
+        <v>392449.5633163138</v>
       </c>
       <c r="H590" t="n">
-        <v>59.54830045287135</v>
+        <v>59.55555277719386</v>
       </c>
       <c r="I590" t="n">
-        <v>4.123432464034384</v>
+        <v>4.110228590486467</v>
       </c>
       <c r="J590" t="n">
-        <v>3.333139837861173</v>
+        <v>3.33801129235732</v>
       </c>
       <c r="K590" t="n">
-        <v>0.1410228026137113</v>
+        <v>0.1415300958730715</v>
       </c>
       <c r="L590" t="n">
-        <v>0.04811938695907614</v>
+        <v>0.04802138446304177</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B591" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C591" s="2" t="n">
         <v>45625.75</v>
@@ -24073,33 +24073,33 @@
         <v>240</v>
       </c>
       <c r="F591" s="2" t="n">
-        <v>45625.57402166571</v>
+        <v>45625.66539430452</v>
       </c>
       <c r="G591" t="n">
-        <v>389809.5633163138</v>
+        <v>392689.5633163138</v>
       </c>
       <c r="H591" t="n">
-        <v>59.54867384538146</v>
+        <v>59.55647477158153</v>
       </c>
       <c r="I591" t="n">
-        <v>4.122405477964667</v>
+        <v>4.109026191172034</v>
       </c>
       <c r="J591" t="n">
-        <v>3.33372479005417</v>
+        <v>3.338172259634628</v>
       </c>
       <c r="K591" t="n">
-        <v>0.1410595240508431</v>
+        <v>0.1415800442771615</v>
       </c>
       <c r="L591" t="n">
-        <v>0.04811264127318837</v>
+        <v>0.04801125714456266</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B592" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C592" s="2" t="n">
         <v>45625.75</v>
@@ -24113,33 +24113,33 @@
         <v>240</v>
       </c>
       <c r="F592" s="2" t="n">
-        <v>45625.57891434249</v>
+        <v>45625.67028698129</v>
       </c>
       <c r="G592" t="n">
-        <v>390049.5633163138</v>
+        <v>392929.5633163138</v>
       </c>
       <c r="H592" t="n">
-        <v>59.54904677838996</v>
+        <v>59.55739563966731</v>
       </c>
       <c r="I592" t="n">
-        <v>4.121379755717192</v>
+        <v>4.107825260700174</v>
       </c>
       <c r="J592" t="n">
-        <v>3.33430902239749</v>
+        <v>3.338333030275438</v>
       </c>
       <c r="K592" t="n">
-        <v>0.1410962002981029</v>
+        <v>0.1416299316646313</v>
       </c>
       <c r="L592" t="n">
-        <v>0.04810590388862826</v>
+        <v>0.0480011421975448</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B593" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C593" s="2" t="n">
         <v>45625.75</v>
@@ -24153,33 +24153,33 @@
         <v>240</v>
       </c>
       <c r="F593" s="2" t="n">
-        <v>45625.58380701926</v>
+        <v>45625.67517965806</v>
       </c>
       <c r="G593" t="n">
-        <v>390289.5633163138</v>
+        <v>393169.5633163138</v>
       </c>
       <c r="H593" t="n">
-        <v>59.54941925274452</v>
+        <v>59.55831538351378</v>
       </c>
       <c r="I593" t="n">
-        <v>4.120355294960479</v>
+        <v>4.106625796381039</v>
       </c>
       <c r="J593" t="n">
-        <v>3.334892536219098</v>
+        <v>3.338493604639845</v>
       </c>
       <c r="K593" t="n">
-        <v>0.1411328314388564</v>
+        <v>0.1416797581472187</v>
       </c>
       <c r="L593" t="n">
-        <v>0.04809917479008164</v>
+        <v>0.0479910395993327</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B594" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C594" s="2" t="n">
         <v>45625.75</v>
@@ -24193,33 +24193,33 @@
         <v>240</v>
       </c>
       <c r="F594" s="2" t="n">
-        <v>45625.58869969603</v>
+        <v>45625.68007233484</v>
       </c>
       <c r="G594" t="n">
-        <v>390529.5633163138</v>
+        <v>393409.5633163138</v>
       </c>
       <c r="H594" t="n">
-        <v>59.54979126929074</v>
+        <v>59.55923400517846</v>
       </c>
       <c r="I594" t="n">
-        <v>4.119332093368781</v>
+        <v>4.105427795531343</v>
       </c>
       <c r="J594" t="n">
-        <v>3.335475332843699</v>
+        <v>3.338653983087065</v>
       </c>
       <c r="K594" t="n">
-        <v>0.1411694175562641</v>
+        <v>0.1417295238363891</v>
       </c>
       <c r="L594" t="n">
-        <v>0.04809245396227201</v>
+        <v>0.04798094932732615</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B595" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C595" s="2" t="n">
         <v>45625.75</v>
@@ -24233,33 +24233,33 @@
         <v>240</v>
       </c>
       <c r="F595" s="2" t="n">
-        <v>45625.5935923728</v>
+        <v>45625.68496501161</v>
       </c>
       <c r="G595" t="n">
-        <v>390769.5633163138</v>
+        <v>393649.5633163138</v>
       </c>
       <c r="H595" t="n">
-        <v>59.55016282887215</v>
+        <v>59.56015150671387</v>
       </c>
       <c r="I595" t="n">
-        <v>4.118310148622063</v>
+        <v>4.104231255474346</v>
       </c>
       <c r="J595" t="n">
-        <v>3.336057413592739</v>
+        <v>3.338814165975439</v>
       </c>
       <c r="K595" t="n">
-        <v>0.1412059587332824</v>
+        <v>0.141779228843336</v>
       </c>
       <c r="L595" t="n">
-        <v>0.04808574138996037</v>
+        <v>0.04797087135898005</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B596" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C596" s="2" t="n">
         <v>45625.75</v>
@@ -24273,33 +24273,33 @@
         <v>240</v>
       </c>
       <c r="F596" s="2" t="n">
-        <v>45625.59848504957</v>
+        <v>45625.68985768838</v>
       </c>
       <c r="G596" t="n">
-        <v>391009.5633163138</v>
+        <v>393889.5633163138</v>
       </c>
       <c r="H596" t="n">
-        <v>59.55053393233019</v>
+        <v>59.56106789016751</v>
       </c>
       <c r="I596" t="n">
-        <v>4.117289458405986</v>
+        <v>4.10303617353983</v>
       </c>
       <c r="J596" t="n">
-        <v>3.336638779784425</v>
+        <v>3.338974153662432</v>
       </c>
       <c r="K596" t="n">
-        <v>0.1412424550526639</v>
+        <v>0.1418288732789818</v>
       </c>
       <c r="L596" t="n">
-        <v>0.04807903705794517</v>
+        <v>0.04796080567180425</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B597" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C597" s="2" t="n">
         <v>45625.75</v>
@@ -24313,33 +24313,33 @@
         <v>240</v>
       </c>
       <c r="F597" s="2" t="n">
-        <v>45625.60337772634</v>
+        <v>45625.69475036515</v>
       </c>
       <c r="G597" t="n">
-        <v>391249.5633163138</v>
+        <v>394129.5633163138</v>
       </c>
       <c r="H597" t="n">
-        <v>59.55092583818333</v>
+        <v>59.56198315758193</v>
       </c>
       <c r="I597" t="n">
-        <v>4.116262714303936</v>
+        <v>4.101842547064082</v>
       </c>
       <c r="J597" t="n">
-        <v>3.337203493758155</v>
+        <v>3.339133946504641</v>
       </c>
       <c r="K597" t="n">
-        <v>0.1412794346732964</v>
+        <v>0.1418784572539788</v>
       </c>
       <c r="L597" t="n">
-        <v>0.04807220742418991</v>
+        <v>0.04795075224336338</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B598" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C598" s="2" t="n">
         <v>45625.75</v>
@@ -24353,33 +24353,33 @@
         <v>240</v>
       </c>
       <c r="F598" s="2" t="n">
-        <v>45625.64093092067</v>
+        <v>45625.69964304192</v>
       </c>
       <c r="G598" t="n">
-        <v>391489.5633163138</v>
+        <v>394369.5633163138</v>
       </c>
       <c r="H598" t="n">
-        <v>59.5518534951961</v>
+        <v>59.56289731099464</v>
       </c>
       <c r="I598" t="n">
-        <v>4.115052930197763</v>
+        <v>4.100650373389872</v>
       </c>
       <c r="J598" t="n">
-        <v>3.337365449650315</v>
+        <v>3.339293544857794</v>
       </c>
       <c r="K598" t="n">
-        <v>0.1413296898461591</v>
+        <v>0.1419279808787099</v>
       </c>
       <c r="L598" t="n">
-        <v>0.04806201790662522</v>
+        <v>0.04794071105127667</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B599" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C599" s="2" t="n">
         <v>45625.75</v>
@@ -24393,33 +24393,33 @@
         <v>240</v>
       </c>
       <c r="F599" s="2" t="n">
-        <v>45625.64582359744</v>
+        <v>45625.70453571869</v>
       </c>
       <c r="G599" t="n">
-        <v>391729.5633163138</v>
+        <v>394609.5633163138</v>
       </c>
       <c r="H599" t="n">
-        <v>59.55278001551812</v>
+        <v>59.56381035243827</v>
       </c>
       <c r="I599" t="n">
-        <v>4.113844628482568</v>
+        <v>4.099459649866436</v>
       </c>
       <c r="J599" t="n">
-        <v>3.337527207092228</v>
+        <v>3.339452949076752</v>
       </c>
       <c r="K599" t="n">
-        <v>0.1413798834395925</v>
+        <v>0.1419774442632895</v>
       </c>
       <c r="L599" t="n">
-        <v>0.04805184087463447</v>
+        <v>0.04793068207321784</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B600" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C600" s="2" t="n">
         <v>45625.75</v>
@@ -24433,33 +24433,33 @@
         <v>240</v>
       </c>
       <c r="F600" s="2" t="n">
-        <v>45625.65071627421</v>
+        <v>45625.70942839546</v>
       </c>
       <c r="G600" t="n">
-        <v>391969.5633163138</v>
+        <v>394849.5633163138</v>
       </c>
       <c r="H600" t="n">
-        <v>59.55370540123737</v>
+        <v>59.56472228394046</v>
       </c>
       <c r="I600" t="n">
-        <v>4.112637806435384</v>
+        <v>4.098270373849454</v>
       </c>
       <c r="J600" t="n">
-        <v>3.337688766448424</v>
+        <v>3.339612159515516</v>
       </c>
       <c r="K600" t="n">
-        <v>0.1414300155667103</v>
+        <v>0.1420268475175643</v>
       </c>
       <c r="L600" t="n">
-        <v>0.04804167630528321</v>
+        <v>0.04792066528691484</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B601" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C601" s="2" t="n">
         <v>45625.75</v>
@@ -24473,33 +24473,33 @@
         <v>240</v>
       </c>
       <c r="F601" s="2" t="n">
-        <v>45625.65560895098</v>
+        <v>45625.71432107224</v>
       </c>
       <c r="G601" t="n">
-        <v>392209.5633163138</v>
+        <v>395089.5633163138</v>
       </c>
       <c r="H601" t="n">
-        <v>59.5546296544367</v>
+        <v>59.56563310752394</v>
       </c>
       <c r="I601" t="n">
-        <v>4.111432461339902</v>
+        <v>4.097082542701031</v>
       </c>
       <c r="J601" t="n">
-        <v>3.337850128082539</v>
+        <v>3.339771176527226</v>
       </c>
       <c r="K601" t="n">
-        <v>0.1414800863403497</v>
+        <v>0.1420761907511141</v>
       </c>
       <c r="L601" t="n">
-        <v>0.0480315241756931</v>
+        <v>0.04791066067014976</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B602" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C602" s="2" t="n">
         <v>45625.75</v>
@@ -24513,33 +24513,33 @@
         <v>240</v>
       </c>
       <c r="F602" s="2" t="n">
-        <v>45625.66050162775</v>
+        <v>45625.71921374901</v>
       </c>
       <c r="G602" t="n">
-        <v>392449.5633163138</v>
+        <v>395329.5633163138</v>
       </c>
       <c r="H602" t="n">
-        <v>59.55555277719386</v>
+        <v>59.56654282520651</v>
       </c>
       <c r="I602" t="n">
-        <v>4.110228590486463</v>
+        <v>4.095896153789679</v>
       </c>
       <c r="J602" t="n">
-        <v>3.33801129235732</v>
+        <v>3.339930000464162</v>
       </c>
       <c r="K602" t="n">
-        <v>0.1415300958730715</v>
+        <v>0.1421254740732524</v>
       </c>
       <c r="L602" t="n">
-        <v>0.04802138446304177</v>
+        <v>0.04790066820075867</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B603" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C603" s="2" t="n">
         <v>45625.75</v>
@@ -24553,33 +24553,33 @@
         <v>240</v>
       </c>
       <c r="F603" s="2" t="n">
-        <v>45625.66539430452</v>
+        <v>45625.72410642578</v>
       </c>
       <c r="G603" t="n">
-        <v>392689.5633163138</v>
+        <v>395569.5633163138</v>
       </c>
       <c r="H603" t="n">
-        <v>59.55647477158153</v>
+        <v>59.5674514390011</v>
       </c>
       <c r="I603" t="n">
-        <v>4.109026191172029</v>
+        <v>4.094711204490294</v>
       </c>
       <c r="J603" t="n">
-        <v>3.338172259634628</v>
+        <v>3.340088631677753</v>
       </c>
       <c r="K603" t="n">
-        <v>0.1415800442771615</v>
+        <v>0.1421746975930277</v>
       </c>
       <c r="L603" t="n">
-        <v>0.04801125714456266</v>
+        <v>0.04789068785663136</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B604" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C604" s="2" t="n">
         <v>45625.75</v>
@@ -24593,33 +24593,33 @@
         <v>240</v>
       </c>
       <c r="F604" s="2" t="n">
-        <v>45625.67028698129</v>
+        <v>45625.72899910255</v>
       </c>
       <c r="G604" t="n">
-        <v>392929.5633163138</v>
+        <v>395809.5633163138</v>
       </c>
       <c r="H604" t="n">
-        <v>59.55739563966731</v>
+        <v>59.56835895091574</v>
       </c>
       <c r="I604" t="n">
-        <v>4.107825260700169</v>
+        <v>4.093527692184142</v>
       </c>
       <c r="J604" t="n">
-        <v>3.338333030275438</v>
+        <v>3.340247070518573</v>
       </c>
       <c r="K604" t="n">
-        <v>0.1416299316646313</v>
+        <v>0.1422238614192239</v>
       </c>
       <c r="L604" t="n">
-        <v>0.0480011421975448</v>
+        <v>0.04788071961571133</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B605" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C605" s="2" t="n">
         <v>45625.75</v>
@@ -24633,33 +24633,33 @@
         <v>240</v>
       </c>
       <c r="F605" s="2" t="n">
-        <v>45625.67517965806</v>
+        <v>45625.73389177932</v>
       </c>
       <c r="G605" t="n">
-        <v>393169.5633163138</v>
+        <v>396049.5633163138</v>
       </c>
       <c r="H605" t="n">
-        <v>59.55831538351378</v>
+        <v>59.5692653629536</v>
       </c>
       <c r="I605" t="n">
-        <v>4.106625796381033</v>
+        <v>4.092345614258834</v>
       </c>
       <c r="J605" t="n">
-        <v>3.338493604639845</v>
+        <v>3.340405317336347</v>
       </c>
       <c r="K605" t="n">
-        <v>0.1416797581472187</v>
+        <v>0.1422729656603612</v>
       </c>
       <c r="L605" t="n">
-        <v>0.0479910395993327</v>
+        <v>0.04787076345599547</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B606" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C606" s="2" t="n">
         <v>45625.75</v>
@@ -24673,33 +24673,33 @@
         <v>240</v>
       </c>
       <c r="F606" s="2" t="n">
-        <v>45625.68007233484</v>
+        <v>45625.73878445609</v>
       </c>
       <c r="G606" t="n">
-        <v>393409.5633163138</v>
+        <v>396289.5633163138</v>
       </c>
       <c r="H606" t="n">
-        <v>59.55923400517846</v>
+        <v>59.57017067711299</v>
       </c>
       <c r="I606" t="n">
-        <v>4.105427795531337</v>
+        <v>4.09116496810831</v>
       </c>
       <c r="J606" t="n">
-        <v>3.338653983087065</v>
+        <v>3.340563372479952</v>
       </c>
       <c r="K606" t="n">
-        <v>0.1417295238363891</v>
+        <v>0.1423220104246968</v>
       </c>
       <c r="L606" t="n">
-        <v>0.04798094932732615</v>
+        <v>0.04786081935553403</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B607" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C607" s="2" t="n">
         <v>45625.75</v>
@@ -24713,33 +24713,33 @@
         <v>240</v>
       </c>
       <c r="F607" s="2" t="n">
-        <v>45625.68496501161</v>
+        <v>45625.74367713286</v>
       </c>
       <c r="G607" t="n">
-        <v>393649.5633163138</v>
+        <v>396529.5633163138</v>
       </c>
       <c r="H607" t="n">
-        <v>59.56015150671387</v>
+        <v>59.5710748953874</v>
       </c>
       <c r="I607" t="n">
-        <v>4.104231255474341</v>
+        <v>4.08998575113282</v>
       </c>
       <c r="J607" t="n">
-        <v>3.338814165975439</v>
+        <v>3.340721236297421</v>
       </c>
       <c r="K607" t="n">
-        <v>0.141779228843336</v>
+        <v>0.1423709958202261</v>
       </c>
       <c r="L607" t="n">
-        <v>0.04797087135898005</v>
+        <v>0.04785088729243037</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B608" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C608" s="2" t="n">
         <v>45625.75</v>
@@ -24753,504 +24753,24 @@
         <v>240</v>
       </c>
       <c r="F608" s="2" t="n">
-        <v>45625.68985768838</v>
+        <v>45625.74856980963</v>
       </c>
       <c r="G608" t="n">
-        <v>393889.5633163138</v>
+        <v>396769.5633163138</v>
       </c>
       <c r="H608" t="n">
-        <v>59.56106789016751</v>
+        <v>59.57197801976546</v>
       </c>
       <c r="I608" t="n">
-        <v>4.103036173539825</v>
+        <v>4.088807960738905</v>
       </c>
       <c r="J608" t="n">
-        <v>3.338974153662432</v>
+        <v>3.340878909135947</v>
       </c>
       <c r="K608" t="n">
-        <v>0.1418288732789818</v>
+        <v>0.1424199219546828</v>
       </c>
       <c r="L608" t="n">
-        <v>0.04796080567180425</v>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="n">
-        <v>2</v>
-      </c>
-      <c r="B609" s="2" t="n">
-        <v>45625.25</v>
-      </c>
-      <c r="C609" s="2" t="n">
-        <v>45625.75</v>
-      </c>
-      <c r="D609" t="inlineStr">
-        <is>
-          <t>CEN01_RP01_0107</t>
-        </is>
-      </c>
-      <c r="E609" t="n">
-        <v>240</v>
-      </c>
-      <c r="F609" s="2" t="n">
-        <v>45625.69475036515</v>
-      </c>
-      <c r="G609" t="n">
-        <v>394129.5633163138</v>
-      </c>
-      <c r="H609" t="n">
-        <v>59.56198315758193</v>
-      </c>
-      <c r="I609" t="n">
-        <v>4.101842547064076</v>
-      </c>
-      <c r="J609" t="n">
-        <v>3.339133946504641</v>
-      </c>
-      <c r="K609" t="n">
-        <v>0.1418784572539788</v>
-      </c>
-      <c r="L609" t="n">
-        <v>0.04795075224336338</v>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" t="n">
-        <v>2</v>
-      </c>
-      <c r="B610" s="2" t="n">
-        <v>45625.25</v>
-      </c>
-      <c r="C610" s="2" t="n">
-        <v>45625.75</v>
-      </c>
-      <c r="D610" t="inlineStr">
-        <is>
-          <t>CEN01_RP01_0107</t>
-        </is>
-      </c>
-      <c r="E610" t="n">
-        <v>240</v>
-      </c>
-      <c r="F610" s="2" t="n">
-        <v>45625.69964304192</v>
-      </c>
-      <c r="G610" t="n">
-        <v>394369.5633163138</v>
-      </c>
-      <c r="H610" t="n">
-        <v>59.56289731099464</v>
-      </c>
-      <c r="I610" t="n">
-        <v>4.100650373389866</v>
-      </c>
-      <c r="J610" t="n">
-        <v>3.339293544857794</v>
-      </c>
-      <c r="K610" t="n">
-        <v>0.1419279808787099</v>
-      </c>
-      <c r="L610" t="n">
-        <v>0.04794071105127667</v>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="n">
-        <v>2</v>
-      </c>
-      <c r="B611" s="2" t="n">
-        <v>45625.25</v>
-      </c>
-      <c r="C611" s="2" t="n">
-        <v>45625.75</v>
-      </c>
-      <c r="D611" t="inlineStr">
-        <is>
-          <t>CEN01_RP01_0107</t>
-        </is>
-      </c>
-      <c r="E611" t="n">
-        <v>240</v>
-      </c>
-      <c r="F611" s="2" t="n">
-        <v>45625.70453571869</v>
-      </c>
-      <c r="G611" t="n">
-        <v>394609.5633163138</v>
-      </c>
-      <c r="H611" t="n">
-        <v>59.56381035243827</v>
-      </c>
-      <c r="I611" t="n">
-        <v>4.09945964986643</v>
-      </c>
-      <c r="J611" t="n">
-        <v>3.339452949076752</v>
-      </c>
-      <c r="K611" t="n">
-        <v>0.1419774442632895</v>
-      </c>
-      <c r="L611" t="n">
-        <v>0.04793068207321784</v>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="n">
-        <v>2</v>
-      </c>
-      <c r="B612" s="2" t="n">
-        <v>45625.25</v>
-      </c>
-      <c r="C612" s="2" t="n">
-        <v>45625.75</v>
-      </c>
-      <c r="D612" t="inlineStr">
-        <is>
-          <t>CEN01_RP01_0107</t>
-        </is>
-      </c>
-      <c r="E612" t="n">
-        <v>240</v>
-      </c>
-      <c r="F612" s="2" t="n">
-        <v>45625.70942839546</v>
-      </c>
-      <c r="G612" t="n">
-        <v>394849.5633163138</v>
-      </c>
-      <c r="H612" t="n">
-        <v>59.56472228394046</v>
-      </c>
-      <c r="I612" t="n">
-        <v>4.098270373849449</v>
-      </c>
-      <c r="J612" t="n">
-        <v>3.339612159515516</v>
-      </c>
-      <c r="K612" t="n">
-        <v>0.1420268475175643</v>
-      </c>
-      <c r="L612" t="n">
-        <v>0.04792066528691484</v>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="n">
-        <v>2</v>
-      </c>
-      <c r="B613" s="2" t="n">
-        <v>45625.25</v>
-      </c>
-      <c r="C613" s="2" t="n">
-        <v>45625.75</v>
-      </c>
-      <c r="D613" t="inlineStr">
-        <is>
-          <t>CEN01_RP01_0107</t>
-        </is>
-      </c>
-      <c r="E613" t="n">
-        <v>240</v>
-      </c>
-      <c r="F613" s="2" t="n">
-        <v>45625.71432107224</v>
-      </c>
-      <c r="G613" t="n">
-        <v>395089.5633163138</v>
-      </c>
-      <c r="H613" t="n">
-        <v>59.56563310752394</v>
-      </c>
-      <c r="I613" t="n">
-        <v>4.097082542701026</v>
-      </c>
-      <c r="J613" t="n">
-        <v>3.339771176527226</v>
-      </c>
-      <c r="K613" t="n">
-        <v>0.1420761907511141</v>
-      </c>
-      <c r="L613" t="n">
-        <v>0.04791066067014976</v>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="n">
-        <v>2</v>
-      </c>
-      <c r="B614" s="2" t="n">
-        <v>45625.25</v>
-      </c>
-      <c r="C614" s="2" t="n">
-        <v>45625.75</v>
-      </c>
-      <c r="D614" t="inlineStr">
-        <is>
-          <t>CEN01_RP01_0107</t>
-        </is>
-      </c>
-      <c r="E614" t="n">
-        <v>240</v>
-      </c>
-      <c r="F614" s="2" t="n">
-        <v>45625.71921374901</v>
-      </c>
-      <c r="G614" t="n">
-        <v>395329.5633163138</v>
-      </c>
-      <c r="H614" t="n">
-        <v>59.56654282520651</v>
-      </c>
-      <c r="I614" t="n">
-        <v>4.095896153789673</v>
-      </c>
-      <c r="J614" t="n">
-        <v>3.339930000464162</v>
-      </c>
-      <c r="K614" t="n">
-        <v>0.1421254740732524</v>
-      </c>
-      <c r="L614" t="n">
-        <v>0.04790066820075867</v>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="n">
-        <v>2</v>
-      </c>
-      <c r="B615" s="2" t="n">
-        <v>45625.25</v>
-      </c>
-      <c r="C615" s="2" t="n">
-        <v>45625.75</v>
-      </c>
-      <c r="D615" t="inlineStr">
-        <is>
-          <t>CEN01_RP01_0107</t>
-        </is>
-      </c>
-      <c r="E615" t="n">
-        <v>240</v>
-      </c>
-      <c r="F615" s="2" t="n">
-        <v>45625.72410642578</v>
-      </c>
-      <c r="G615" t="n">
-        <v>395569.5633163138</v>
-      </c>
-      <c r="H615" t="n">
-        <v>59.5674514390011</v>
-      </c>
-      <c r="I615" t="n">
-        <v>4.094711204490289</v>
-      </c>
-      <c r="J615" t="n">
-        <v>3.340088631677753</v>
-      </c>
-      <c r="K615" t="n">
-        <v>0.1421746975930277</v>
-      </c>
-      <c r="L615" t="n">
-        <v>0.04789068785663136</v>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="n">
-        <v>2</v>
-      </c>
-      <c r="B616" s="2" t="n">
-        <v>45625.25</v>
-      </c>
-      <c r="C616" s="2" t="n">
-        <v>45625.75</v>
-      </c>
-      <c r="D616" t="inlineStr">
-        <is>
-          <t>CEN01_RP01_0107</t>
-        </is>
-      </c>
-      <c r="E616" t="n">
-        <v>240</v>
-      </c>
-      <c r="F616" s="2" t="n">
-        <v>45625.72899910255</v>
-      </c>
-      <c r="G616" t="n">
-        <v>395809.5633163138</v>
-      </c>
-      <c r="H616" t="n">
-        <v>59.56835895091574</v>
-      </c>
-      <c r="I616" t="n">
-        <v>4.093527692184137</v>
-      </c>
-      <c r="J616" t="n">
-        <v>3.340247070518573</v>
-      </c>
-      <c r="K616" t="n">
-        <v>0.1422238614192239</v>
-      </c>
-      <c r="L616" t="n">
-        <v>0.04788071961571133</v>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="n">
-        <v>2</v>
-      </c>
-      <c r="B617" s="2" t="n">
-        <v>45625.25</v>
-      </c>
-      <c r="C617" s="2" t="n">
-        <v>45625.75</v>
-      </c>
-      <c r="D617" t="inlineStr">
-        <is>
-          <t>CEN01_RP01_0107</t>
-        </is>
-      </c>
-      <c r="E617" t="n">
-        <v>240</v>
-      </c>
-      <c r="F617" s="2" t="n">
-        <v>45625.73389177932</v>
-      </c>
-      <c r="G617" t="n">
-        <v>396049.5633163138</v>
-      </c>
-      <c r="H617" t="n">
-        <v>59.5692653629536</v>
-      </c>
-      <c r="I617" t="n">
-        <v>4.092345614258829</v>
-      </c>
-      <c r="J617" t="n">
-        <v>3.340405317336347</v>
-      </c>
-      <c r="K617" t="n">
-        <v>0.1422729656603612</v>
-      </c>
-      <c r="L617" t="n">
-        <v>0.04787076345599547</v>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="n">
-        <v>2</v>
-      </c>
-      <c r="B618" s="2" t="n">
-        <v>45625.25</v>
-      </c>
-      <c r="C618" s="2" t="n">
-        <v>45625.75</v>
-      </c>
-      <c r="D618" t="inlineStr">
-        <is>
-          <t>CEN01_RP01_0107</t>
-        </is>
-      </c>
-      <c r="E618" t="n">
-        <v>240</v>
-      </c>
-      <c r="F618" s="2" t="n">
-        <v>45625.73878445609</v>
-      </c>
-      <c r="G618" t="n">
-        <v>396289.5633163138</v>
-      </c>
-      <c r="H618" t="n">
-        <v>59.57017067711299</v>
-      </c>
-      <c r="I618" t="n">
-        <v>4.091164968108306</v>
-      </c>
-      <c r="J618" t="n">
-        <v>3.340563372479952</v>
-      </c>
-      <c r="K618" t="n">
-        <v>0.1423220104246968</v>
-      </c>
-      <c r="L618" t="n">
-        <v>0.04786081935553403</v>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="n">
-        <v>2</v>
-      </c>
-      <c r="B619" s="2" t="n">
-        <v>45625.25</v>
-      </c>
-      <c r="C619" s="2" t="n">
-        <v>45625.75</v>
-      </c>
-      <c r="D619" t="inlineStr">
-        <is>
-          <t>CEN01_RP01_0107</t>
-        </is>
-      </c>
-      <c r="E619" t="n">
-        <v>240</v>
-      </c>
-      <c r="F619" s="2" t="n">
-        <v>45625.74367713286</v>
-      </c>
-      <c r="G619" t="n">
-        <v>396529.5633163138</v>
-      </c>
-      <c r="H619" t="n">
-        <v>59.5710748953874</v>
-      </c>
-      <c r="I619" t="n">
-        <v>4.089985751132817</v>
-      </c>
-      <c r="J619" t="n">
-        <v>3.340721236297421</v>
-      </c>
-      <c r="K619" t="n">
-        <v>0.1423709958202261</v>
-      </c>
-      <c r="L619" t="n">
-        <v>0.04785088729243037</v>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="n">
-        <v>2</v>
-      </c>
-      <c r="B620" s="2" t="n">
-        <v>45625.25</v>
-      </c>
-      <c r="C620" s="2" t="n">
-        <v>45625.75</v>
-      </c>
-      <c r="D620" t="inlineStr">
-        <is>
-          <t>CEN01_RP01_0107</t>
-        </is>
-      </c>
-      <c r="E620" t="n">
-        <v>240</v>
-      </c>
-      <c r="F620" s="2" t="n">
-        <v>45625.74856980963</v>
-      </c>
-      <c r="G620" t="n">
-        <v>396769.5633163138</v>
-      </c>
-      <c r="H620" t="n">
-        <v>59.57197801976546</v>
-      </c>
-      <c r="I620" t="n">
-        <v>4.088807960738902</v>
-      </c>
-      <c r="J620" t="n">
-        <v>3.340878909135947</v>
-      </c>
-      <c r="K620" t="n">
-        <v>0.1424199219546828</v>
-      </c>
-      <c r="L620" t="n">
         <v>0.04784096724484081</v>
       </c>
     </row>

--- a/blendmaster_backend_OOP/output/build_report_2024-11-28_06-00.xlsx
+++ b/blendmaster_backend_OOP/output/build_report_2024-11-28_06-00.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L608"/>
+  <dimension ref="A1:L607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20586,32 +20586,32 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E504" t="n">
-        <v>171.5431458111511</v>
+        <v>240</v>
       </c>
       <c r="F504" s="2" t="n">
-        <v>45625.56427019872</v>
+        <v>45625.56376538513</v>
       </c>
       <c r="G504" t="n">
-        <v>445744.7353634185</v>
+        <v>372370.9866868142</v>
       </c>
       <c r="H504" t="n">
-        <v>60.88547961380101</v>
+        <v>59.52524598312571</v>
       </c>
       <c r="I504" t="n">
-        <v>3.876761165120385</v>
+        <v>4.135327298523092</v>
       </c>
       <c r="J504" t="n">
-        <v>2.516358845756266</v>
+        <v>3.32028289040059</v>
       </c>
       <c r="K504" t="n">
-        <v>0.114023005291366</v>
+        <v>0.1407428129768286</v>
       </c>
       <c r="L504" t="n">
-        <v>0.041376618923828</v>
+        <v>0.04837176857847136</v>
       </c>
     </row>
     <row r="505">
@@ -20633,25 +20633,25 @@
         <v>240</v>
       </c>
       <c r="F505" s="2" t="n">
-        <v>45625.56376538513</v>
+        <v>45625.25234285779</v>
       </c>
       <c r="G505" t="n">
-        <v>372370.9866868142</v>
+        <v>372610.9866868142</v>
       </c>
       <c r="H505" t="n">
-        <v>59.52524598312571</v>
+        <v>59.52598767269989</v>
       </c>
       <c r="I505" t="n">
-        <v>4.135327298523092</v>
+        <v>4.13477551685537</v>
       </c>
       <c r="J505" t="n">
-        <v>3.32028289040059</v>
+        <v>3.320874886541835</v>
       </c>
       <c r="K505" t="n">
-        <v>0.1407428129768286</v>
+        <v>0.140740873701981</v>
       </c>
       <c r="L505" t="n">
-        <v>0.04837176857847136</v>
+        <v>0.04836762327810713</v>
       </c>
     </row>
     <row r="506">
@@ -20673,25 +20673,25 @@
         <v>240</v>
       </c>
       <c r="F506" s="2" t="n">
-        <v>45625.25234285779</v>
+        <v>45625.25723553456</v>
       </c>
       <c r="G506" t="n">
-        <v>372610.9866868142</v>
+        <v>372850.9866868142</v>
       </c>
       <c r="H506" t="n">
-        <v>59.52598767269989</v>
+        <v>59.52672840743954</v>
       </c>
       <c r="I506" t="n">
-        <v>4.13477551685537</v>
+        <v>4.134224445538995</v>
       </c>
       <c r="J506" t="n">
-        <v>3.320874886541835</v>
+        <v>3.321466120560521</v>
       </c>
       <c r="K506" t="n">
-        <v>0.140740873701981</v>
+        <v>0.1407389369237123</v>
       </c>
       <c r="L506" t="n">
-        <v>0.04836762327810713</v>
+        <v>0.04836348331430963</v>
       </c>
     </row>
     <row r="507">
@@ -20713,25 +20713,25 @@
         <v>240</v>
       </c>
       <c r="F507" s="2" t="n">
-        <v>45625.25723553456</v>
+        <v>45625.26212821133</v>
       </c>
       <c r="G507" t="n">
-        <v>372850.9866868142</v>
+        <v>373090.9866868142</v>
       </c>
       <c r="H507" t="n">
-        <v>59.52672840743954</v>
+        <v>59.52746818918732</v>
       </c>
       <c r="I507" t="n">
-        <v>4.134224445538995</v>
+        <v>4.133674083203113</v>
       </c>
       <c r="J507" t="n">
-        <v>3.321466120560521</v>
+        <v>3.322056593927412</v>
       </c>
       <c r="K507" t="n">
-        <v>0.1407389369237123</v>
+        <v>0.1407370026372046</v>
       </c>
       <c r="L507" t="n">
-        <v>0.04836348331430963</v>
+        <v>0.04835934867678023</v>
       </c>
     </row>
     <row r="508">
@@ -20753,25 +20753,25 @@
         <v>240</v>
       </c>
       <c r="F508" s="2" t="n">
-        <v>45625.26212821133</v>
+        <v>45625.2670208881</v>
       </c>
       <c r="G508" t="n">
-        <v>373090.9866868142</v>
+        <v>373330.9866868142</v>
       </c>
       <c r="H508" t="n">
-        <v>59.52746818918732</v>
+        <v>59.52820701978117</v>
       </c>
       <c r="I508" t="n">
-        <v>4.133674083203113</v>
+        <v>4.133124428480397</v>
       </c>
       <c r="J508" t="n">
-        <v>3.322056593927412</v>
+        <v>3.322646308109488</v>
       </c>
       <c r="K508" t="n">
-        <v>0.1407370026372046</v>
+        <v>0.1407350708376523</v>
       </c>
       <c r="L508" t="n">
-        <v>0.04835934867678023</v>
+        <v>0.04835521935524679</v>
       </c>
     </row>
     <row r="509">
@@ -20793,25 +20793,25 @@
         <v>240</v>
       </c>
       <c r="F509" s="2" t="n">
-        <v>45625.2670208881</v>
+        <v>45625.27191356487</v>
       </c>
       <c r="G509" t="n">
-        <v>373330.9866868142</v>
+        <v>373570.9866868142</v>
       </c>
       <c r="H509" t="n">
-        <v>59.52820701978117</v>
+        <v>59.52894490105428</v>
       </c>
       <c r="I509" t="n">
-        <v>4.133124428480397</v>
+        <v>4.132575480007032</v>
       </c>
       <c r="J509" t="n">
-        <v>3.322646308109488</v>
+        <v>3.323235264569959</v>
       </c>
       <c r="K509" t="n">
-        <v>0.1407350708376523</v>
+        <v>0.1407331415202623</v>
       </c>
       <c r="L509" t="n">
-        <v>0.04835521935524679</v>
+        <v>0.04835109533946354</v>
       </c>
     </row>
     <row r="510">
@@ -20833,25 +20833,25 @@
         <v>240</v>
       </c>
       <c r="F510" s="2" t="n">
-        <v>45625.27191356487</v>
+        <v>45625.27680624164</v>
       </c>
       <c r="G510" t="n">
-        <v>373570.9866868142</v>
+        <v>373810.9866868142</v>
       </c>
       <c r="H510" t="n">
-        <v>59.52894490105428</v>
+        <v>59.52968183483515</v>
       </c>
       <c r="I510" t="n">
-        <v>4.132575480007032</v>
+        <v>4.132027236422705</v>
       </c>
       <c r="J510" t="n">
-        <v>3.323235264569959</v>
+        <v>3.323823464768279</v>
       </c>
       <c r="K510" t="n">
-        <v>0.1407331415202623</v>
+        <v>0.1407312146802535</v>
       </c>
       <c r="L510" t="n">
-        <v>0.04835109533946354</v>
+        <v>0.04834697661921106</v>
       </c>
     </row>
     <row r="511">
@@ -20873,25 +20873,25 @@
         <v>240</v>
       </c>
       <c r="F511" s="2" t="n">
-        <v>45625.27680624164</v>
+        <v>45625.28169891841</v>
       </c>
       <c r="G511" t="n">
-        <v>373810.9866868142</v>
+        <v>374050.9866868142</v>
       </c>
       <c r="H511" t="n">
-        <v>59.52968183483515</v>
+        <v>59.53041782294756</v>
       </c>
       <c r="I511" t="n">
-        <v>4.132027236422705</v>
+        <v>4.131479696370597</v>
       </c>
       <c r="J511" t="n">
-        <v>3.323823464768279</v>
+        <v>3.324410910160155</v>
       </c>
       <c r="K511" t="n">
-        <v>0.1407312146802535</v>
+        <v>0.1407292903128574</v>
       </c>
       <c r="L511" t="n">
-        <v>0.04834697661921106</v>
+        <v>0.0483428631842961</v>
       </c>
     </row>
     <row r="512">
@@ -20913,25 +20913,25 @@
         <v>240</v>
       </c>
       <c r="F512" s="2" t="n">
-        <v>45625.28169891841</v>
+        <v>45625.28659159518</v>
       </c>
       <c r="G512" t="n">
-        <v>374050.9866868142</v>
+        <v>374290.9866868142</v>
       </c>
       <c r="H512" t="n">
-        <v>59.53041782294756</v>
+        <v>59.53115286721066</v>
       </c>
       <c r="I512" t="n">
-        <v>4.131479696370597</v>
+        <v>4.130932858497367</v>
       </c>
       <c r="J512" t="n">
-        <v>3.324410910160155</v>
+        <v>3.32499760219756</v>
       </c>
       <c r="K512" t="n">
-        <v>0.1407292903128574</v>
+        <v>0.1407273684133175</v>
       </c>
       <c r="L512" t="n">
-        <v>0.0483428631842961</v>
+        <v>0.04833875502455161</v>
       </c>
     </row>
     <row r="513">
@@ -20953,25 +20953,25 @@
         <v>240</v>
       </c>
       <c r="F513" s="2" t="n">
-        <v>45625.28659159518</v>
+        <v>45625.29148427195</v>
       </c>
       <c r="G513" t="n">
-        <v>374290.9866868142</v>
+        <v>374530.9866868142</v>
       </c>
       <c r="H513" t="n">
-        <v>59.53115286721066</v>
+        <v>59.53188696943889</v>
       </c>
       <c r="I513" t="n">
-        <v>4.130932858497367</v>
+        <v>4.130386721453143</v>
       </c>
       <c r="J513" t="n">
-        <v>3.32499760219756</v>
+        <v>3.325583542328746</v>
       </c>
       <c r="K513" t="n">
-        <v>0.1407273684133175</v>
+        <v>0.1407254489768897</v>
       </c>
       <c r="L513" t="n">
-        <v>0.04833875502455161</v>
+        <v>0.04833465212983658</v>
       </c>
     </row>
     <row r="514">
@@ -20993,25 +20993,25 @@
         <v>240</v>
       </c>
       <c r="F514" s="2" t="n">
-        <v>45625.29148427195</v>
+        <v>45625.29637694873</v>
       </c>
       <c r="G514" t="n">
-        <v>374530.9866868142</v>
+        <v>374770.9866868142</v>
       </c>
       <c r="H514" t="n">
-        <v>59.53188696943889</v>
+        <v>59.53262013144207</v>
       </c>
       <c r="I514" t="n">
-        <v>4.130386721453143</v>
+        <v>4.129841283891511</v>
       </c>
       <c r="J514" t="n">
-        <v>3.325583542328746</v>
+        <v>3.326168731998256</v>
       </c>
       <c r="K514" t="n">
-        <v>0.1407254489768897</v>
+        <v>0.1407235319988418</v>
       </c>
       <c r="L514" t="n">
-        <v>0.04833465212983658</v>
+        <v>0.04833055449003598</v>
       </c>
     </row>
     <row r="515">
@@ -21033,25 +21033,25 @@
         <v>240</v>
       </c>
       <c r="F515" s="2" t="n">
-        <v>45625.29637694873</v>
+        <v>45625.3012696255</v>
       </c>
       <c r="G515" t="n">
-        <v>374770.9866868142</v>
+        <v>375010.9866868142</v>
       </c>
       <c r="H515" t="n">
-        <v>59.53262013144207</v>
+        <v>59.53335235502539</v>
       </c>
       <c r="I515" t="n">
-        <v>4.129841283891511</v>
+        <v>4.129296544469504</v>
       </c>
       <c r="J515" t="n">
-        <v>3.326168731998256</v>
+        <v>3.326753172646934</v>
       </c>
       <c r="K515" t="n">
-        <v>0.1407235319988418</v>
+        <v>0.1407216174744539</v>
       </c>
       <c r="L515" t="n">
-        <v>0.04833055449003598</v>
+        <v>0.04832646209506066</v>
       </c>
     </row>
     <row r="516">
@@ -21073,25 +21073,25 @@
         <v>240</v>
       </c>
       <c r="F516" s="2" t="n">
-        <v>45625.3012696255</v>
+        <v>45625.30616230227</v>
       </c>
       <c r="G516" t="n">
-        <v>375010.9866868142</v>
+        <v>375250.9866868142</v>
       </c>
       <c r="H516" t="n">
-        <v>59.53335235502539</v>
+        <v>59.53408364198939</v>
       </c>
       <c r="I516" t="n">
-        <v>4.129296544469504</v>
+        <v>4.128752501847591</v>
       </c>
       <c r="J516" t="n">
-        <v>3.326753172646934</v>
+        <v>3.327336865711938</v>
       </c>
       <c r="K516" t="n">
-        <v>0.1407216174744539</v>
+        <v>0.1407197053990182</v>
       </c>
       <c r="L516" t="n">
-        <v>0.04832646209506066</v>
+        <v>0.04832237493484729</v>
       </c>
     </row>
     <row r="517">
@@ -21113,25 +21113,25 @@
         <v>240</v>
       </c>
       <c r="F517" s="2" t="n">
-        <v>45625.30616230227</v>
+        <v>45625.31105497904</v>
       </c>
       <c r="G517" t="n">
-        <v>375250.9866868142</v>
+        <v>375490.9866868142</v>
       </c>
       <c r="H517" t="n">
-        <v>59.53408364198939</v>
+        <v>59.53481399413004</v>
       </c>
       <c r="I517" t="n">
-        <v>4.128752501847591</v>
+        <v>4.128209154689664</v>
       </c>
       <c r="J517" t="n">
-        <v>3.327336865711938</v>
+        <v>3.327919812626751</v>
       </c>
       <c r="K517" t="n">
-        <v>0.1407197053990182</v>
+        <v>0.1407177957678388</v>
       </c>
       <c r="L517" t="n">
-        <v>0.04832237493484729</v>
+        <v>0.04831829299935827</v>
       </c>
     </row>
     <row r="518">
@@ -21153,25 +21153,25 @@
         <v>240</v>
       </c>
       <c r="F518" s="2" t="n">
-        <v>45625.31105497904</v>
+        <v>45625.31594765581</v>
       </c>
       <c r="G518" t="n">
-        <v>375490.9866868142</v>
+        <v>375730.9866868142</v>
       </c>
       <c r="H518" t="n">
-        <v>59.53481399413004</v>
+        <v>59.53554341323871</v>
       </c>
       <c r="I518" t="n">
-        <v>4.128209154689664</v>
+        <v>4.127666501663031</v>
       </c>
       <c r="J518" t="n">
-        <v>3.327919812626751</v>
+        <v>3.328502014821195</v>
       </c>
       <c r="K518" t="n">
-        <v>0.1407177957678388</v>
+        <v>0.1407158885762319</v>
       </c>
       <c r="L518" t="n">
-        <v>0.04831829299935827</v>
+        <v>0.04831421627858165</v>
       </c>
     </row>
     <row r="519">
@@ -21193,25 +21193,25 @@
         <v>240</v>
       </c>
       <c r="F519" s="2" t="n">
-        <v>45625.31594765581</v>
+        <v>45625.32084033258</v>
       </c>
       <c r="G519" t="n">
-        <v>375730.9866868142</v>
+        <v>375970.9866868142</v>
       </c>
       <c r="H519" t="n">
-        <v>59.53554341323871</v>
+        <v>59.53627190110219</v>
       </c>
       <c r="I519" t="n">
-        <v>4.127666501663031</v>
+        <v>4.127124541438401</v>
       </c>
       <c r="J519" t="n">
-        <v>3.328502014821195</v>
+        <v>3.32908347372144</v>
       </c>
       <c r="K519" t="n">
-        <v>0.1407158885762319</v>
+        <v>0.1407139838195255</v>
       </c>
       <c r="L519" t="n">
-        <v>0.04831421627858165</v>
+        <v>0.04831014476253104</v>
       </c>
     </row>
     <row r="520">
@@ -21233,25 +21233,25 @@
         <v>240</v>
       </c>
       <c r="F520" s="2" t="n">
-        <v>45625.32084033258</v>
+        <v>45625.32573300935</v>
       </c>
       <c r="G520" t="n">
-        <v>375970.9866868142</v>
+        <v>376210.9866868142</v>
       </c>
       <c r="H520" t="n">
-        <v>59.53627190110219</v>
+        <v>59.53699945950272</v>
       </c>
       <c r="I520" t="n">
-        <v>4.127124541438401</v>
+        <v>4.126583272689877</v>
       </c>
       <c r="J520" t="n">
-        <v>3.32908347372144</v>
+        <v>3.329664190750017</v>
       </c>
       <c r="K520" t="n">
-        <v>0.1407139838195255</v>
+        <v>0.1407120814930597</v>
       </c>
       <c r="L520" t="n">
-        <v>0.04831014476253104</v>
+        <v>0.04830607844124554</v>
       </c>
     </row>
     <row r="521">
@@ -21273,25 +21273,25 @@
         <v>240</v>
       </c>
       <c r="F521" s="2" t="n">
-        <v>45625.32573300935</v>
+        <v>45625.33062568613</v>
       </c>
       <c r="G521" t="n">
-        <v>376210.9866868142</v>
+        <v>376450.9866868142</v>
       </c>
       <c r="H521" t="n">
-        <v>59.53699945950272</v>
+        <v>59.53772609021799</v>
       </c>
       <c r="I521" t="n">
-        <v>4.126583272689877</v>
+        <v>4.126042694094941</v>
       </c>
       <c r="J521" t="n">
-        <v>3.329664190750017</v>
+        <v>3.330244167325831</v>
       </c>
       <c r="K521" t="n">
-        <v>0.1407120814930597</v>
+        <v>0.1407101815921865</v>
       </c>
       <c r="L521" t="n">
-        <v>0.04830607844124554</v>
+        <v>0.04830201730478962</v>
       </c>
     </row>
     <row r="522">
@@ -21313,25 +21313,25 @@
         <v>240</v>
       </c>
       <c r="F522" s="2" t="n">
-        <v>45625.33062568613</v>
+        <v>45625.3355183629</v>
       </c>
       <c r="G522" t="n">
-        <v>376450.9866868142</v>
+        <v>376690.9866868142</v>
       </c>
       <c r="H522" t="n">
-        <v>59.53772609021799</v>
+        <v>59.53845179502115</v>
       </c>
       <c r="I522" t="n">
-        <v>4.126042694094941</v>
+        <v>4.125502804334446</v>
       </c>
       <c r="J522" t="n">
-        <v>3.330244167325831</v>
+        <v>3.330823404864167</v>
       </c>
       <c r="K522" t="n">
-        <v>0.1407101815921865</v>
+        <v>0.1407082841122695</v>
       </c>
       <c r="L522" t="n">
-        <v>0.04830201730478962</v>
+        <v>0.04829796134325312</v>
       </c>
     </row>
     <row r="523">
@@ -21353,25 +21353,25 @@
         <v>240</v>
       </c>
       <c r="F523" s="2" t="n">
-        <v>45625.3355183629</v>
+        <v>45625.34041103967</v>
       </c>
       <c r="G523" t="n">
-        <v>376690.9866868142</v>
+        <v>376930.9866868142</v>
       </c>
       <c r="H523" t="n">
-        <v>59.53845179502115</v>
+        <v>59.53917657568086</v>
       </c>
       <c r="I523" t="n">
-        <v>4.125502804334446</v>
+        <v>4.124963602092607</v>
       </c>
       <c r="J523" t="n">
-        <v>3.330823404864167</v>
+        <v>3.331401904776709</v>
       </c>
       <c r="K523" t="n">
-        <v>0.1407082841122695</v>
+        <v>0.1407063890486845</v>
       </c>
       <c r="L523" t="n">
-        <v>0.04829796134325312</v>
+        <v>0.04829391054675108</v>
       </c>
     </row>
     <row r="524">
@@ -21390,28 +21390,28 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>240</v>
+        <v>166.2199859162001</v>
       </c>
       <c r="F524" s="2" t="n">
-        <v>45625.34041103967</v>
+        <v>45625.34530371644</v>
       </c>
       <c r="G524" t="n">
-        <v>376930.9866868142</v>
+        <v>377097.2066727304</v>
       </c>
       <c r="H524" t="n">
-        <v>59.53917657568086</v>
+        <v>59.53967800590596</v>
       </c>
       <c r="I524" t="n">
-        <v>4.124963602092607</v>
+        <v>4.124590561921236</v>
       </c>
       <c r="J524" t="n">
-        <v>3.331401904776709</v>
+        <v>3.331802132538701</v>
       </c>
       <c r="K524" t="n">
-        <v>0.1407063890486845</v>
+        <v>0.1407050779731925</v>
       </c>
       <c r="L524" t="n">
-        <v>0.04829391054675108</v>
+        <v>0.04829110805502524</v>
       </c>
     </row>
     <row r="525">
@@ -21430,28 +21430,28 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>166.2199859162001</v>
+        <v>240</v>
       </c>
       <c r="F525" s="2" t="n">
-        <v>45625.34530371644</v>
+        <v>45625.42051092322</v>
       </c>
       <c r="G525" t="n">
-        <v>377097.2066727304</v>
+        <v>377337.2066727304</v>
       </c>
       <c r="H525" t="n">
-        <v>59.53967800590596</v>
+        <v>59.53922109426733</v>
       </c>
       <c r="I525" t="n">
-        <v>4.124590561921236</v>
+        <v>4.123987583018447</v>
       </c>
       <c r="J525" t="n">
-        <v>3.331802132538701</v>
+        <v>3.332695649006806</v>
       </c>
       <c r="K525" t="n">
-        <v>0.1407050779731925</v>
+        <v>0.1407423890600333</v>
       </c>
       <c r="L525" t="n">
-        <v>0.04829110805502524</v>
+        <v>0.04829592595804314</v>
       </c>
     </row>
     <row r="526">
@@ -21473,25 +21473,25 @@
         <v>240</v>
       </c>
       <c r="F526" s="2" t="n">
-        <v>45625.42051092322</v>
+        <v>45625.42540359999</v>
       </c>
       <c r="G526" t="n">
-        <v>377337.2066727304</v>
+        <v>377577.2066727304</v>
       </c>
       <c r="H526" t="n">
-        <v>59.53922109426733</v>
+        <v>59.53876476348364</v>
       </c>
       <c r="I526" t="n">
-        <v>4.123987583018447</v>
+        <v>4.123385370660535</v>
       </c>
       <c r="J526" t="n">
-        <v>3.332695649006806</v>
+        <v>3.333588029580326</v>
       </c>
       <c r="K526" t="n">
-        <v>0.1407423890600333</v>
+        <v>0.1407796527146632</v>
       </c>
       <c r="L526" t="n">
-        <v>0.04829592595804314</v>
+        <v>0.04830073773623833</v>
       </c>
     </row>
     <row r="527">
@@ -21513,25 +21513,25 @@
         <v>240</v>
       </c>
       <c r="F527" s="2" t="n">
-        <v>45625.42540359999</v>
+        <v>45625.43029627676</v>
       </c>
       <c r="G527" t="n">
-        <v>377577.2066727304</v>
+        <v>377817.2066727304</v>
       </c>
       <c r="H527" t="n">
-        <v>59.53876476348364</v>
+        <v>59.53830901244797</v>
       </c>
       <c r="I527" t="n">
-        <v>4.123385370660535</v>
+        <v>4.122783923386707</v>
       </c>
       <c r="J527" t="n">
-        <v>3.333588029580326</v>
+        <v>3.334479276423915</v>
       </c>
       <c r="K527" t="n">
-        <v>0.1407796527146632</v>
+        <v>0.1408168690274731</v>
       </c>
       <c r="L527" t="n">
-        <v>0.04830073773623833</v>
+        <v>0.04830554340128279</v>
       </c>
     </row>
     <row r="528">
@@ -21553,25 +21553,25 @@
         <v>240</v>
       </c>
       <c r="F528" s="2" t="n">
-        <v>45625.43029627676</v>
+        <v>45625.43518895353</v>
       </c>
       <c r="G528" t="n">
-        <v>377817.2066727304</v>
+        <v>378057.2066727304</v>
       </c>
       <c r="H528" t="n">
-        <v>59.53830901244797</v>
+        <v>59.53785384005619</v>
       </c>
       <c r="I528" t="n">
-        <v>4.122783923386707</v>
+        <v>4.122183239739881</v>
       </c>
       <c r="J528" t="n">
-        <v>3.334479276423915</v>
+        <v>3.335369391696733</v>
       </c>
       <c r="K528" t="n">
-        <v>0.1408168690274731</v>
+        <v>0.1408540380886241</v>
       </c>
       <c r="L528" t="n">
-        <v>0.04830554340128279</v>
+        <v>0.04831034296481886</v>
       </c>
     </row>
     <row r="529">
@@ -21593,25 +21593,25 @@
         <v>240</v>
       </c>
       <c r="F529" s="2" t="n">
-        <v>45625.43518895353</v>
+        <v>45625.4400816303</v>
       </c>
       <c r="G529" t="n">
-        <v>378057.2066727304</v>
+        <v>378297.2066727304</v>
       </c>
       <c r="H529" t="n">
-        <v>59.53785384005619</v>
+        <v>59.53739924520701</v>
       </c>
       <c r="I529" t="n">
-        <v>4.122183239739881</v>
+        <v>4.121583318266673</v>
       </c>
       <c r="J529" t="n">
-        <v>3.335369391696733</v>
+        <v>3.336258377552459</v>
       </c>
       <c r="K529" t="n">
-        <v>0.1408540380886241</v>
+        <v>0.1408911599880488</v>
       </c>
       <c r="L529" t="n">
-        <v>0.04831034296481886</v>
+        <v>0.04831513643845931</v>
       </c>
     </row>
     <row r="530">
@@ -21633,25 +21633,25 @@
         <v>240</v>
       </c>
       <c r="F530" s="2" t="n">
-        <v>45625.4400816303</v>
+        <v>45625.44497430707</v>
       </c>
       <c r="G530" t="n">
-        <v>378297.2066727304</v>
+        <v>378537.2066727304</v>
       </c>
       <c r="H530" t="n">
-        <v>59.53739924520701</v>
+        <v>59.5369452268019</v>
       </c>
       <c r="I530" t="n">
-        <v>4.121583318266673</v>
+        <v>4.120984157517383</v>
       </c>
       <c r="J530" t="n">
-        <v>3.336258377552459</v>
+        <v>3.337146236139312</v>
       </c>
       <c r="K530" t="n">
-        <v>0.1408911599880488</v>
+        <v>0.1409282348154514</v>
       </c>
       <c r="L530" t="n">
-        <v>0.04831513643845931</v>
+        <v>0.0483199238337875</v>
       </c>
     </row>
     <row r="531">
@@ -21673,25 +21673,25 @@
         <v>240</v>
       </c>
       <c r="F531" s="2" t="n">
-        <v>45625.44497430707</v>
+        <v>45625.44986698384</v>
       </c>
       <c r="G531" t="n">
-        <v>378537.2066727304</v>
+        <v>378777.2066727304</v>
       </c>
       <c r="H531" t="n">
-        <v>59.5369452268019</v>
+        <v>59.53649178374511</v>
       </c>
       <c r="I531" t="n">
-        <v>4.120984157517383</v>
+        <v>4.120385756045987</v>
       </c>
       <c r="J531" t="n">
-        <v>3.337146236139312</v>
+        <v>3.338032969600063</v>
       </c>
       <c r="K531" t="n">
-        <v>0.1409282348154514</v>
+        <v>0.1409652626603091</v>
       </c>
       <c r="L531" t="n">
-        <v>0.0483199238337875</v>
+        <v>0.04832470516235739</v>
       </c>
     </row>
     <row r="532">
@@ -21713,25 +21713,25 @@
         <v>240</v>
       </c>
       <c r="F532" s="2" t="n">
-        <v>45625.44986698384</v>
+        <v>45625.45475966061</v>
       </c>
       <c r="G532" t="n">
-        <v>378777.2066727304</v>
+        <v>379017.2066727304</v>
       </c>
       <c r="H532" t="n">
-        <v>59.53649178374511</v>
+        <v>59.53603891494371</v>
       </c>
       <c r="I532" t="n">
-        <v>4.120385756045987</v>
+        <v>4.119788112410123</v>
       </c>
       <c r="J532" t="n">
-        <v>3.338032969600063</v>
+        <v>3.33891858007206</v>
       </c>
       <c r="K532" t="n">
-        <v>0.1409652626603091</v>
+        <v>0.1410022436118721</v>
       </c>
       <c r="L532" t="n">
-        <v>0.04832470516235739</v>
+        <v>0.04832948043569373</v>
       </c>
     </row>
     <row r="533">
@@ -21753,25 +21753,25 @@
         <v>240</v>
       </c>
       <c r="F533" s="2" t="n">
-        <v>45625.45475966061</v>
+        <v>45625.45965233738</v>
       </c>
       <c r="G533" t="n">
-        <v>379017.2066727304</v>
+        <v>379257.2066727304</v>
       </c>
       <c r="H533" t="n">
-        <v>59.53603891494371</v>
+        <v>59.53558661930748</v>
       </c>
       <c r="I533" t="n">
-        <v>4.119788112410123</v>
+        <v>4.119191225171078</v>
       </c>
       <c r="J533" t="n">
-        <v>3.33891858007206</v>
+        <v>3.339803069687236</v>
       </c>
       <c r="K533" t="n">
-        <v>0.1410022436118721</v>
+        <v>0.1410391777591651</v>
       </c>
       <c r="L533" t="n">
-        <v>0.04832948043569373</v>
+        <v>0.04833424966529203</v>
       </c>
     </row>
     <row r="534">
@@ -21793,25 +21793,25 @@
         <v>240</v>
       </c>
       <c r="F534" s="2" t="n">
-        <v>45625.45965233738</v>
+        <v>45625.46454501415</v>
       </c>
       <c r="G534" t="n">
-        <v>379257.2066727304</v>
+        <v>379497.2066727304</v>
       </c>
       <c r="H534" t="n">
-        <v>59.53558661930748</v>
+        <v>59.53513489574899</v>
       </c>
       <c r="I534" t="n">
-        <v>4.119191225171078</v>
+        <v>4.118595092893782</v>
       </c>
       <c r="J534" t="n">
-        <v>3.339803069687236</v>
+        <v>3.340686440572135</v>
       </c>
       <c r="K534" t="n">
-        <v>0.1410391777591651</v>
+        <v>0.1410760651909871</v>
       </c>
       <c r="L534" t="n">
-        <v>0.04833424966529203</v>
+        <v>0.04833901286261877</v>
       </c>
     </row>
     <row r="535">
@@ -21833,25 +21833,25 @@
         <v>240</v>
       </c>
       <c r="F535" s="2" t="n">
-        <v>45625.46454501415</v>
+        <v>45625.46943769092</v>
       </c>
       <c r="G535" t="n">
-        <v>379497.2066727304</v>
+        <v>379737.2066727304</v>
       </c>
       <c r="H535" t="n">
-        <v>59.53513489574899</v>
+        <v>59.53468374318356</v>
       </c>
       <c r="I535" t="n">
-        <v>4.118595092893782</v>
+        <v>4.117999714146792</v>
       </c>
       <c r="J535" t="n">
-        <v>3.340686440572135</v>
+        <v>3.341568694847923</v>
       </c>
       <c r="K535" t="n">
-        <v>0.1410760651909871</v>
+        <v>0.1411129059959131</v>
       </c>
       <c r="L535" t="n">
-        <v>0.04833901286261877</v>
+        <v>0.04834377003911143</v>
       </c>
     </row>
     <row r="536">
@@ -21873,25 +21873,25 @@
         <v>240</v>
       </c>
       <c r="F536" s="2" t="n">
-        <v>45625.46943769092</v>
+        <v>45625.4743303677</v>
       </c>
       <c r="G536" t="n">
-        <v>379737.2066727304</v>
+        <v>379977.2066727304</v>
       </c>
       <c r="H536" t="n">
-        <v>59.53468374318356</v>
+        <v>59.53423316052923</v>
       </c>
       <c r="I536" t="n">
-        <v>4.117999714146792</v>
+        <v>4.117405087502278</v>
       </c>
       <c r="J536" t="n">
-        <v>3.341568694847923</v>
+        <v>3.342449834630407</v>
       </c>
       <c r="K536" t="n">
-        <v>0.1411129059959131</v>
+        <v>0.141149700262294</v>
       </c>
       <c r="L536" t="n">
-        <v>0.04834377003911143</v>
+        <v>0.04834852120617859</v>
       </c>
     </row>
     <row r="537">
@@ -21913,25 +21913,25 @@
         <v>240</v>
       </c>
       <c r="F537" s="2" t="n">
-        <v>45625.4743303677</v>
+        <v>45625.47922304447</v>
       </c>
       <c r="G537" t="n">
-        <v>379977.2066727304</v>
+        <v>380217.2066727304</v>
       </c>
       <c r="H537" t="n">
-        <v>59.53423316052923</v>
+        <v>59.53378314670681</v>
       </c>
       <c r="I537" t="n">
-        <v>4.117405087502278</v>
+        <v>4.116811211536021</v>
       </c>
       <c r="J537" t="n">
-        <v>3.342449834630407</v>
+        <v>3.343329862030053</v>
       </c>
       <c r="K537" t="n">
-        <v>0.141149700262294</v>
+        <v>0.1411864480782577</v>
       </c>
       <c r="L537" t="n">
-        <v>0.04834852120617859</v>
+        <v>0.04835326637520001</v>
       </c>
     </row>
     <row r="538">
@@ -21953,25 +21953,25 @@
         <v>240</v>
       </c>
       <c r="F538" s="2" t="n">
-        <v>45625.47922304447</v>
+        <v>45625.48411572124</v>
       </c>
       <c r="G538" t="n">
-        <v>380217.2066727304</v>
+        <v>380457.2066727304</v>
       </c>
       <c r="H538" t="n">
-        <v>59.53378314670681</v>
+        <v>59.53333370063979</v>
       </c>
       <c r="I538" t="n">
-        <v>4.116811211536021</v>
+        <v>4.11621808482739</v>
       </c>
       <c r="J538" t="n">
-        <v>3.343329862030053</v>
+        <v>3.344208779152</v>
       </c>
       <c r="K538" t="n">
-        <v>0.1411864480782577</v>
+        <v>0.1412231495317098</v>
       </c>
       <c r="L538" t="n">
-        <v>0.04835326637520001</v>
+        <v>0.04835800555752677</v>
       </c>
     </row>
     <row r="539">
@@ -21993,25 +21993,25 @@
         <v>240</v>
       </c>
       <c r="F539" s="2" t="n">
-        <v>45625.48411572124</v>
+        <v>45625.48900839801</v>
       </c>
       <c r="G539" t="n">
-        <v>380457.2066727304</v>
+        <v>380697.2066727304</v>
       </c>
       <c r="H539" t="n">
-        <v>59.53333370063979</v>
+        <v>59.53288482125438</v>
       </c>
       <c r="I539" t="n">
-        <v>4.11621808482739</v>
+        <v>4.11562570595934</v>
       </c>
       <c r="J539" t="n">
-        <v>3.344208779152</v>
+        <v>3.345086588096081</v>
       </c>
       <c r="K539" t="n">
-        <v>0.1412231495317098</v>
+        <v>0.1412598047103342</v>
       </c>
       <c r="L539" t="n">
-        <v>0.04835800555752677</v>
+        <v>0.0483627387644813</v>
       </c>
     </row>
     <row r="540">
@@ -22033,25 +22033,25 @@
         <v>240</v>
       </c>
       <c r="F540" s="2" t="n">
-        <v>45625.48900839801</v>
+        <v>45625.49390107478</v>
       </c>
       <c r="G540" t="n">
-        <v>380697.2066727304</v>
+        <v>380937.2066727304</v>
       </c>
       <c r="H540" t="n">
-        <v>59.53288482125438</v>
+        <v>59.53243650747955</v>
       </c>
       <c r="I540" t="n">
-        <v>4.11562570595934</v>
+        <v>4.115034073518395</v>
       </c>
       <c r="J540" t="n">
-        <v>3.345086588096081</v>
+        <v>3.345963290956833</v>
       </c>
       <c r="K540" t="n">
-        <v>0.1412598047103342</v>
+        <v>0.1412964137015938</v>
       </c>
       <c r="L540" t="n">
-        <v>0.0483627387644813</v>
+        <v>0.0483674660073575</v>
       </c>
     </row>
     <row r="541">
@@ -22073,25 +22073,25 @@
         <v>240</v>
       </c>
       <c r="F541" s="2" t="n">
-        <v>45625.49390107478</v>
+        <v>45625.49879375155</v>
       </c>
       <c r="G541" t="n">
-        <v>380937.2066727304</v>
+        <v>381177.2066727304</v>
       </c>
       <c r="H541" t="n">
-        <v>59.53243650747955</v>
+        <v>59.53198875824688</v>
       </c>
       <c r="I541" t="n">
-        <v>4.115034073518395</v>
+        <v>4.114443186094642</v>
       </c>
       <c r="J541" t="n">
-        <v>3.345963290956833</v>
+        <v>3.346838889823522</v>
       </c>
       <c r="K541" t="n">
-        <v>0.1412964137015938</v>
+        <v>0.1413329765927312</v>
       </c>
       <c r="L541" t="n">
-        <v>0.0483674660073575</v>
+        <v>0.04837218729742084</v>
       </c>
     </row>
     <row r="542">
@@ -22113,25 +22113,25 @@
         <v>240</v>
       </c>
       <c r="F542" s="2" t="n">
-        <v>45625.49879375155</v>
+        <v>45625.50368642832</v>
       </c>
       <c r="G542" t="n">
-        <v>381177.2066727304</v>
+        <v>381417.2066727304</v>
       </c>
       <c r="H542" t="n">
-        <v>59.53198875824688</v>
+        <v>59.53155070319304</v>
       </c>
       <c r="I542" t="n">
-        <v>4.114443186094642</v>
+        <v>4.113848104177349</v>
       </c>
       <c r="J542" t="n">
-        <v>3.346838889823522</v>
+        <v>3.347710282186754</v>
       </c>
       <c r="K542" t="n">
-        <v>0.1413329765927312</v>
+        <v>0.1413695023654911</v>
       </c>
       <c r="L542" t="n">
-        <v>0.04837218729742084</v>
+        <v>0.04837677457971879</v>
       </c>
     </row>
     <row r="543">
@@ -22153,25 +22153,25 @@
         <v>240</v>
       </c>
       <c r="F543" s="2" t="n">
-        <v>45625.50368642832</v>
+        <v>45625.51530954447</v>
       </c>
       <c r="G543" t="n">
-        <v>381417.2066727304</v>
+        <v>381657.2066727304</v>
       </c>
       <c r="H543" t="n">
-        <v>59.53155070319304</v>
+        <v>59.53194260437719</v>
       </c>
       <c r="I543" t="n">
-        <v>4.113848104177349</v>
+        <v>4.112805208253878</v>
       </c>
       <c r="J543" t="n">
-        <v>3.347710282186754</v>
+        <v>3.348298566773943</v>
       </c>
       <c r="K543" t="n">
-        <v>0.1413695023654911</v>
+        <v>0.1414067901703156</v>
       </c>
       <c r="L543" t="n">
-        <v>0.04837677457971879</v>
+        <v>0.0483697229484327</v>
       </c>
     </row>
     <row r="544">
@@ -22193,25 +22193,25 @@
         <v>240</v>
       </c>
       <c r="F544" s="2" t="n">
-        <v>45625.51530954447</v>
+        <v>45625.52020222124</v>
       </c>
       <c r="G544" t="n">
-        <v>381657.2066727304</v>
+        <v>381897.2066727304</v>
       </c>
       <c r="H544" t="n">
-        <v>59.53194260437719</v>
+        <v>59.53233401298752</v>
       </c>
       <c r="I544" t="n">
-        <v>4.112805208253878</v>
+        <v>4.111763623128272</v>
       </c>
       <c r="J544" t="n">
-        <v>3.348298566773943</v>
+        <v>3.3488861119564</v>
       </c>
       <c r="K544" t="n">
-        <v>0.1414067901703156</v>
+        <v>0.1414440311087425</v>
       </c>
       <c r="L544" t="n">
-        <v>0.0483697229484327</v>
+        <v>0.04836268018022013</v>
       </c>
     </row>
     <row r="545">
@@ -22233,25 +22233,25 @@
         <v>240</v>
       </c>
       <c r="F545" s="2" t="n">
-        <v>45625.52020222124</v>
+        <v>45625.52509489801</v>
       </c>
       <c r="G545" t="n">
-        <v>381897.2066727304</v>
+        <v>382137.2066727304</v>
       </c>
       <c r="H545" t="n">
-        <v>59.53233401298752</v>
+        <v>59.5327249299521</v>
       </c>
       <c r="I545" t="n">
-        <v>4.111763623128272</v>
+        <v>4.110723346330805</v>
       </c>
       <c r="J545" t="n">
-        <v>3.3488861119564</v>
+        <v>3.349472919127266</v>
       </c>
       <c r="K545" t="n">
-        <v>0.1414440311087425</v>
+        <v>0.1414812252690748</v>
       </c>
       <c r="L545" t="n">
-        <v>0.04836268018022013</v>
+        <v>0.0483556462583818</v>
       </c>
     </row>
     <row r="546">
@@ -22273,25 +22273,25 @@
         <v>240</v>
       </c>
       <c r="F546" s="2" t="n">
-        <v>45625.52509489801</v>
+        <v>45625.52998757478</v>
       </c>
       <c r="G546" t="n">
-        <v>382137.2066727304</v>
+        <v>382377.2066727304</v>
       </c>
       <c r="H546" t="n">
-        <v>59.5327249299521</v>
+        <v>59.53311535619667</v>
       </c>
       <c r="I546" t="n">
-        <v>4.110723346330805</v>
+        <v>4.10968437539795</v>
       </c>
       <c r="J546" t="n">
-        <v>3.349472919127266</v>
+        <v>3.350058989676187</v>
       </c>
       <c r="K546" t="n">
-        <v>0.1414812252690748</v>
+        <v>0.1415183727393935</v>
       </c>
       <c r="L546" t="n">
-        <v>0.0483556462583818</v>
+        <v>0.04834862116626037</v>
       </c>
     </row>
     <row r="547">
@@ -22313,25 +22313,25 @@
         <v>240</v>
       </c>
       <c r="F547" s="2" t="n">
-        <v>45625.52998757478</v>
+        <v>45625.53488025155</v>
       </c>
       <c r="G547" t="n">
-        <v>382377.2066727304</v>
+        <v>382617.2066727304</v>
       </c>
       <c r="H547" t="n">
-        <v>59.53311535619667</v>
+        <v>59.53350529264468</v>
       </c>
       <c r="I547" t="n">
-        <v>4.10968437539795</v>
+        <v>4.108646707872362</v>
       </c>
       <c r="J547" t="n">
-        <v>3.350058989676187</v>
+        <v>3.350644324989319</v>
       </c>
       <c r="K547" t="n">
-        <v>0.1415183727393935</v>
+        <v>0.1415554736075588</v>
       </c>
       <c r="L547" t="n">
-        <v>0.04834862116626037</v>
+        <v>0.04834160488724027</v>
       </c>
     </row>
     <row r="548">
@@ -22353,25 +22353,25 @@
         <v>240</v>
       </c>
       <c r="F548" s="2" t="n">
-        <v>45625.53488025155</v>
+        <v>45625.53977292832</v>
       </c>
       <c r="G548" t="n">
-        <v>382617.2066727304</v>
+        <v>382857.2066727304</v>
       </c>
       <c r="H548" t="n">
-        <v>59.53350529264468</v>
+        <v>59.53389474021721</v>
       </c>
       <c r="I548" t="n">
-        <v>4.108646707872362</v>
+        <v>4.107610341302857</v>
       </c>
       <c r="J548" t="n">
-        <v>3.350644324989319</v>
+        <v>3.351228926449346</v>
       </c>
       <c r="K548" t="n">
-        <v>0.1415554736075588</v>
+        <v>0.1415925279612106</v>
       </c>
       <c r="L548" t="n">
-        <v>0.04834160488724027</v>
+        <v>0.04833459740474764</v>
       </c>
     </row>
     <row r="549">
@@ -22393,25 +22393,25 @@
         <v>240</v>
       </c>
       <c r="F549" s="2" t="n">
-        <v>45625.53977292832</v>
+        <v>45625.54466560509</v>
       </c>
       <c r="G549" t="n">
-        <v>382857.2066727304</v>
+        <v>383097.2066727304</v>
       </c>
       <c r="H549" t="n">
-        <v>59.53389474021721</v>
+        <v>59.53428369983309</v>
       </c>
       <c r="I549" t="n">
-        <v>4.107610341302857</v>
+        <v>4.106575273244396</v>
       </c>
       <c r="J549" t="n">
-        <v>3.351228926449346</v>
+        <v>3.351812795435483</v>
       </c>
       <c r="K549" t="n">
-        <v>0.1415925279612106</v>
+        <v>0.1416295358877691</v>
       </c>
       <c r="L549" t="n">
-        <v>0.04833459740474764</v>
+        <v>0.0483275987022501</v>
       </c>
     </row>
     <row r="550">
@@ -22433,25 +22433,25 @@
         <v>240</v>
       </c>
       <c r="F550" s="2" t="n">
-        <v>45625.54466560509</v>
+        <v>45625.54955828186</v>
       </c>
       <c r="G550" t="n">
-        <v>383097.2066727304</v>
+        <v>383337.2066727304</v>
       </c>
       <c r="H550" t="n">
-        <v>59.53428369983309</v>
+        <v>59.5346721724088</v>
       </c>
       <c r="I550" t="n">
-        <v>4.106575273244396</v>
+        <v>4.10554150125806</v>
       </c>
       <c r="J550" t="n">
-        <v>3.351812795435483</v>
+        <v>3.352395933323495</v>
       </c>
       <c r="K550" t="n">
-        <v>0.1416295358877691</v>
+        <v>0.1416664974744356</v>
       </c>
       <c r="L550" t="n">
-        <v>0.0483275987022501</v>
+        <v>0.0483206087632567</v>
       </c>
     </row>
     <row r="551">
@@ -22473,25 +22473,25 @@
         <v>240</v>
       </c>
       <c r="F551" s="2" t="n">
-        <v>45625.54955828186</v>
+        <v>45625.55445095863</v>
       </c>
       <c r="G551" t="n">
-        <v>383337.2066727304</v>
+        <v>383577.2066727304</v>
       </c>
       <c r="H551" t="n">
-        <v>59.5346721724088</v>
+        <v>59.53506015885856</v>
       </c>
       <c r="I551" t="n">
-        <v>4.10554150125806</v>
+        <v>4.104509022911035</v>
       </c>
       <c r="J551" t="n">
-        <v>3.352395933323495</v>
+        <v>3.352978341485701</v>
       </c>
       <c r="K551" t="n">
-        <v>0.1416664974744356</v>
+        <v>0.1417034128081932</v>
       </c>
       <c r="L551" t="n">
-        <v>0.0483206087632567</v>
+        <v>0.04831362757131777</v>
       </c>
     </row>
     <row r="552">
@@ -22513,25 +22513,25 @@
         <v>240</v>
       </c>
       <c r="F552" s="2" t="n">
-        <v>45625.55445095863</v>
+        <v>45625.5593436354</v>
       </c>
       <c r="G552" t="n">
-        <v>383577.2066727304</v>
+        <v>383817.2066727304</v>
       </c>
       <c r="H552" t="n">
-        <v>59.53506015885856</v>
+        <v>59.53544766009427</v>
       </c>
       <c r="I552" t="n">
-        <v>4.104509022911035</v>
+        <v>4.103477835776593</v>
       </c>
       <c r="J552" t="n">
-        <v>3.352978341485701</v>
+        <v>3.353560021290989</v>
       </c>
       <c r="K552" t="n">
-        <v>0.1417034128081932</v>
+        <v>0.1417402819758075</v>
       </c>
       <c r="L552" t="n">
-        <v>0.04831362757131777</v>
+        <v>0.04830665511002476</v>
       </c>
     </row>
     <row r="553">
@@ -22553,65 +22553,65 @@
         <v>240</v>
       </c>
       <c r="F553" s="2" t="n">
-        <v>45625.5593436354</v>
+        <v>45625.56423631217</v>
       </c>
       <c r="G553" t="n">
-        <v>383817.2066727304</v>
+        <v>384057.2066727304</v>
       </c>
       <c r="H553" t="n">
-        <v>59.53544766009427</v>
+        <v>59.5358346770256</v>
       </c>
       <c r="I553" t="n">
-        <v>4.103477835776593</v>
+        <v>4.10244793743407</v>
       </c>
       <c r="J553" t="n">
-        <v>3.353560021290989</v>
+        <v>3.354140974104824</v>
       </c>
       <c r="K553" t="n">
-        <v>0.1417402819758075</v>
+        <v>0.1417771050638269</v>
       </c>
       <c r="L553" t="n">
-        <v>0.04830665511002476</v>
+        <v>0.04829969136301014</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B554" s="2" t="n">
-        <v>45625.25</v>
+        <v>45625.56427019872</v>
       </c>
       <c r="C554" s="2" t="n">
+        <v>45625.75</v>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>CEN01_RP01_0106</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>171.5431458111511</v>
+      </c>
+      <c r="F554" s="2" t="n">
         <v>45625.56427019872</v>
       </c>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>CEN01_RP01_0107</t>
-        </is>
-      </c>
-      <c r="E554" t="n">
-        <v>240</v>
-      </c>
-      <c r="F554" s="2" t="n">
-        <v>45625.56423631217</v>
-      </c>
       <c r="G554" t="n">
-        <v>384057.2066727304</v>
+        <v>441287.2201325851</v>
       </c>
       <c r="H554" t="n">
-        <v>59.5358346770256</v>
+        <v>60.88549117897628</v>
       </c>
       <c r="I554" t="n">
-        <v>4.10244793743407</v>
+        <v>3.876758898677794</v>
       </c>
       <c r="J554" t="n">
-        <v>3.354140974104824</v>
+        <v>2.51635316393893</v>
       </c>
       <c r="K554" t="n">
-        <v>0.1417771050638269</v>
+        <v>0.1140228984790576</v>
       </c>
       <c r="L554" t="n">
-        <v>0.04829969136301014</v>
+        <v>0.04137660131252136</v>
       </c>
     </row>
     <row r="555">
@@ -22626,32 +22626,32 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>CEN01_RP01_0106</t>
+          <t>CEN01_RP01_0107</t>
         </is>
       </c>
       <c r="E555" t="n">
-        <v>171.5431458111511</v>
+        <v>240</v>
       </c>
       <c r="F555" s="2" t="n">
-        <v>45625.56427019872</v>
+        <v>45625.56811260735</v>
       </c>
       <c r="G555" t="n">
-        <v>441458.7632783963</v>
+        <v>384297.2066727304</v>
       </c>
       <c r="H555" t="n">
-        <v>60.88663521942041</v>
+        <v>59.53746955562113</v>
       </c>
       <c r="I555" t="n">
-        <v>3.876534699569179</v>
+        <v>4.102678198007082</v>
       </c>
       <c r="J555" t="n">
-        <v>2.515791112031039</v>
+        <v>3.352948698788143</v>
       </c>
       <c r="K555" t="n">
-        <v>0.1140123324826181</v>
+        <v>0.1417395178397604</v>
       </c>
       <c r="L555" t="n">
-        <v>0.04137485918180678</v>
+        <v>0.04828603087879124</v>
       </c>
     </row>
     <row r="556">
@@ -22673,25 +22673,25 @@
         <v>240</v>
       </c>
       <c r="F556" s="2" t="n">
-        <v>45625.56811260735</v>
+        <v>45625.57245982957</v>
       </c>
       <c r="G556" t="n">
-        <v>384297.2066727304</v>
+        <v>384537.2066727304</v>
       </c>
       <c r="H556" t="n">
-        <v>59.53746955562113</v>
+        <v>59.53910239347337</v>
       </c>
       <c r="I556" t="n">
-        <v>4.102678198007082</v>
+        <v>4.102908171156477</v>
       </c>
       <c r="J556" t="n">
-        <v>3.352948698788143</v>
+        <v>3.351757911733566</v>
       </c>
       <c r="K556" t="n">
-        <v>0.1417395178397604</v>
+        <v>0.1417019775340864</v>
       </c>
       <c r="L556" t="n">
-        <v>0.04828603087879124</v>
+        <v>0.04827238744632263</v>
       </c>
     </row>
     <row r="557">
@@ -22713,25 +22713,25 @@
         <v>240</v>
       </c>
       <c r="F557" s="2" t="n">
-        <v>45625.57245982957</v>
+        <v>45625.5768070518</v>
       </c>
       <c r="G557" t="n">
-        <v>384537.2066727304</v>
+        <v>384777.2066727304</v>
       </c>
       <c r="H557" t="n">
-        <v>59.53910239347337</v>
+        <v>59.54073319440099</v>
       </c>
       <c r="I557" t="n">
-        <v>4.102908171156477</v>
+        <v>4.103137857420085</v>
       </c>
       <c r="J557" t="n">
-        <v>3.351757911733566</v>
+        <v>3.350568610156237</v>
       </c>
       <c r="K557" t="n">
-        <v>0.1417019775340864</v>
+        <v>0.1416644840590104</v>
       </c>
       <c r="L557" t="n">
-        <v>0.04827238744632263</v>
+        <v>0.04825876103369686</v>
       </c>
     </row>
     <row r="558">
@@ -22753,25 +22753,25 @@
         <v>240</v>
       </c>
       <c r="F558" s="2" t="n">
-        <v>45625.5768070518</v>
+        <v>45625.58115427402</v>
       </c>
       <c r="G558" t="n">
-        <v>384777.2066727304</v>
+        <v>385017.2066727304</v>
       </c>
       <c r="H558" t="n">
-        <v>59.54073319440099</v>
+        <v>59.54236196221311</v>
       </c>
       <c r="I558" t="n">
-        <v>4.103137857420085</v>
+        <v>4.103367257334397</v>
       </c>
       <c r="J558" t="n">
-        <v>3.350568610156237</v>
+        <v>3.349380791278245</v>
       </c>
       <c r="K558" t="n">
-        <v>0.1416644840590104</v>
+        <v>0.1416270373269572</v>
       </c>
       <c r="L558" t="n">
-        <v>0.04825876103369686</v>
+        <v>0.04824515160908602</v>
       </c>
     </row>
     <row r="559">
@@ -22793,25 +22793,25 @@
         <v>240</v>
       </c>
       <c r="F559" s="2" t="n">
-        <v>45625.58115427402</v>
+        <v>45625.58550149624</v>
       </c>
       <c r="G559" t="n">
-        <v>385017.2066727304</v>
+        <v>385257.2066727304</v>
       </c>
       <c r="H559" t="n">
-        <v>59.54236196221311</v>
+        <v>59.54398870070941</v>
       </c>
       <c r="I559" t="n">
-        <v>4.103367257334397</v>
+        <v>4.103596371434564</v>
       </c>
       <c r="J559" t="n">
-        <v>3.349380791278245</v>
+        <v>3.348194452328601</v>
       </c>
       <c r="K559" t="n">
-        <v>0.1416270373269572</v>
+        <v>0.1415896372505695</v>
       </c>
       <c r="L559" t="n">
-        <v>0.04824515160908602</v>
+        <v>0.04823155914074155</v>
       </c>
     </row>
     <row r="560">
@@ -22833,25 +22833,25 @@
         <v>240</v>
       </c>
       <c r="F560" s="2" t="n">
-        <v>45625.58550149624</v>
+        <v>45625.58984871846</v>
       </c>
       <c r="G560" t="n">
-        <v>385257.2066727304</v>
+        <v>385497.2066727304</v>
       </c>
       <c r="H560" t="n">
-        <v>59.54398870070941</v>
+        <v>59.54561341368005</v>
       </c>
       <c r="I560" t="n">
-        <v>4.103596371434564</v>
+        <v>4.103825200254407</v>
       </c>
       <c r="J560" t="n">
-        <v>3.348194452328601</v>
+        <v>3.347009590543216</v>
       </c>
       <c r="K560" t="n">
-        <v>0.1415896372505695</v>
+        <v>0.1415522837427077</v>
       </c>
       <c r="L560" t="n">
-        <v>0.04823155914074155</v>
+        <v>0.04821798359699392</v>
       </c>
     </row>
     <row r="561">
@@ -22873,25 +22873,25 @@
         <v>240</v>
       </c>
       <c r="F561" s="2" t="n">
-        <v>45625.58984871846</v>
+        <v>45625.59419594068</v>
       </c>
       <c r="G561" t="n">
-        <v>385497.2066727304</v>
+        <v>385737.2066727304</v>
       </c>
       <c r="H561" t="n">
-        <v>59.54561341368005</v>
+        <v>59.54723610490581</v>
       </c>
       <c r="I561" t="n">
-        <v>4.103825200254407</v>
+        <v>4.104053744326418</v>
       </c>
       <c r="J561" t="n">
-        <v>3.347009590543216</v>
+        <v>3.345826203164882</v>
       </c>
       <c r="K561" t="n">
-        <v>0.1415522837427077</v>
+        <v>0.1415149767164492</v>
       </c>
       <c r="L561" t="n">
-        <v>0.04821798359699392</v>
+        <v>0.04820442494625242</v>
       </c>
     </row>
     <row r="562">
@@ -22913,25 +22913,25 @@
         <v>240</v>
       </c>
       <c r="F562" s="2" t="n">
-        <v>45625.59419594068</v>
+        <v>45625.5985431629</v>
       </c>
       <c r="G562" t="n">
-        <v>385737.2066727304</v>
+        <v>385977.2066727304</v>
       </c>
       <c r="H562" t="n">
-        <v>59.54723610490581</v>
+        <v>59.54885677815803</v>
       </c>
       <c r="I562" t="n">
-        <v>4.104053744326418</v>
+        <v>4.104282004181763</v>
       </c>
       <c r="J562" t="n">
-        <v>3.345826203164882</v>
+        <v>3.344644287443246</v>
       </c>
       <c r="K562" t="n">
-        <v>0.1415149767164492</v>
+        <v>0.1414777160850872</v>
       </c>
       <c r="L562" t="n">
-        <v>0.04820442494625242</v>
+        <v>0.04819088315700493</v>
       </c>
     </row>
     <row r="563">
@@ -22953,25 +22953,25 @@
         <v>240</v>
       </c>
       <c r="F563" s="2" t="n">
-        <v>45625.5985431629</v>
+        <v>45625.60289038513</v>
       </c>
       <c r="G563" t="n">
-        <v>385977.2066727304</v>
+        <v>386217.2066727304</v>
       </c>
       <c r="H563" t="n">
-        <v>59.54885677815803</v>
+        <v>59.5504754371987</v>
       </c>
       <c r="I563" t="n">
-        <v>4.104282004181763</v>
+        <v>4.10450998035029</v>
       </c>
       <c r="J563" t="n">
-        <v>3.344644287443246</v>
+        <v>3.343463840634793</v>
       </c>
       <c r="K563" t="n">
-        <v>0.1414777160850872</v>
+        <v>0.1414405017621309</v>
       </c>
       <c r="L563" t="n">
-        <v>0.04819088315700493</v>
+        <v>0.04817735819781763</v>
       </c>
     </row>
     <row r="564">
@@ -22993,25 +22993,25 @@
         <v>240</v>
       </c>
       <c r="F564" s="2" t="n">
-        <v>45625.60289038513</v>
+        <v>45625.60723760735</v>
       </c>
       <c r="G564" t="n">
-        <v>386217.2066727304</v>
+        <v>386457.2066727304</v>
       </c>
       <c r="H564" t="n">
-        <v>59.5504754371987</v>
+        <v>59.55209208578044</v>
       </c>
       <c r="I564" t="n">
-        <v>4.10450998035029</v>
+        <v>4.104737673360529</v>
       </c>
       <c r="J564" t="n">
-        <v>3.343463840634793</v>
+        <v>3.342284860002823</v>
       </c>
       <c r="K564" t="n">
-        <v>0.1414405017621309</v>
+        <v>0.1414033336613039</v>
       </c>
       <c r="L564" t="n">
-        <v>0.04817735819781763</v>
+        <v>0.04816385003733482</v>
       </c>
     </row>
     <row r="565">
@@ -23033,25 +23033,25 @@
         <v>240</v>
       </c>
       <c r="F565" s="2" t="n">
-        <v>45625.60723760735</v>
+        <v>45625.61158482957</v>
       </c>
       <c r="G565" t="n">
-        <v>386457.2066727304</v>
+        <v>386697.2066727304</v>
       </c>
       <c r="H565" t="n">
-        <v>59.55209208578044</v>
+        <v>59.55370672764658</v>
       </c>
       <c r="I565" t="n">
-        <v>4.104737673360529</v>
+        <v>4.104965083739699</v>
       </c>
       <c r="J565" t="n">
-        <v>3.342284860002823</v>
+        <v>3.341107342817429</v>
       </c>
       <c r="K565" t="n">
-        <v>0.1414033336613039</v>
+        <v>0.1413662116965444</v>
       </c>
       <c r="L565" t="n">
-        <v>0.04816385003733482</v>
+        <v>0.04815035864427861</v>
       </c>
     </row>
     <row r="566">
@@ -23070,28 +23070,28 @@
         </is>
       </c>
       <c r="E566" t="n">
-        <v>240</v>
+        <v>232.3566435834532</v>
       </c>
       <c r="F566" s="2" t="n">
-        <v>45625.61158482957</v>
+        <v>45625.61593205179</v>
       </c>
       <c r="G566" t="n">
-        <v>386697.2066727304</v>
+        <v>386929.5633163138</v>
       </c>
       <c r="H566" t="n">
-        <v>59.55370672764658</v>
+        <v>59.55526803914846</v>
       </c>
       <c r="I566" t="n">
-        <v>4.104965083739699</v>
+        <v>4.105184982931024</v>
       </c>
       <c r="J566" t="n">
-        <v>3.341107342817429</v>
+        <v>3.339968718108282</v>
       </c>
       <c r="K566" t="n">
-        <v>0.1413662116965444</v>
+        <v>0.1413303158413912</v>
       </c>
       <c r="L566" t="n">
-        <v>0.04815035864427861</v>
+        <v>0.04813731286143554</v>
       </c>
     </row>
     <row r="567">
@@ -23110,28 +23110,28 @@
         </is>
       </c>
       <c r="E567" t="n">
-        <v>232.3566435834532</v>
+        <v>240</v>
       </c>
       <c r="F567" s="2" t="n">
-        <v>45625.61593205179</v>
+        <v>45625.70924535386</v>
       </c>
       <c r="G567" t="n">
-        <v>386929.5633163138</v>
+        <v>387169.5633163138</v>
       </c>
       <c r="H567" t="n">
-        <v>59.55526803914846</v>
+        <v>59.55452979948172</v>
       </c>
       <c r="I567" t="n">
-        <v>4.105184982931024</v>
+        <v>4.107123310101342</v>
       </c>
       <c r="J567" t="n">
-        <v>3.339968718108282</v>
+        <v>3.339223126203088</v>
       </c>
       <c r="K567" t="n">
-        <v>0.1413303158413912</v>
+        <v>0.1412956957754771</v>
       </c>
       <c r="L567" t="n">
-        <v>0.04813731286143554</v>
+        <v>0.04813618943870825</v>
       </c>
     </row>
     <row r="568">
@@ -23153,25 +23153,25 @@
         <v>240</v>
       </c>
       <c r="F568" s="2" t="n">
-        <v>45625.70924535386</v>
+        <v>45625.71359257609</v>
       </c>
       <c r="G568" t="n">
-        <v>387169.5633163138</v>
+        <v>387409.5633163138</v>
       </c>
       <c r="H568" t="n">
-        <v>59.55452979948172</v>
+        <v>59.55379247449307</v>
       </c>
       <c r="I568" t="n">
-        <v>4.107123310101342</v>
+        <v>4.109059235686543</v>
       </c>
       <c r="J568" t="n">
-        <v>3.339223126203088</v>
+        <v>3.338478458085401</v>
       </c>
       <c r="K568" t="n">
-        <v>0.1412956957754771</v>
+        <v>0.1412611186037846</v>
       </c>
       <c r="L568" t="n">
-        <v>0.04813618943870825</v>
+        <v>0.04813506740790042</v>
       </c>
     </row>
     <row r="569">
@@ -23193,25 +23193,25 @@
         <v>240</v>
       </c>
       <c r="F569" s="2" t="n">
-        <v>45625.71359257609</v>
+        <v>45625.71793979831</v>
       </c>
       <c r="G569" t="n">
-        <v>387409.5633163138</v>
+        <v>387649.5633163138</v>
       </c>
       <c r="H569" t="n">
-        <v>59.55379247449307</v>
+        <v>59.55305606248363</v>
       </c>
       <c r="I569" t="n">
-        <v>4.109059235686543</v>
+        <v>4.110992764147205</v>
       </c>
       <c r="J569" t="n">
-        <v>3.338478458085401</v>
+        <v>3.337734712039426</v>
       </c>
       <c r="K569" t="n">
-        <v>0.1412611186037846</v>
+        <v>0.1412265842466442</v>
       </c>
       <c r="L569" t="n">
-        <v>0.04813506740790042</v>
+        <v>0.04813394676642676</v>
       </c>
     </row>
     <row r="570">
@@ -23233,25 +23233,25 @@
         <v>240</v>
       </c>
       <c r="F570" s="2" t="n">
-        <v>45625.71793979831</v>
+        <v>45625.72228702053</v>
       </c>
       <c r="G570" t="n">
-        <v>387649.5633163138</v>
+        <v>387889.5633163138</v>
       </c>
       <c r="H570" t="n">
-        <v>59.55305606248363</v>
+        <v>59.55232056175875</v>
       </c>
       <c r="I570" t="n">
-        <v>4.110992764147205</v>
+        <v>4.112923899932866</v>
       </c>
       <c r="J570" t="n">
-        <v>3.337734712039426</v>
+        <v>3.336991886353615</v>
       </c>
       <c r="K570" t="n">
-        <v>0.1412265842466442</v>
+        <v>0.1411920926245835</v>
       </c>
       <c r="L570" t="n">
-        <v>0.04813394676642676</v>
+        <v>0.0481328275117084</v>
       </c>
     </row>
     <row r="571">
@@ -23273,25 +23273,25 @@
         <v>240</v>
       </c>
       <c r="F571" s="2" t="n">
-        <v>45625.72228702053</v>
+        <v>45625.72663424275</v>
       </c>
       <c r="G571" t="n">
-        <v>387889.5633163138</v>
+        <v>388129.5633163138</v>
       </c>
       <c r="H571" t="n">
-        <v>59.55232056175875</v>
+        <v>59.55158597062793</v>
       </c>
       <c r="I571" t="n">
-        <v>4.112923899932866</v>
+        <v>4.11485264748206</v>
       </c>
       <c r="J571" t="n">
-        <v>3.336991886353615</v>
+        <v>3.336249979320653</v>
       </c>
       <c r="K571" t="n">
-        <v>0.1411920926245835</v>
+        <v>0.1411576436583268</v>
       </c>
       <c r="L571" t="n">
-        <v>0.0481328275117084</v>
+        <v>0.04813170964117284</v>
       </c>
     </row>
     <row r="572">
@@ -23313,25 +23313,25 @@
         <v>240</v>
       </c>
       <c r="F572" s="2" t="n">
-        <v>45625.72663424275</v>
+        <v>45625.73098146498</v>
       </c>
       <c r="G572" t="n">
-        <v>388129.5633163138</v>
+        <v>388369.5633163138</v>
       </c>
       <c r="H572" t="n">
-        <v>59.55158597062793</v>
+        <v>59.55085228740487</v>
       </c>
       <c r="I572" t="n">
-        <v>4.11485264748206</v>
+        <v>4.116779011222349</v>
       </c>
       <c r="J572" t="n">
-        <v>3.336249979320653</v>
+        <v>3.335508989237446</v>
       </c>
       <c r="K572" t="n">
-        <v>0.1411576436583268</v>
+        <v>0.1411232372687944</v>
       </c>
       <c r="L572" t="n">
-        <v>0.04813170964117284</v>
+        <v>0.04813059315225393</v>
       </c>
     </row>
     <row r="573">
@@ -23353,25 +23353,25 @@
         <v>240</v>
       </c>
       <c r="F573" s="2" t="n">
-        <v>45625.73098146498</v>
+        <v>45625.7353286872</v>
       </c>
       <c r="G573" t="n">
-        <v>388369.5633163138</v>
+        <v>388609.5633163138</v>
       </c>
       <c r="H573" t="n">
-        <v>59.55085228740487</v>
+        <v>59.55011951040745</v>
       </c>
       <c r="I573" t="n">
-        <v>4.116779011222349</v>
+        <v>4.118702995570356</v>
       </c>
       <c r="J573" t="n">
-        <v>3.335508989237446</v>
+        <v>3.334768914405106</v>
       </c>
       <c r="K573" t="n">
-        <v>0.1411232372687944</v>
+        <v>0.1410888733771018</v>
       </c>
       <c r="L573" t="n">
-        <v>0.04813059315225393</v>
+        <v>0.04812947804239188</v>
       </c>
     </row>
     <row r="574">
@@ -23393,25 +23393,25 @@
         <v>240</v>
       </c>
       <c r="F574" s="2" t="n">
-        <v>45625.7353286872</v>
+        <v>45625.73967590942</v>
       </c>
       <c r="G574" t="n">
-        <v>388609.5633163138</v>
+        <v>388849.5633163138</v>
       </c>
       <c r="H574" t="n">
-        <v>59.55011951040745</v>
+        <v>59.54938763795768</v>
       </c>
       <c r="I574" t="n">
-        <v>4.118702995570356</v>
+        <v>4.120624604931802</v>
       </c>
       <c r="J574" t="n">
-        <v>3.334768914405106</v>
+        <v>3.33402975312894</v>
       </c>
       <c r="K574" t="n">
-        <v>0.1410888733771018</v>
+        <v>0.1410545519045593</v>
       </c>
       <c r="L574" t="n">
-        <v>0.04812947804239188</v>
+        <v>0.04812836430903319</v>
       </c>
     </row>
     <row r="575">
@@ -23433,25 +23433,25 @@
         <v>240</v>
       </c>
       <c r="F575" s="2" t="n">
-        <v>45625.73967590942</v>
+        <v>45625.74402313164</v>
       </c>
       <c r="G575" t="n">
-        <v>388849.5633163138</v>
+        <v>389089.5633163138</v>
       </c>
       <c r="H575" t="n">
-        <v>59.54938763795768</v>
+        <v>59.54865666838172</v>
       </c>
       <c r="I575" t="n">
-        <v>4.120624604931802</v>
+        <v>4.122543843701537</v>
       </c>
       <c r="J575" t="n">
-        <v>3.33402975312894</v>
+        <v>3.333291503718438</v>
       </c>
       <c r="K575" t="n">
-        <v>0.1410545519045593</v>
+        <v>0.1410202727726715</v>
       </c>
       <c r="L575" t="n">
-        <v>0.04812836430903319</v>
+        <v>0.0481272519496307</v>
       </c>
     </row>
     <row r="576">
@@ -23473,25 +23473,25 @@
         <v>240</v>
       </c>
       <c r="F576" s="2" t="n">
-        <v>45625.74402313164</v>
+        <v>45625.74837035387</v>
       </c>
       <c r="G576" t="n">
-        <v>389089.5633163138</v>
+        <v>389329.5633163138</v>
       </c>
       <c r="H576" t="n">
-        <v>59.54865666838172</v>
+        <v>59.54792660000984</v>
       </c>
       <c r="I576" t="n">
-        <v>4.122543843701537</v>
+        <v>4.124460716263576</v>
       </c>
       <c r="J576" t="n">
-        <v>3.333291503718438</v>
+        <v>3.332554164487255</v>
       </c>
       <c r="K576" t="n">
-        <v>0.1410202727726715</v>
+        <v>0.1409860359031364</v>
       </c>
       <c r="L576" t="n">
-        <v>0.0481272519496307</v>
+        <v>0.04812614096164348</v>
       </c>
     </row>
     <row r="577">
@@ -23513,25 +23513,25 @@
         <v>240</v>
       </c>
       <c r="F577" s="2" t="n">
-        <v>45625.74837035387</v>
+        <v>45625.56912898894</v>
       </c>
       <c r="G577" t="n">
-        <v>389329.5633163138</v>
+        <v>389569.5633163138</v>
       </c>
       <c r="H577" t="n">
-        <v>59.54792660000984</v>
+        <v>59.54830045287135</v>
       </c>
       <c r="I577" t="n">
-        <v>4.124460716263576</v>
+        <v>4.12343246403439</v>
       </c>
       <c r="J577" t="n">
-        <v>3.332554164487255</v>
+        <v>3.333139837861173</v>
       </c>
       <c r="K577" t="n">
-        <v>0.1409860359031364</v>
+        <v>0.1410228026137113</v>
       </c>
       <c r="L577" t="n">
-        <v>0.04812614096164348</v>
+        <v>0.04811938695907614</v>
       </c>
     </row>
     <row r="578">
@@ -23553,25 +23553,25 @@
         <v>240</v>
       </c>
       <c r="F578" s="2" t="n">
-        <v>45625.56912898894</v>
+        <v>45625.57402166571</v>
       </c>
       <c r="G578" t="n">
-        <v>389569.5633163138</v>
+        <v>389809.5633163138</v>
       </c>
       <c r="H578" t="n">
-        <v>59.54830045287135</v>
+        <v>59.54867384538146</v>
       </c>
       <c r="I578" t="n">
-        <v>4.12343246403439</v>
+        <v>4.122405477964673</v>
       </c>
       <c r="J578" t="n">
-        <v>3.333139837861173</v>
+        <v>3.33372479005417</v>
       </c>
       <c r="K578" t="n">
-        <v>0.1410228026137113</v>
+        <v>0.1410595240508431</v>
       </c>
       <c r="L578" t="n">
-        <v>0.04811938695907614</v>
+        <v>0.04811264127318837</v>
       </c>
     </row>
     <row r="579">
@@ -23593,25 +23593,25 @@
         <v>240</v>
       </c>
       <c r="F579" s="2" t="n">
-        <v>45625.57402166571</v>
+        <v>45625.57891434249</v>
       </c>
       <c r="G579" t="n">
-        <v>389809.5633163138</v>
+        <v>390049.5633163138</v>
       </c>
       <c r="H579" t="n">
-        <v>59.54867384538146</v>
+        <v>59.54904677838996</v>
       </c>
       <c r="I579" t="n">
-        <v>4.122405477964673</v>
+        <v>4.121379755717197</v>
       </c>
       <c r="J579" t="n">
-        <v>3.33372479005417</v>
+        <v>3.33430902239749</v>
       </c>
       <c r="K579" t="n">
-        <v>0.1410595240508431</v>
+        <v>0.141096200298103</v>
       </c>
       <c r="L579" t="n">
-        <v>0.04811264127318837</v>
+        <v>0.04810590388862826</v>
       </c>
     </row>
     <row r="580">
@@ -23633,25 +23633,25 @@
         <v>240</v>
       </c>
       <c r="F580" s="2" t="n">
-        <v>45625.57891434249</v>
+        <v>45625.58380701926</v>
       </c>
       <c r="G580" t="n">
-        <v>390049.5633163138</v>
+        <v>390289.5633163138</v>
       </c>
       <c r="H580" t="n">
-        <v>59.54904677838996</v>
+        <v>59.54941925274452</v>
       </c>
       <c r="I580" t="n">
-        <v>4.121379755717197</v>
+        <v>4.120355294960484</v>
       </c>
       <c r="J580" t="n">
-        <v>3.33430902239749</v>
+        <v>3.334892536219098</v>
       </c>
       <c r="K580" t="n">
-        <v>0.141096200298103</v>
+        <v>0.1411328314388565</v>
       </c>
       <c r="L580" t="n">
-        <v>0.04810590388862826</v>
+        <v>0.04809917479008164</v>
       </c>
     </row>
     <row r="581">
@@ -23673,25 +23673,25 @@
         <v>240</v>
       </c>
       <c r="F581" s="2" t="n">
-        <v>45625.58380701926</v>
+        <v>45625.58869969603</v>
       </c>
       <c r="G581" t="n">
-        <v>390289.5633163138</v>
+        <v>390529.5633163138</v>
       </c>
       <c r="H581" t="n">
-        <v>59.54941925274452</v>
+        <v>59.54979126929074</v>
       </c>
       <c r="I581" t="n">
-        <v>4.120355294960484</v>
+        <v>4.119332093368786</v>
       </c>
       <c r="J581" t="n">
-        <v>3.334892536219098</v>
+        <v>3.335475332843699</v>
       </c>
       <c r="K581" t="n">
-        <v>0.1411328314388565</v>
+        <v>0.1411694175562642</v>
       </c>
       <c r="L581" t="n">
-        <v>0.04809917479008164</v>
+        <v>0.04809245396227201</v>
       </c>
     </row>
     <row r="582">
@@ -23713,25 +23713,25 @@
         <v>240</v>
       </c>
       <c r="F582" s="2" t="n">
-        <v>45625.58869969603</v>
+        <v>45625.5935923728</v>
       </c>
       <c r="G582" t="n">
-        <v>390529.5633163138</v>
+        <v>390769.5633163138</v>
       </c>
       <c r="H582" t="n">
-        <v>59.54979126929074</v>
+        <v>59.55016282887215</v>
       </c>
       <c r="I582" t="n">
-        <v>4.119332093368786</v>
+        <v>4.118310148622068</v>
       </c>
       <c r="J582" t="n">
-        <v>3.335475332843699</v>
+        <v>3.336057413592739</v>
       </c>
       <c r="K582" t="n">
-        <v>0.1411694175562642</v>
+        <v>0.1412059587332825</v>
       </c>
       <c r="L582" t="n">
-        <v>0.04809245396227201</v>
+        <v>0.04808574138996037</v>
       </c>
     </row>
     <row r="583">
@@ -23753,25 +23753,25 @@
         <v>240</v>
       </c>
       <c r="F583" s="2" t="n">
-        <v>45625.5935923728</v>
+        <v>45625.59848504957</v>
       </c>
       <c r="G583" t="n">
-        <v>390769.5633163138</v>
+        <v>391009.5633163138</v>
       </c>
       <c r="H583" t="n">
-        <v>59.55016282887215</v>
+        <v>59.55053393233019</v>
       </c>
       <c r="I583" t="n">
-        <v>4.118310148622068</v>
+        <v>4.117289458405991</v>
       </c>
       <c r="J583" t="n">
-        <v>3.336057413592739</v>
+        <v>3.336638779784425</v>
       </c>
       <c r="K583" t="n">
-        <v>0.1412059587332825</v>
+        <v>0.141242455052664</v>
       </c>
       <c r="L583" t="n">
-        <v>0.04808574138996037</v>
+        <v>0.04807903705794517</v>
       </c>
     </row>
     <row r="584">
@@ -23793,25 +23793,25 @@
         <v>240</v>
       </c>
       <c r="F584" s="2" t="n">
-        <v>45625.59848504957</v>
+        <v>45625.60337772634</v>
       </c>
       <c r="G584" t="n">
-        <v>391009.5633163138</v>
+        <v>391249.5633163138</v>
       </c>
       <c r="H584" t="n">
-        <v>59.55053393233019</v>
+        <v>59.55092583818333</v>
       </c>
       <c r="I584" t="n">
-        <v>4.117289458405991</v>
+        <v>4.116262714303941</v>
       </c>
       <c r="J584" t="n">
-        <v>3.336638779784425</v>
+        <v>3.337203493758155</v>
       </c>
       <c r="K584" t="n">
-        <v>0.141242455052664</v>
+        <v>0.1412794346732965</v>
       </c>
       <c r="L584" t="n">
-        <v>0.04807903705794517</v>
+        <v>0.04807220742418991</v>
       </c>
     </row>
     <row r="585">
@@ -23833,25 +23833,25 @@
         <v>240</v>
       </c>
       <c r="F585" s="2" t="n">
-        <v>45625.60337772634</v>
+        <v>45625.64093092067</v>
       </c>
       <c r="G585" t="n">
-        <v>391249.5633163138</v>
+        <v>391489.5633163138</v>
       </c>
       <c r="H585" t="n">
-        <v>59.55092583818333</v>
+        <v>59.5518534951961</v>
       </c>
       <c r="I585" t="n">
-        <v>4.116262714303941</v>
+        <v>4.115052930197768</v>
       </c>
       <c r="J585" t="n">
-        <v>3.337203493758155</v>
+        <v>3.337365449650315</v>
       </c>
       <c r="K585" t="n">
-        <v>0.1412794346732965</v>
+        <v>0.1413296898461592</v>
       </c>
       <c r="L585" t="n">
-        <v>0.04807220742418991</v>
+        <v>0.04806201790662522</v>
       </c>
     </row>
     <row r="586">
@@ -23873,25 +23873,25 @@
         <v>240</v>
       </c>
       <c r="F586" s="2" t="n">
-        <v>45625.64093092067</v>
+        <v>45625.64582359744</v>
       </c>
       <c r="G586" t="n">
-        <v>391489.5633163138</v>
+        <v>391729.5633163138</v>
       </c>
       <c r="H586" t="n">
-        <v>59.5518534951961</v>
+        <v>59.55278001551812</v>
       </c>
       <c r="I586" t="n">
-        <v>4.115052930197768</v>
+        <v>4.113844628482574</v>
       </c>
       <c r="J586" t="n">
-        <v>3.337365449650315</v>
+        <v>3.337527207092228</v>
       </c>
       <c r="K586" t="n">
-        <v>0.1413296898461592</v>
+        <v>0.1413798834395925</v>
       </c>
       <c r="L586" t="n">
-        <v>0.04806201790662522</v>
+        <v>0.04805184087463447</v>
       </c>
     </row>
     <row r="587">
@@ -23913,25 +23913,25 @@
         <v>240</v>
       </c>
       <c r="F587" s="2" t="n">
-        <v>45625.64582359744</v>
+        <v>45625.65071627421</v>
       </c>
       <c r="G587" t="n">
-        <v>391729.5633163138</v>
+        <v>391969.5633163138</v>
       </c>
       <c r="H587" t="n">
-        <v>59.55278001551812</v>
+        <v>59.55370540123737</v>
       </c>
       <c r="I587" t="n">
-        <v>4.113844628482574</v>
+        <v>4.112637806435388</v>
       </c>
       <c r="J587" t="n">
-        <v>3.337527207092228</v>
+        <v>3.337688766448424</v>
       </c>
       <c r="K587" t="n">
-        <v>0.1413798834395925</v>
+        <v>0.1414300155667104</v>
       </c>
       <c r="L587" t="n">
-        <v>0.04805184087463447</v>
+        <v>0.04804167630528321</v>
       </c>
     </row>
     <row r="588">
@@ -23953,25 +23953,25 @@
         <v>240</v>
       </c>
       <c r="F588" s="2" t="n">
-        <v>45625.65071627421</v>
+        <v>45625.65560895098</v>
       </c>
       <c r="G588" t="n">
-        <v>391969.5633163138</v>
+        <v>392209.5633163138</v>
       </c>
       <c r="H588" t="n">
-        <v>59.55370540123737</v>
+        <v>59.5546296544367</v>
       </c>
       <c r="I588" t="n">
-        <v>4.112637806435388</v>
+        <v>4.111432461339906</v>
       </c>
       <c r="J588" t="n">
-        <v>3.337688766448424</v>
+        <v>3.337850128082539</v>
       </c>
       <c r="K588" t="n">
-        <v>0.1414300155667104</v>
+        <v>0.1414800863403497</v>
       </c>
       <c r="L588" t="n">
-        <v>0.04804167630528321</v>
+        <v>0.0480315241756931</v>
       </c>
     </row>
     <row r="589">
@@ -23993,25 +23993,25 @@
         <v>240</v>
       </c>
       <c r="F589" s="2" t="n">
-        <v>45625.65560895098</v>
+        <v>45625.66050162775</v>
       </c>
       <c r="G589" t="n">
-        <v>392209.5633163138</v>
+        <v>392449.5633163138</v>
       </c>
       <c r="H589" t="n">
-        <v>59.5546296544367</v>
+        <v>59.55555277719386</v>
       </c>
       <c r="I589" t="n">
-        <v>4.111432461339906</v>
+        <v>4.110228590486467</v>
       </c>
       <c r="J589" t="n">
-        <v>3.337850128082539</v>
+        <v>3.33801129235732</v>
       </c>
       <c r="K589" t="n">
-        <v>0.1414800863403497</v>
+        <v>0.1415300958730715</v>
       </c>
       <c r="L589" t="n">
-        <v>0.0480315241756931</v>
+        <v>0.04802138446304177</v>
       </c>
     </row>
     <row r="590">
@@ -24033,25 +24033,25 @@
         <v>240</v>
       </c>
       <c r="F590" s="2" t="n">
-        <v>45625.66050162775</v>
+        <v>45625.66539430452</v>
       </c>
       <c r="G590" t="n">
-        <v>392449.5633163138</v>
+        <v>392689.5633163138</v>
       </c>
       <c r="H590" t="n">
-        <v>59.55555277719386</v>
+        <v>59.55647477158153</v>
       </c>
       <c r="I590" t="n">
-        <v>4.110228590486467</v>
+        <v>4.109026191172034</v>
       </c>
       <c r="J590" t="n">
-        <v>3.33801129235732</v>
+        <v>3.338172259634628</v>
       </c>
       <c r="K590" t="n">
-        <v>0.1415300958730715</v>
+        <v>0.1415800442771615</v>
       </c>
       <c r="L590" t="n">
-        <v>0.04802138446304177</v>
+        <v>0.04801125714456266</v>
       </c>
     </row>
     <row r="591">
@@ -24073,25 +24073,25 @@
         <v>240</v>
       </c>
       <c r="F591" s="2" t="n">
-        <v>45625.66539430452</v>
+        <v>45625.67028698129</v>
       </c>
       <c r="G591" t="n">
-        <v>392689.5633163138</v>
+        <v>392929.5633163138</v>
       </c>
       <c r="H591" t="n">
-        <v>59.55647477158153</v>
+        <v>59.55739563966731</v>
       </c>
       <c r="I591" t="n">
-        <v>4.109026191172034</v>
+        <v>4.107825260700174</v>
       </c>
       <c r="J591" t="n">
-        <v>3.338172259634628</v>
+        <v>3.338333030275438</v>
       </c>
       <c r="K591" t="n">
-        <v>0.1415800442771615</v>
+        <v>0.1416299316646313</v>
       </c>
       <c r="L591" t="n">
-        <v>0.04801125714456266</v>
+        <v>0.0480011421975448</v>
       </c>
     </row>
     <row r="592">
@@ -24113,25 +24113,25 @@
         <v>240</v>
       </c>
       <c r="F592" s="2" t="n">
-        <v>45625.67028698129</v>
+        <v>45625.67517965806</v>
       </c>
       <c r="G592" t="n">
-        <v>392929.5633163138</v>
+        <v>393169.5633163138</v>
       </c>
       <c r="H592" t="n">
-        <v>59.55739563966731</v>
+        <v>59.55831538351378</v>
       </c>
       <c r="I592" t="n">
-        <v>4.107825260700174</v>
+        <v>4.106625796381039</v>
       </c>
       <c r="J592" t="n">
-        <v>3.338333030275438</v>
+        <v>3.338493604639845</v>
       </c>
       <c r="K592" t="n">
-        <v>0.1416299316646313</v>
+        <v>0.1416797581472187</v>
       </c>
       <c r="L592" t="n">
-        <v>0.0480011421975448</v>
+        <v>0.0479910395993327</v>
       </c>
     </row>
     <row r="593">
@@ -24153,25 +24153,25 @@
         <v>240</v>
       </c>
       <c r="F593" s="2" t="n">
-        <v>45625.67517965806</v>
+        <v>45625.68007233484</v>
       </c>
       <c r="G593" t="n">
-        <v>393169.5633163138</v>
+        <v>393409.5633163138</v>
       </c>
       <c r="H593" t="n">
-        <v>59.55831538351378</v>
+        <v>59.55923400517846</v>
       </c>
       <c r="I593" t="n">
-        <v>4.106625796381039</v>
+        <v>4.105427795531343</v>
       </c>
       <c r="J593" t="n">
-        <v>3.338493604639845</v>
+        <v>3.338653983087065</v>
       </c>
       <c r="K593" t="n">
-        <v>0.1416797581472187</v>
+        <v>0.1417295238363891</v>
       </c>
       <c r="L593" t="n">
-        <v>0.0479910395993327</v>
+        <v>0.04798094932732615</v>
       </c>
     </row>
     <row r="594">
@@ -24193,25 +24193,25 @@
         <v>240</v>
       </c>
       <c r="F594" s="2" t="n">
-        <v>45625.68007233484</v>
+        <v>45625.68496501161</v>
       </c>
       <c r="G594" t="n">
-        <v>393409.5633163138</v>
+        <v>393649.5633163138</v>
       </c>
       <c r="H594" t="n">
-        <v>59.55923400517846</v>
+        <v>59.56015150671387</v>
       </c>
       <c r="I594" t="n">
-        <v>4.105427795531343</v>
+        <v>4.104231255474346</v>
       </c>
       <c r="J594" t="n">
-        <v>3.338653983087065</v>
+        <v>3.338814165975439</v>
       </c>
       <c r="K594" t="n">
-        <v>0.1417295238363891</v>
+        <v>0.141779228843336</v>
       </c>
       <c r="L594" t="n">
-        <v>0.04798094932732615</v>
+        <v>0.04797087135898005</v>
       </c>
     </row>
     <row r="595">
@@ -24233,25 +24233,25 @@
         <v>240</v>
       </c>
       <c r="F595" s="2" t="n">
-        <v>45625.68496501161</v>
+        <v>45625.68985768838</v>
       </c>
       <c r="G595" t="n">
-        <v>393649.5633163138</v>
+        <v>393889.5633163138</v>
       </c>
       <c r="H595" t="n">
-        <v>59.56015150671387</v>
+        <v>59.56106789016751</v>
       </c>
       <c r="I595" t="n">
-        <v>4.104231255474346</v>
+        <v>4.10303617353983</v>
       </c>
       <c r="J595" t="n">
-        <v>3.338814165975439</v>
+        <v>3.338974153662432</v>
       </c>
       <c r="K595" t="n">
-        <v>0.141779228843336</v>
+        <v>0.1418288732789818</v>
       </c>
       <c r="L595" t="n">
-        <v>0.04797087135898005</v>
+        <v>0.04796080567180425</v>
       </c>
     </row>
     <row r="596">
@@ -24273,25 +24273,25 @@
         <v>240</v>
       </c>
       <c r="F596" s="2" t="n">
-        <v>45625.68985768838</v>
+        <v>45625.69475036515</v>
       </c>
       <c r="G596" t="n">
-        <v>393889.5633163138</v>
+        <v>394129.5633163138</v>
       </c>
       <c r="H596" t="n">
-        <v>59.56106789016751</v>
+        <v>59.56198315758193</v>
       </c>
       <c r="I596" t="n">
-        <v>4.10303617353983</v>
+        <v>4.101842547064082</v>
       </c>
       <c r="J596" t="n">
-        <v>3.338974153662432</v>
+        <v>3.339133946504641</v>
       </c>
       <c r="K596" t="n">
-        <v>0.1418288732789818</v>
+        <v>0.1418784572539788</v>
       </c>
       <c r="L596" t="n">
-        <v>0.04796080567180425</v>
+        <v>0.04795075224336338</v>
       </c>
     </row>
     <row r="597">
@@ -24313,25 +24313,25 @@
         <v>240</v>
       </c>
       <c r="F597" s="2" t="n">
-        <v>45625.69475036515</v>
+        <v>45625.69964304192</v>
       </c>
       <c r="G597" t="n">
-        <v>394129.5633163138</v>
+        <v>394369.5633163138</v>
       </c>
       <c r="H597" t="n">
-        <v>59.56198315758193</v>
+        <v>59.56289731099464</v>
       </c>
       <c r="I597" t="n">
-        <v>4.101842547064082</v>
+        <v>4.100650373389872</v>
       </c>
       <c r="J597" t="n">
-        <v>3.339133946504641</v>
+        <v>3.339293544857794</v>
       </c>
       <c r="K597" t="n">
-        <v>0.1418784572539788</v>
+        <v>0.1419279808787099</v>
       </c>
       <c r="L597" t="n">
-        <v>0.04795075224336338</v>
+        <v>0.04794071105127667</v>
       </c>
     </row>
     <row r="598">
@@ -24353,25 +24353,25 @@
         <v>240</v>
       </c>
       <c r="F598" s="2" t="n">
-        <v>45625.69964304192</v>
+        <v>45625.70453571869</v>
       </c>
       <c r="G598" t="n">
-        <v>394369.5633163138</v>
+        <v>394609.5633163138</v>
       </c>
       <c r="H598" t="n">
-        <v>59.56289731099464</v>
+        <v>59.56381035243827</v>
       </c>
       <c r="I598" t="n">
-        <v>4.100650373389872</v>
+        <v>4.099459649866436</v>
       </c>
       <c r="J598" t="n">
-        <v>3.339293544857794</v>
+        <v>3.339452949076752</v>
       </c>
       <c r="K598" t="n">
-        <v>0.1419279808787099</v>
+        <v>0.1419774442632895</v>
       </c>
       <c r="L598" t="n">
-        <v>0.04794071105127667</v>
+        <v>0.04793068207321784</v>
       </c>
     </row>
     <row r="599">
@@ -24393,25 +24393,25 @@
         <v>240</v>
       </c>
       <c r="F599" s="2" t="n">
-        <v>45625.70453571869</v>
+        <v>45625.70942839546</v>
       </c>
       <c r="G599" t="n">
-        <v>394609.5633163138</v>
+        <v>394849.5633163138</v>
       </c>
       <c r="H599" t="n">
-        <v>59.56381035243827</v>
+        <v>59.56472228394046</v>
       </c>
       <c r="I599" t="n">
-        <v>4.099459649866436</v>
+        <v>4.098270373849454</v>
       </c>
       <c r="J599" t="n">
-        <v>3.339452949076752</v>
+        <v>3.339612159515516</v>
       </c>
       <c r="K599" t="n">
-        <v>0.1419774442632895</v>
+        <v>0.1420268475175643</v>
       </c>
       <c r="L599" t="n">
-        <v>0.04793068207321784</v>
+        <v>0.04792066528691484</v>
       </c>
     </row>
     <row r="600">
@@ -24433,25 +24433,25 @@
         <v>240</v>
       </c>
       <c r="F600" s="2" t="n">
-        <v>45625.70942839546</v>
+        <v>45625.71432107224</v>
       </c>
       <c r="G600" t="n">
-        <v>394849.5633163138</v>
+        <v>395089.5633163138</v>
       </c>
       <c r="H600" t="n">
-        <v>59.56472228394046</v>
+        <v>59.56563310752394</v>
       </c>
       <c r="I600" t="n">
-        <v>4.098270373849454</v>
+        <v>4.097082542701031</v>
       </c>
       <c r="J600" t="n">
-        <v>3.339612159515516</v>
+        <v>3.339771176527226</v>
       </c>
       <c r="K600" t="n">
-        <v>0.1420268475175643</v>
+        <v>0.1420761907511141</v>
       </c>
       <c r="L600" t="n">
-        <v>0.04792066528691484</v>
+        <v>0.04791066067014976</v>
       </c>
     </row>
     <row r="601">
@@ -24473,25 +24473,25 @@
         <v>240</v>
       </c>
       <c r="F601" s="2" t="n">
-        <v>45625.71432107224</v>
+        <v>45625.71921374901</v>
       </c>
       <c r="G601" t="n">
-        <v>395089.5633163138</v>
+        <v>395329.5633163138</v>
       </c>
       <c r="H601" t="n">
-        <v>59.56563310752394</v>
+        <v>59.56654282520651</v>
       </c>
       <c r="I601" t="n">
-        <v>4.097082542701031</v>
+        <v>4.095896153789679</v>
       </c>
       <c r="J601" t="n">
-        <v>3.339771176527226</v>
+        <v>3.339930000464162</v>
       </c>
       <c r="K601" t="n">
-        <v>0.1420761907511141</v>
+        <v>0.1421254740732524</v>
       </c>
       <c r="L601" t="n">
-        <v>0.04791066067014976</v>
+        <v>0.04790066820075867</v>
       </c>
     </row>
     <row r="602">
@@ -24513,25 +24513,25 @@
         <v>240</v>
       </c>
       <c r="F602" s="2" t="n">
-        <v>45625.71921374901</v>
+        <v>45625.72410642578</v>
       </c>
       <c r="G602" t="n">
-        <v>395329.5633163138</v>
+        <v>395569.5633163138</v>
       </c>
       <c r="H602" t="n">
-        <v>59.56654282520651</v>
+        <v>59.5674514390011</v>
       </c>
       <c r="I602" t="n">
-        <v>4.095896153789679</v>
+        <v>4.094711204490294</v>
       </c>
       <c r="J602" t="n">
-        <v>3.339930000464162</v>
+        <v>3.340088631677753</v>
       </c>
       <c r="K602" t="n">
-        <v>0.1421254740732524</v>
+        <v>0.1421746975930277</v>
       </c>
       <c r="L602" t="n">
-        <v>0.04790066820075867</v>
+        <v>0.04789068785663136</v>
       </c>
     </row>
     <row r="603">
@@ -24553,25 +24553,25 @@
         <v>240</v>
       </c>
       <c r="F603" s="2" t="n">
-        <v>45625.72410642578</v>
+        <v>45625.72899910255</v>
       </c>
       <c r="G603" t="n">
-        <v>395569.5633163138</v>
+        <v>395809.5633163138</v>
       </c>
       <c r="H603" t="n">
-        <v>59.5674514390011</v>
+        <v>59.56835895091574</v>
       </c>
       <c r="I603" t="n">
-        <v>4.094711204490294</v>
+        <v>4.093527692184142</v>
       </c>
       <c r="J603" t="n">
-        <v>3.340088631677753</v>
+        <v>3.340247070518573</v>
       </c>
       <c r="K603" t="n">
-        <v>0.1421746975930277</v>
+        <v>0.1422238614192239</v>
       </c>
       <c r="L603" t="n">
-        <v>0.04789068785663136</v>
+        <v>0.04788071961571133</v>
       </c>
     </row>
     <row r="604">
@@ -24593,25 +24593,25 @@
         <v>240</v>
       </c>
       <c r="F604" s="2" t="n">
-        <v>45625.72899910255</v>
+        <v>45625.73389177932</v>
       </c>
       <c r="G604" t="n">
-        <v>395809.5633163138</v>
+        <v>396049.5633163138</v>
       </c>
       <c r="H604" t="n">
-        <v>59.56835895091574</v>
+        <v>59.5692653629536</v>
       </c>
       <c r="I604" t="n">
-        <v>4.093527692184142</v>
+        <v>4.092345614258834</v>
       </c>
       <c r="J604" t="n">
-        <v>3.340247070518573</v>
+        <v>3.340405317336347</v>
       </c>
       <c r="K604" t="n">
-        <v>0.1422238614192239</v>
+        <v>0.1422729656603612</v>
       </c>
       <c r="L604" t="n">
-        <v>0.04788071961571133</v>
+        <v>0.04787076345599547</v>
       </c>
     </row>
     <row r="605">
@@ -24633,25 +24633,25 @@
         <v>240</v>
       </c>
       <c r="F605" s="2" t="n">
-        <v>45625.73389177932</v>
+        <v>45625.73878445609</v>
       </c>
       <c r="G605" t="n">
-        <v>396049.5633163138</v>
+        <v>396289.5633163138</v>
       </c>
       <c r="H605" t="n">
-        <v>59.5692653629536</v>
+        <v>59.57017067711299</v>
       </c>
       <c r="I605" t="n">
-        <v>4.092345614258834</v>
+        <v>4.09116496810831</v>
       </c>
       <c r="J605" t="n">
-        <v>3.340405317336347</v>
+        <v>3.340563372479952</v>
       </c>
       <c r="K605" t="n">
-        <v>0.1422729656603612</v>
+        <v>0.1423220104246968</v>
       </c>
       <c r="L605" t="n">
-        <v>0.04787076345599547</v>
+        <v>0.04786081935553403</v>
       </c>
     </row>
     <row r="606">
@@ -24673,25 +24673,25 @@
         <v>240</v>
       </c>
       <c r="F606" s="2" t="n">
-        <v>45625.73878445609</v>
+        <v>45625.74367713286</v>
       </c>
       <c r="G606" t="n">
-        <v>396289.5633163138</v>
+        <v>396529.5633163138</v>
       </c>
       <c r="H606" t="n">
-        <v>59.57017067711299</v>
+        <v>59.5710748953874</v>
       </c>
       <c r="I606" t="n">
-        <v>4.09116496810831</v>
+        <v>4.08998575113282</v>
       </c>
       <c r="J606" t="n">
-        <v>3.340563372479952</v>
+        <v>3.340721236297421</v>
       </c>
       <c r="K606" t="n">
-        <v>0.1423220104246968</v>
+        <v>0.1423709958202261</v>
       </c>
       <c r="L606" t="n">
-        <v>0.04786081935553403</v>
+        <v>0.04785088729243037</v>
       </c>
     </row>
     <row r="607">
@@ -24713,64 +24713,24 @@
         <v>240</v>
       </c>
       <c r="F607" s="2" t="n">
-        <v>45625.74367713286</v>
+        <v>45625.74856980963</v>
       </c>
       <c r="G607" t="n">
-        <v>396529.5633163138</v>
+        <v>396769.5633163138</v>
       </c>
       <c r="H607" t="n">
-        <v>59.5710748953874</v>
+        <v>59.57197801976546</v>
       </c>
       <c r="I607" t="n">
-        <v>4.08998575113282</v>
+        <v>4.088807960738905</v>
       </c>
       <c r="J607" t="n">
-        <v>3.340721236297421</v>
+        <v>3.340878909135947</v>
       </c>
       <c r="K607" t="n">
-        <v>0.1423709958202261</v>
+        <v>0.1424199219546828</v>
       </c>
       <c r="L607" t="n">
-        <v>0.04785088729243037</v>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="n">
-        <v>3</v>
-      </c>
-      <c r="B608" s="2" t="n">
-        <v>45625.56427019872</v>
-      </c>
-      <c r="C608" s="2" t="n">
-        <v>45625.75</v>
-      </c>
-      <c r="D608" t="inlineStr">
-        <is>
-          <t>CEN01_RP01_0107</t>
-        </is>
-      </c>
-      <c r="E608" t="n">
-        <v>240</v>
-      </c>
-      <c r="F608" s="2" t="n">
-        <v>45625.74856980963</v>
-      </c>
-      <c r="G608" t="n">
-        <v>396769.5633163138</v>
-      </c>
-      <c r="H608" t="n">
-        <v>59.57197801976546</v>
-      </c>
-      <c r="I608" t="n">
-        <v>4.088807960738905</v>
-      </c>
-      <c r="J608" t="n">
-        <v>3.340878909135947</v>
-      </c>
-      <c r="K608" t="n">
-        <v>0.1424199219546828</v>
-      </c>
-      <c r="L608" t="n">
         <v>0.04784096724484081</v>
       </c>
     </row>

--- a/blendmaster_backend_OOP/output/build_report_2024-11-28_06-00.xlsx
+++ b/blendmaster_backend_OOP/output/build_report_2024-11-28_06-00.xlsx
@@ -30913,22 +30913,22 @@
         <v>45625.56427019872</v>
       </c>
       <c r="J575" t="n">
-        <v>445744.7353634185</v>
+        <v>441287.2201325851</v>
       </c>
       <c r="K575" t="n">
-        <v>60.88547961380101</v>
+        <v>60.88549117897628</v>
       </c>
       <c r="L575" t="n">
-        <v>3.876761165120385</v>
+        <v>3.876758898677794</v>
       </c>
       <c r="M575" t="n">
-        <v>2.516358845756266</v>
+        <v>2.51635316393893</v>
       </c>
       <c r="N575" t="n">
-        <v>0.114023005291366</v>
+        <v>0.1140228984790576</v>
       </c>
       <c r="O575" t="n">
-        <v>0.041376618923828</v>
+        <v>0.04137660131252136</v>
       </c>
     </row>
     <row r="576">
